--- a/ficha-v01/ficha-projeto-m-0.1.xlsx
+++ b/ficha-v01/ficha-projeto-m-0.1.xlsx
@@ -19,7 +19,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="38">
+  <fonts count="39">
     <font>
       <name val="Roboto"/>
       <color rgb="00F4F1F7"/>
@@ -178,6 +178,11 @@
     <font>
       <name val="Castoro"/>
       <color rgb="FFE8DCD4"/>
+      <sz val="6"/>
+    </font>
+    <font>
+      <name val="Castoro"/>
+      <color rgb="FFE8DCD4"/>
       <sz val="10"/>
     </font>
     <font>
@@ -262,7 +267,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="30">
+  <borders count="31">
     <border>
       <left/>
       <right/>
@@ -520,6 +525,17 @@
       </right>
     </border>
     <border>
+      <left style="medium">
+        <color rgb="FF8A7EC4"/>
+      </left>
+      <top style="medium">
+        <color rgb="FF8A7EC4"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FF8A7EC4"/>
+      </bottom>
+    </border>
+    <border>
       <left/>
       <right style="thin">
         <color rgb="FFFFFFFF"/>
@@ -532,7 +548,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="106">
+  <cellXfs count="108">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -752,7 +768,7 @@
     <xf numFmtId="0" fontId="26" fillId="5" borderId="28" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="30" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="18" fillId="5" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -771,29 +787,35 @@
     <xf numFmtId="0" fontId="30" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="31" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="18" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="32" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="5" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="33" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="32" fillId="5" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="5" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="34" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="35" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="33" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="36" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -805,7 +827,7 @@
     <xf numFmtId="0" fontId="7" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="36" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="3" fontId="37" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -814,13 +836,13 @@
     <xf numFmtId="0" fontId="7" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="37" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="38" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="37" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="38" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1045,9 +1067,9 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>42</col>
+      <col>40</col>
       <colOff>0</colOff>
-      <row>80</row>
+      <row>83</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="2857500" cy="2857500"/>
@@ -6490,7 +6512,11 @@
       <c r="N58" s="47" t="n"/>
       <c r="O58" s="47" t="n"/>
       <c r="P58" s="47" t="n"/>
-      <c r="Q58" s="47" t="n"/>
+      <c r="Q58" s="88" t="inlineStr">
+        <is>
+          <t>Extra</t>
+        </is>
+      </c>
       <c r="R58" s="47" t="n"/>
       <c r="S58" s="47" t="n"/>
       <c r="T58" s="47" t="n"/>
@@ -6505,7 +6531,11 @@
       <c r="AC58" s="47" t="n"/>
       <c r="AD58" s="47" t="n"/>
       <c r="AE58" s="47" t="n"/>
-      <c r="AF58" s="47" t="n"/>
+      <c r="AF58" s="88" t="inlineStr">
+        <is>
+          <t>Extra</t>
+        </is>
+      </c>
       <c r="AG58" s="47" t="n"/>
       <c r="AH58" s="47" t="n"/>
       <c r="AI58" s="47" t="n"/>
@@ -6526,10 +6556,10 @@
       <c r="A59" s="7" t="n"/>
       <c r="B59" s="7" t="n"/>
       <c r="C59" s="40" t="n"/>
-      <c r="D59" s="88" t="b">
+      <c r="D59" s="89" t="b">
         <v>0</v>
       </c>
-      <c r="E59" s="89" t="inlineStr">
+      <c r="E59" s="90" t="inlineStr">
         <is>
           <t>Atletismo</t>
         </is>
@@ -6541,46 +6571,46 @@
       <c r="J59" s="10" t="n"/>
       <c r="K59" s="10" t="n"/>
       <c r="L59" s="11" t="n"/>
-      <c r="M59" s="90" t="inlineStr">
+      <c r="M59" s="91" t="inlineStr">
         <is>
           <t>For</t>
         </is>
       </c>
       <c r="N59" s="11" t="n"/>
-      <c r="O59" s="91">
-        <f>$D$17+IF($D$59=TRUE,(1+COUNTIF(DADOS!$X$5:$X$7,"&lt;="&amp;$AH$11)),0)</f>
+      <c r="O59" s="92">
+        <f>$D$17+IF($D$59=TRUE,(1+COUNTIF(DADOS!$X$5:$X$7,"&lt;="&amp;$AH$11)),0)+Q59</f>
         <v/>
       </c>
       <c r="P59" s="11" t="n"/>
-      <c r="Q59" s="47" t="n"/>
-      <c r="R59" s="88" t="b">
+      <c r="Q59" s="93" t="n"/>
+      <c r="R59" s="47" t="n"/>
+      <c r="S59" s="89" t="b">
         <v>0</v>
       </c>
-      <c r="S59" s="89" t="inlineStr">
+      <c r="T59" s="90" t="inlineStr">
         <is>
           <t>Sobrevivência</t>
         </is>
       </c>
-      <c r="T59" s="10" t="n"/>
       <c r="U59" s="10" t="n"/>
       <c r="V59" s="10" t="n"/>
       <c r="W59" s="10" t="n"/>
       <c r="X59" s="10" t="n"/>
       <c r="Y59" s="10" t="n"/>
-      <c r="Z59" s="11" t="n"/>
-      <c r="AA59" s="90" t="inlineStr">
+      <c r="Z59" s="10" t="n"/>
+      <c r="AA59" s="11" t="n"/>
+      <c r="AB59" s="91" t="inlineStr">
         <is>
           <t>Int</t>
         </is>
       </c>
-      <c r="AB59" s="11" t="n"/>
-      <c r="AC59" s="91">
-        <f>$AB$17+IF($R$59=TRUE,(1+COUNTIF(DADOS!$X$5:$X$7,"&lt;="&amp;$AH$11)),0)</f>
+      <c r="AC59" s="11" t="n"/>
+      <c r="AD59" s="92">
+        <f>$AB$17+IF($S59=TRUE,(1+COUNTIF(DADOS!$X$5:$X$7,"&lt;="&amp;$AH$11)),0)+AF59</f>
         <v/>
       </c>
-      <c r="AD59" s="11" t="n"/>
-      <c r="AE59" s="47" t="n"/>
-      <c r="AF59" s="47" t="n"/>
+      <c r="AE59" s="11" t="n"/>
+      <c r="AF59" s="93" t="n"/>
       <c r="AG59" s="47" t="n"/>
       <c r="AH59" s="47" t="n"/>
       <c r="AI59" s="47" t="n"/>
@@ -6601,10 +6631,10 @@
       <c r="A60" s="7" t="n"/>
       <c r="B60" s="7" t="n"/>
       <c r="C60" s="40" t="n"/>
-      <c r="D60" s="88" t="b">
+      <c r="D60" s="89" t="b">
         <v>0</v>
       </c>
-      <c r="E60" s="89" t="inlineStr">
+      <c r="E60" s="90" t="inlineStr">
         <is>
           <t>Acrobacia</t>
         </is>
@@ -6616,46 +6646,46 @@
       <c r="J60" s="10" t="n"/>
       <c r="K60" s="10" t="n"/>
       <c r="L60" s="11" t="n"/>
-      <c r="M60" s="90" t="inlineStr">
+      <c r="M60" s="91" t="inlineStr">
         <is>
           <t>Des</t>
         </is>
       </c>
       <c r="N60" s="11" t="n"/>
-      <c r="O60" s="91">
-        <f>$L$17+IF($D$60=TRUE,(1+COUNTIF(DADOS!$X$5:$X$7,"&lt;="&amp;$AH$11)),0)</f>
+      <c r="O60" s="92">
+        <f>$L$17+IF($D60=TRUE,(1+COUNTIF(DADOS!$X$5:$X$7,"&lt;="&amp;$AH$11)),0)+Q60</f>
         <v/>
       </c>
       <c r="P60" s="11" t="n"/>
-      <c r="Q60" s="47" t="n"/>
-      <c r="R60" s="88" t="b">
+      <c r="Q60" s="93" t="n"/>
+      <c r="R60" s="47" t="n"/>
+      <c r="S60" s="89" t="b">
         <v>0</v>
       </c>
-      <c r="S60" s="89" t="inlineStr">
+      <c r="T60" s="90" t="inlineStr">
         <is>
           <t>Natureza</t>
         </is>
       </c>
-      <c r="T60" s="10" t="n"/>
       <c r="U60" s="10" t="n"/>
       <c r="V60" s="10" t="n"/>
       <c r="W60" s="10" t="n"/>
       <c r="X60" s="10" t="n"/>
       <c r="Y60" s="10" t="n"/>
-      <c r="Z60" s="11" t="n"/>
-      <c r="AA60" s="90" t="inlineStr">
+      <c r="Z60" s="10" t="n"/>
+      <c r="AA60" s="11" t="n"/>
+      <c r="AB60" s="91" t="inlineStr">
         <is>
           <t>Int</t>
         </is>
       </c>
-      <c r="AB60" s="11" t="n"/>
-      <c r="AC60" s="91">
-        <f>$AB$17+IF($R$60=TRUE,(1+COUNTIF(DADOS!$X$5:$X$7,"&lt;="&amp;$AH$11)),0)</f>
+      <c r="AC60" s="11" t="n"/>
+      <c r="AD60" s="92">
+        <f>$AB$17+IF($S60=TRUE,(1+COUNTIF(DADOS!$X$5:$X$7,"&lt;="&amp;$AH$11)),0)+AF60</f>
         <v/>
       </c>
-      <c r="AD60" s="11" t="n"/>
-      <c r="AE60" s="47" t="n"/>
-      <c r="AF60" s="47" t="n"/>
+      <c r="AE60" s="11" t="n"/>
+      <c r="AF60" s="93" t="n"/>
       <c r="AG60" s="47" t="n"/>
       <c r="AH60" s="47" t="n"/>
       <c r="AI60" s="51" t="inlineStr">
@@ -6680,10 +6710,10 @@
       <c r="A61" s="7" t="n"/>
       <c r="B61" s="7" t="n"/>
       <c r="C61" s="40" t="n"/>
-      <c r="D61" s="88" t="b">
+      <c r="D61" s="89" t="b">
         <v>0</v>
       </c>
-      <c r="E61" s="89" t="inlineStr">
+      <c r="E61" s="90" t="inlineStr">
         <is>
           <t>Furtividade</t>
         </is>
@@ -6695,46 +6725,46 @@
       <c r="J61" s="10" t="n"/>
       <c r="K61" s="10" t="n"/>
       <c r="L61" s="11" t="n"/>
-      <c r="M61" s="90" t="inlineStr">
+      <c r="M61" s="91" t="inlineStr">
         <is>
           <t>Des</t>
         </is>
       </c>
       <c r="N61" s="11" t="n"/>
-      <c r="O61" s="91">
-        <f>$L$17+IF($D$61=TRUE,(1+COUNTIF(DADOS!$X$5:$X$7,"&lt;="&amp;$AH$11)),0)</f>
+      <c r="O61" s="92">
+        <f>$L$17+IF($D61=TRUE,(1+COUNTIF(DADOS!$X$5:$X$7,"&lt;="&amp;$AH$11)),0)+Q61</f>
         <v/>
       </c>
       <c r="P61" s="11" t="n"/>
-      <c r="Q61" s="47" t="n"/>
-      <c r="R61" s="88" t="b">
+      <c r="Q61" s="93" t="n"/>
+      <c r="R61" s="47" t="n"/>
+      <c r="S61" s="89" t="b">
         <v>0</v>
       </c>
-      <c r="S61" s="89" t="inlineStr">
+      <c r="T61" s="90" t="inlineStr">
         <is>
           <t>Lidar com Animais</t>
         </is>
       </c>
-      <c r="T61" s="10" t="n"/>
       <c r="U61" s="10" t="n"/>
       <c r="V61" s="10" t="n"/>
       <c r="W61" s="10" t="n"/>
       <c r="X61" s="10" t="n"/>
       <c r="Y61" s="10" t="n"/>
-      <c r="Z61" s="11" t="n"/>
-      <c r="AA61" s="90" t="inlineStr">
+      <c r="Z61" s="10" t="n"/>
+      <c r="AA61" s="11" t="n"/>
+      <c r="AB61" s="91" t="inlineStr">
         <is>
           <t>Int</t>
         </is>
       </c>
-      <c r="AB61" s="11" t="n"/>
-      <c r="AC61" s="91">
-        <f>$AB$17+IF($R$61=TRUE,(1+COUNTIF(DADOS!$X$5:$X$7,"&lt;="&amp;$AH$11)),0)</f>
+      <c r="AC61" s="11" t="n"/>
+      <c r="AD61" s="92">
+        <f>$AB$17+IF($S61=TRUE,(1+COUNTIF(DADOS!$X$5:$X$7,"&lt;="&amp;$AH$11)),0)+AF61</f>
         <v/>
       </c>
-      <c r="AD61" s="11" t="n"/>
-      <c r="AE61" s="47" t="n"/>
-      <c r="AF61" s="47" t="n"/>
+      <c r="AE61" s="11" t="n"/>
+      <c r="AF61" s="93" t="n"/>
       <c r="AG61" s="47" t="n"/>
       <c r="AH61" s="47" t="n"/>
       <c r="AI61" s="86" t="n"/>
@@ -6755,10 +6785,10 @@
       <c r="A62" s="7" t="n"/>
       <c r="B62" s="7" t="n"/>
       <c r="C62" s="40" t="n"/>
-      <c r="D62" s="88" t="b">
+      <c r="D62" s="89" t="b">
         <v>0</v>
       </c>
-      <c r="E62" s="89" t="inlineStr">
+      <c r="E62" s="90" t="inlineStr">
         <is>
           <t>Pontaria</t>
         </is>
@@ -6770,46 +6800,46 @@
       <c r="J62" s="10" t="n"/>
       <c r="K62" s="10" t="n"/>
       <c r="L62" s="11" t="n"/>
-      <c r="M62" s="90" t="inlineStr">
+      <c r="M62" s="91" t="inlineStr">
         <is>
           <t>Des</t>
         </is>
       </c>
       <c r="N62" s="11" t="n"/>
-      <c r="O62" s="91">
-        <f>$L$17+IF($D$62=TRUE,(1+COUNTIF(DADOS!$X$5:$X$7,"&lt;="&amp;$AH$11)),0)</f>
+      <c r="O62" s="92">
+        <f>$L$17+IF($D62=TRUE,(1+COUNTIF(DADOS!$X$5:$X$7,"&lt;="&amp;$AH$11)),0)+Q62</f>
         <v/>
       </c>
       <c r="P62" s="11" t="n"/>
-      <c r="Q62" s="47" t="n"/>
-      <c r="R62" s="88" t="b">
+      <c r="Q62" s="93" t="n"/>
+      <c r="R62" s="47" t="n"/>
+      <c r="S62" s="89" t="b">
         <v>0</v>
       </c>
-      <c r="S62" s="89" t="inlineStr">
+      <c r="T62" s="90" t="inlineStr">
         <is>
           <t>Tecnologia</t>
         </is>
       </c>
-      <c r="T62" s="10" t="n"/>
       <c r="U62" s="10" t="n"/>
       <c r="V62" s="10" t="n"/>
       <c r="W62" s="10" t="n"/>
       <c r="X62" s="10" t="n"/>
       <c r="Y62" s="10" t="n"/>
-      <c r="Z62" s="11" t="n"/>
-      <c r="AA62" s="90" t="inlineStr">
+      <c r="Z62" s="10" t="n"/>
+      <c r="AA62" s="11" t="n"/>
+      <c r="AB62" s="91" t="inlineStr">
         <is>
           <t>Int</t>
         </is>
       </c>
-      <c r="AB62" s="11" t="n"/>
-      <c r="AC62" s="91">
-        <f>$AB$17+IF($R$62=TRUE,(1+COUNTIF(DADOS!$X$5:$X$7,"&lt;="&amp;$AH$11)),0)</f>
+      <c r="AC62" s="11" t="n"/>
+      <c r="AD62" s="92">
+        <f>$AB$17+IF($S62=TRUE,(1+COUNTIF(DADOS!$X$5:$X$7,"&lt;="&amp;$AH$11)),0)+AF62</f>
         <v/>
       </c>
-      <c r="AD62" s="11" t="n"/>
-      <c r="AE62" s="47" t="n"/>
-      <c r="AF62" s="47" t="n"/>
+      <c r="AE62" s="11" t="n"/>
+      <c r="AF62" s="93" t="n"/>
       <c r="AG62" s="47" t="n"/>
       <c r="AH62" s="47" t="n"/>
       <c r="AI62" s="17" t="n"/>
@@ -6830,10 +6860,10 @@
       <c r="A63" s="7" t="n"/>
       <c r="B63" s="7" t="n"/>
       <c r="C63" s="40" t="n"/>
-      <c r="D63" s="88" t="b">
+      <c r="D63" s="89" t="b">
         <v>0</v>
       </c>
-      <c r="E63" s="89" t="inlineStr">
+      <c r="E63" s="90" t="inlineStr">
         <is>
           <t>Prestidigitação</t>
         </is>
@@ -6845,46 +6875,46 @@
       <c r="J63" s="10" t="n"/>
       <c r="K63" s="10" t="n"/>
       <c r="L63" s="11" t="n"/>
-      <c r="M63" s="90" t="inlineStr">
+      <c r="M63" s="91" t="inlineStr">
         <is>
           <t>Des</t>
         </is>
       </c>
       <c r="N63" s="11" t="n"/>
-      <c r="O63" s="91">
-        <f>$L$17+IF($D$63=TRUE,(1+COUNTIF(DADOS!$X$5:$X$7,"&lt;="&amp;$AH$11)),0)</f>
+      <c r="O63" s="92">
+        <f>$L$17+IF($D63=TRUE,(1+COUNTIF(DADOS!$X$5:$X$7,"&lt;="&amp;$AH$11)),0)+Q63</f>
         <v/>
       </c>
       <c r="P63" s="11" t="n"/>
-      <c r="Q63" s="47" t="n"/>
-      <c r="R63" s="88" t="b">
+      <c r="Q63" s="93" t="n"/>
+      <c r="R63" s="47" t="n"/>
+      <c r="S63" s="89" t="b">
         <v>0</v>
       </c>
-      <c r="S63" s="89" t="inlineStr">
+      <c r="T63" s="90" t="inlineStr">
         <is>
           <t>Sentir Energia</t>
         </is>
       </c>
-      <c r="T63" s="10" t="n"/>
       <c r="U63" s="10" t="n"/>
       <c r="V63" s="10" t="n"/>
       <c r="W63" s="10" t="n"/>
       <c r="X63" s="10" t="n"/>
       <c r="Y63" s="10" t="n"/>
-      <c r="Z63" s="11" t="n"/>
-      <c r="AA63" s="90" t="inlineStr">
+      <c r="Z63" s="10" t="n"/>
+      <c r="AA63" s="11" t="n"/>
+      <c r="AB63" s="91" t="inlineStr">
         <is>
           <t>Ess</t>
         </is>
       </c>
-      <c r="AB63" s="11" t="n"/>
-      <c r="AC63" s="91">
-        <f>$AJ$17+IF($R$63=TRUE,(1+COUNTIF(DADOS!$X$5:$X$7,"&lt;="&amp;$AH$11)),0)</f>
+      <c r="AC63" s="11" t="n"/>
+      <c r="AD63" s="92">
+        <f>$AB$17+IF($S63=TRUE,(1+COUNTIF(DADOS!$X$5:$X$7,"&lt;="&amp;$AH$11)),0)+AF63</f>
         <v/>
       </c>
-      <c r="AD63" s="11" t="n"/>
-      <c r="AE63" s="47" t="n"/>
-      <c r="AF63" s="47" t="n"/>
+      <c r="AE63" s="11" t="n"/>
+      <c r="AF63" s="93" t="n"/>
       <c r="AG63" s="47" t="n"/>
       <c r="AH63" s="47" t="n"/>
       <c r="AI63" s="86" t="n"/>
@@ -6905,10 +6935,10 @@
       <c r="A64" s="7" t="n"/>
       <c r="B64" s="7" t="n"/>
       <c r="C64" s="40" t="n"/>
-      <c r="D64" s="88" t="b">
+      <c r="D64" s="89" t="b">
         <v>0</v>
       </c>
-      <c r="E64" s="89" t="inlineStr">
+      <c r="E64" s="90" t="inlineStr">
         <is>
           <t>Investigação</t>
         </is>
@@ -6920,46 +6950,46 @@
       <c r="J64" s="10" t="n"/>
       <c r="K64" s="10" t="n"/>
       <c r="L64" s="11" t="n"/>
-      <c r="M64" s="90" t="inlineStr">
+      <c r="M64" s="91" t="inlineStr">
         <is>
           <t>Int</t>
         </is>
       </c>
       <c r="N64" s="11" t="n"/>
-      <c r="O64" s="91">
-        <f>$AB$17+IF($D$64=TRUE,(1+COUNTIF(DADOS!$X$5:$X$7,"&lt;="&amp;$AH$11)),0)</f>
+      <c r="O64" s="92">
+        <f>$L$17+IF($D64=TRUE,(1+COUNTIF(DADOS!$X$5:$X$7,"&lt;="&amp;$AH$11)),0)+Q64</f>
         <v/>
       </c>
       <c r="P64" s="11" t="n"/>
-      <c r="Q64" s="47" t="n"/>
-      <c r="R64" s="88" t="b">
+      <c r="Q64" s="93" t="n"/>
+      <c r="R64" s="47" t="n"/>
+      <c r="S64" s="89" t="b">
         <v>0</v>
       </c>
-      <c r="S64" s="89" t="inlineStr">
+      <c r="T64" s="90" t="inlineStr">
         <is>
           <t>Percepção</t>
         </is>
       </c>
-      <c r="T64" s="10" t="n"/>
       <c r="U64" s="10" t="n"/>
       <c r="V64" s="10" t="n"/>
       <c r="W64" s="10" t="n"/>
       <c r="X64" s="10" t="n"/>
       <c r="Y64" s="10" t="n"/>
-      <c r="Z64" s="11" t="n"/>
-      <c r="AA64" s="90" t="inlineStr">
+      <c r="Z64" s="10" t="n"/>
+      <c r="AA64" s="11" t="n"/>
+      <c r="AB64" s="91" t="inlineStr">
         <is>
           <t>Ess</t>
         </is>
       </c>
-      <c r="AB64" s="11" t="n"/>
-      <c r="AC64" s="91">
-        <f>$AJ$17+IF($R$64=TRUE,(1+COUNTIF(DADOS!$X$5:$X$7,"&lt;="&amp;$AH$11)),0)</f>
+      <c r="AC64" s="11" t="n"/>
+      <c r="AD64" s="92">
+        <f>$AB$17+IF($S64=TRUE,(1+COUNTIF(DADOS!$X$5:$X$7,"&lt;="&amp;$AH$11)),0)+AF64</f>
         <v/>
       </c>
-      <c r="AD64" s="11" t="n"/>
-      <c r="AE64" s="47" t="n"/>
-      <c r="AF64" s="47" t="n"/>
+      <c r="AE64" s="11" t="n"/>
+      <c r="AF64" s="93" t="n"/>
       <c r="AG64" s="47" t="n"/>
       <c r="AH64" s="47" t="n"/>
       <c r="AI64" s="17" t="n"/>
@@ -6980,10 +7010,10 @@
       <c r="A65" s="7" t="n"/>
       <c r="B65" s="7" t="n"/>
       <c r="C65" s="40" t="n"/>
-      <c r="D65" s="88" t="b">
+      <c r="D65" s="89" t="b">
         <v>0</v>
       </c>
-      <c r="E65" s="89" t="inlineStr">
+      <c r="E65" s="90" t="inlineStr">
         <is>
           <t>Intuição</t>
         </is>
@@ -6995,46 +7025,46 @@
       <c r="J65" s="10" t="n"/>
       <c r="K65" s="10" t="n"/>
       <c r="L65" s="11" t="n"/>
-      <c r="M65" s="90" t="inlineStr">
+      <c r="M65" s="91" t="inlineStr">
         <is>
           <t>Int</t>
         </is>
       </c>
       <c r="N65" s="11" t="n"/>
-      <c r="O65" s="91">
-        <f>$AB$17+IF($D$65=TRUE,(1+COUNTIF(DADOS!$X$5:$X$7,"&lt;="&amp;$AH$11)),0)</f>
+      <c r="O65" s="92">
+        <f>$L$17+IF($D65=TRUE,(1+COUNTIF(DADOS!$X$5:$X$7,"&lt;="&amp;$AH$11)),0)+Q65</f>
         <v/>
       </c>
       <c r="P65" s="11" t="n"/>
-      <c r="Q65" s="47" t="n"/>
-      <c r="R65" s="88" t="b">
+      <c r="Q65" s="93" t="n"/>
+      <c r="R65" s="47" t="n"/>
+      <c r="S65" s="89" t="b">
         <v>0</v>
       </c>
-      <c r="S65" s="89" t="inlineStr">
+      <c r="T65" s="90" t="inlineStr">
         <is>
           <t>Persuasão</t>
         </is>
       </c>
-      <c r="T65" s="10" t="n"/>
       <c r="U65" s="10" t="n"/>
       <c r="V65" s="10" t="n"/>
       <c r="W65" s="10" t="n"/>
       <c r="X65" s="10" t="n"/>
       <c r="Y65" s="10" t="n"/>
-      <c r="Z65" s="11" t="n"/>
-      <c r="AA65" s="90" t="inlineStr">
+      <c r="Z65" s="10" t="n"/>
+      <c r="AA65" s="11" t="n"/>
+      <c r="AB65" s="91" t="inlineStr">
         <is>
           <t>Ess</t>
         </is>
       </c>
-      <c r="AB65" s="11" t="n"/>
-      <c r="AC65" s="91">
-        <f>$AJ$17+IF($R$65=TRUE,(1+COUNTIF(DADOS!$X$5:$X$7,"&lt;="&amp;$AH$11)),0)</f>
+      <c r="AC65" s="11" t="n"/>
+      <c r="AD65" s="92">
+        <f>$AB$17+IF($S65=TRUE,(1+COUNTIF(DADOS!$X$5:$X$7,"&lt;="&amp;$AH$11)),0)+AF65</f>
         <v/>
       </c>
-      <c r="AD65" s="11" t="n"/>
-      <c r="AE65" s="47" t="n"/>
-      <c r="AF65" s="47" t="n"/>
+      <c r="AE65" s="11" t="n"/>
+      <c r="AF65" s="93" t="n"/>
       <c r="AG65" s="47" t="n"/>
       <c r="AH65" s="47" t="n"/>
       <c r="AI65" s="86" t="n"/>
@@ -7055,10 +7085,10 @@
       <c r="A66" s="7" t="n"/>
       <c r="B66" s="7" t="n"/>
       <c r="C66" s="40" t="n"/>
-      <c r="D66" s="88" t="b">
+      <c r="D66" s="89" t="b">
         <v>0</v>
       </c>
-      <c r="E66" s="89" t="inlineStr">
+      <c r="E66" s="90" t="inlineStr">
         <is>
           <t>Ocultismo</t>
         </is>
@@ -7070,46 +7100,46 @@
       <c r="J66" s="10" t="n"/>
       <c r="K66" s="10" t="n"/>
       <c r="L66" s="11" t="n"/>
-      <c r="M66" s="90" t="inlineStr">
+      <c r="M66" s="91" t="inlineStr">
         <is>
           <t>Int</t>
         </is>
       </c>
       <c r="N66" s="11" t="n"/>
-      <c r="O66" s="91">
-        <f>$AB$17+IF($D$66=TRUE,(1+COUNTIF(DADOS!$X$5:$X$7,"&lt;="&amp;$AH$11)),0)</f>
+      <c r="O66" s="92">
+        <f>$L$17+IF($D66=TRUE,(1+COUNTIF(DADOS!$X$5:$X$7,"&lt;="&amp;$AH$11)),0)+Q66</f>
         <v/>
       </c>
       <c r="P66" s="11" t="n"/>
-      <c r="Q66" s="47" t="n"/>
-      <c r="R66" s="88" t="b">
+      <c r="Q66" s="93" t="n"/>
+      <c r="R66" s="47" t="n"/>
+      <c r="S66" s="89" t="b">
         <v>0</v>
       </c>
-      <c r="S66" s="89" t="inlineStr">
+      <c r="T66" s="90" t="inlineStr">
         <is>
           <t>Enganação</t>
         </is>
       </c>
-      <c r="T66" s="10" t="n"/>
       <c r="U66" s="10" t="n"/>
       <c r="V66" s="10" t="n"/>
       <c r="W66" s="10" t="n"/>
       <c r="X66" s="10" t="n"/>
       <c r="Y66" s="10" t="n"/>
-      <c r="Z66" s="11" t="n"/>
-      <c r="AA66" s="90" t="inlineStr">
+      <c r="Z66" s="10" t="n"/>
+      <c r="AA66" s="11" t="n"/>
+      <c r="AB66" s="91" t="inlineStr">
         <is>
           <t>Ess</t>
         </is>
       </c>
-      <c r="AB66" s="11" t="n"/>
-      <c r="AC66" s="91">
-        <f>$AJ$17+IF($R$66=TRUE,(1+COUNTIF(DADOS!$X$5:$X$7,"&lt;="&amp;$AH$11)),0)</f>
+      <c r="AC66" s="11" t="n"/>
+      <c r="AD66" s="92">
+        <f>$AB$17+IF($S66=TRUE,(1+COUNTIF(DADOS!$X$5:$X$7,"&lt;="&amp;$AH$11)),0)+AF66</f>
         <v/>
       </c>
-      <c r="AD66" s="11" t="n"/>
-      <c r="AE66" s="47" t="n"/>
-      <c r="AF66" s="47" t="n"/>
+      <c r="AE66" s="11" t="n"/>
+      <c r="AF66" s="93" t="n"/>
       <c r="AG66" s="47" t="n"/>
       <c r="AH66" s="47" t="n"/>
       <c r="AI66" s="17" t="n"/>
@@ -7130,10 +7160,10 @@
       <c r="A67" s="7" t="n"/>
       <c r="B67" s="7" t="n"/>
       <c r="C67" s="40" t="n"/>
-      <c r="D67" s="88" t="b">
+      <c r="D67" s="89" t="b">
         <v>0</v>
       </c>
-      <c r="E67" s="89" t="inlineStr">
+      <c r="E67" s="90" t="inlineStr">
         <is>
           <t>Religião</t>
         </is>
@@ -7145,46 +7175,46 @@
       <c r="J67" s="10" t="n"/>
       <c r="K67" s="10" t="n"/>
       <c r="L67" s="11" t="n"/>
-      <c r="M67" s="90" t="inlineStr">
+      <c r="M67" s="91" t="inlineStr">
         <is>
           <t>Int</t>
         </is>
       </c>
       <c r="N67" s="11" t="n"/>
-      <c r="O67" s="91">
-        <f>$AB$17+IF($D$67=TRUE,(1+COUNTIF(DADOS!$X$5:$X$7,"&lt;="&amp;$AH$11)),0)</f>
+      <c r="O67" s="92">
+        <f>$L$17+IF($D67=TRUE,(1+COUNTIF(DADOS!$X$5:$X$7,"&lt;="&amp;$AH$11)),0)+Q67</f>
         <v/>
       </c>
       <c r="P67" s="11" t="n"/>
-      <c r="Q67" s="47" t="n"/>
-      <c r="R67" s="88" t="b">
+      <c r="Q67" s="93" t="n"/>
+      <c r="R67" s="47" t="n"/>
+      <c r="S67" s="89" t="b">
         <v>0</v>
       </c>
-      <c r="S67" s="89" t="inlineStr">
+      <c r="T67" s="90" t="inlineStr">
         <is>
           <t>Intimidação</t>
         </is>
       </c>
-      <c r="T67" s="10" t="n"/>
       <c r="U67" s="10" t="n"/>
       <c r="V67" s="10" t="n"/>
       <c r="W67" s="10" t="n"/>
       <c r="X67" s="10" t="n"/>
       <c r="Y67" s="10" t="n"/>
-      <c r="Z67" s="11" t="n"/>
-      <c r="AA67" s="90" t="inlineStr">
+      <c r="Z67" s="10" t="n"/>
+      <c r="AA67" s="11" t="n"/>
+      <c r="AB67" s="91" t="inlineStr">
         <is>
           <t>Ess</t>
         </is>
       </c>
-      <c r="AB67" s="11" t="n"/>
-      <c r="AC67" s="91">
-        <f>$AJ$17+IF($R$67=TRUE,(1+COUNTIF(DADOS!$X$5:$X$7,"&lt;="&amp;$AH$11)),0)</f>
+      <c r="AC67" s="11" t="n"/>
+      <c r="AD67" s="92">
+        <f>$AB$17+IF($S67=TRUE,(1+COUNTIF(DADOS!$X$5:$X$7,"&lt;="&amp;$AH$11)),0)+AF67</f>
         <v/>
       </c>
-      <c r="AD67" s="11" t="n"/>
-      <c r="AE67" s="47" t="n"/>
-      <c r="AF67" s="47" t="n"/>
+      <c r="AE67" s="11" t="n"/>
+      <c r="AF67" s="93" t="n"/>
       <c r="AG67" s="47" t="n"/>
       <c r="AH67" s="47" t="n"/>
       <c r="AI67" s="86" t="n"/>
@@ -7205,10 +7235,10 @@
       <c r="A68" s="7" t="n"/>
       <c r="B68" s="7" t="n"/>
       <c r="C68" s="40" t="n"/>
-      <c r="D68" s="88" t="b">
+      <c r="D68" s="89" t="b">
         <v>0</v>
       </c>
-      <c r="E68" s="89" t="inlineStr">
+      <c r="E68" s="90" t="inlineStr">
         <is>
           <t>História</t>
         </is>
@@ -7220,46 +7250,46 @@
       <c r="J68" s="10" t="n"/>
       <c r="K68" s="10" t="n"/>
       <c r="L68" s="11" t="n"/>
-      <c r="M68" s="90" t="inlineStr">
+      <c r="M68" s="91" t="inlineStr">
         <is>
           <t>Int</t>
         </is>
       </c>
       <c r="N68" s="11" t="n"/>
-      <c r="O68" s="91">
-        <f>$AB$17+IF($D$68=TRUE,(1+COUNTIF(DADOS!$X$5:$X$7,"&lt;="&amp;$AH$11)),0)</f>
+      <c r="O68" s="92">
+        <f>$L$17+IF($D68=TRUE,(1+COUNTIF(DADOS!$X$5:$X$7,"&lt;="&amp;$AH$11)),0)+Q68</f>
         <v/>
       </c>
       <c r="P68" s="11" t="n"/>
-      <c r="Q68" s="47" t="n"/>
-      <c r="R68" s="88" t="b">
+      <c r="Q68" s="93" t="n"/>
+      <c r="R68" s="47" t="n"/>
+      <c r="S68" s="89" t="b">
         <v>0</v>
       </c>
-      <c r="S68" s="89" t="inlineStr">
+      <c r="T68" s="90" t="inlineStr">
         <is>
           <t>Atuação</t>
         </is>
       </c>
-      <c r="T68" s="10" t="n"/>
       <c r="U68" s="10" t="n"/>
       <c r="V68" s="10" t="n"/>
       <c r="W68" s="10" t="n"/>
       <c r="X68" s="10" t="n"/>
       <c r="Y68" s="10" t="n"/>
-      <c r="Z68" s="11" t="n"/>
-      <c r="AA68" s="90" t="inlineStr">
+      <c r="Z68" s="10" t="n"/>
+      <c r="AA68" s="11" t="n"/>
+      <c r="AB68" s="91" t="inlineStr">
         <is>
           <t>Ess</t>
         </is>
       </c>
-      <c r="AB68" s="11" t="n"/>
-      <c r="AC68" s="91">
-        <f>$AJ$17+IF($R$68=TRUE,(1+COUNTIF(DADOS!$X$5:$X$7,"&lt;="&amp;$AH$11)),0)</f>
+      <c r="AC68" s="11" t="n"/>
+      <c r="AD68" s="92">
+        <f>$AB$17+IF($S68=TRUE,(1+COUNTIF(DADOS!$X$5:$X$7,"&lt;="&amp;$AH$11)),0)+AF68</f>
         <v/>
       </c>
-      <c r="AD68" s="11" t="n"/>
-      <c r="AE68" s="47" t="n"/>
-      <c r="AF68" s="47" t="n"/>
+      <c r="AE68" s="11" t="n"/>
+      <c r="AF68" s="93" t="n"/>
       <c r="AG68" s="47" t="n"/>
       <c r="AH68" s="47" t="n"/>
       <c r="AI68" s="17" t="n"/>
@@ -7280,10 +7310,10 @@
       <c r="A69" s="7" t="n"/>
       <c r="B69" s="7" t="n"/>
       <c r="C69" s="40" t="n"/>
-      <c r="D69" s="88" t="b">
+      <c r="D69" s="89" t="b">
         <v>0</v>
       </c>
-      <c r="E69" s="89" t="inlineStr">
+      <c r="E69" s="90" t="inlineStr">
         <is>
           <t>Hierarquia</t>
         </is>
@@ -7295,46 +7325,46 @@
       <c r="J69" s="10" t="n"/>
       <c r="K69" s="10" t="n"/>
       <c r="L69" s="11" t="n"/>
-      <c r="M69" s="90" t="inlineStr">
+      <c r="M69" s="91" t="inlineStr">
         <is>
           <t>Int</t>
         </is>
       </c>
       <c r="N69" s="11" t="n"/>
-      <c r="O69" s="91">
-        <f>$AB$17+IF($D$69=TRUE,(1+COUNTIF(DADOS!$X$5:$X$7,"&lt;="&amp;$AH$11)),0)</f>
+      <c r="O69" s="92">
+        <f>$L$17+IF($D69=TRUE,(1+COUNTIF(DADOS!$X$5:$X$7,"&lt;="&amp;$AH$11)),0)+Q69</f>
         <v/>
       </c>
       <c r="P69" s="11" t="n"/>
-      <c r="Q69" s="47" t="n"/>
-      <c r="R69" s="88" t="b">
+      <c r="Q69" s="93" t="n"/>
+      <c r="R69" s="47" t="n"/>
+      <c r="S69" s="89" t="b">
         <v>0</v>
       </c>
-      <c r="S69" s="89" t="inlineStr">
+      <c r="T69" s="90" t="inlineStr">
         <is>
           <t>Provocar</t>
         </is>
       </c>
-      <c r="T69" s="10" t="n"/>
       <c r="U69" s="10" t="n"/>
       <c r="V69" s="10" t="n"/>
       <c r="W69" s="10" t="n"/>
       <c r="X69" s="10" t="n"/>
       <c r="Y69" s="10" t="n"/>
-      <c r="Z69" s="11" t="n"/>
-      <c r="AA69" s="90" t="inlineStr">
+      <c r="Z69" s="10" t="n"/>
+      <c r="AA69" s="11" t="n"/>
+      <c r="AB69" s="91" t="inlineStr">
         <is>
           <t>Ess</t>
         </is>
       </c>
-      <c r="AB69" s="11" t="n"/>
-      <c r="AC69" s="91">
-        <f>$AJ$17+IF($R$69=TRUE,(1+COUNTIF(DADOS!$X$5:$X$7,"&lt;="&amp;$AH$11)),0)</f>
+      <c r="AC69" s="11" t="n"/>
+      <c r="AD69" s="92">
+        <f>$AB$17+IF($S69=TRUE,(1+COUNTIF(DADOS!$X$5:$X$7,"&lt;="&amp;$AH$11)),0)+AF69</f>
         <v/>
       </c>
-      <c r="AD69" s="11" t="n"/>
-      <c r="AE69" s="47" t="n"/>
-      <c r="AF69" s="47" t="n"/>
+      <c r="AE69" s="11" t="n"/>
+      <c r="AF69" s="93" t="n"/>
       <c r="AG69" s="47" t="n"/>
       <c r="AH69" s="47" t="n"/>
       <c r="AI69" s="47" t="n"/>
@@ -7355,10 +7385,10 @@
       <c r="A70" s="7" t="n"/>
       <c r="B70" s="7" t="n"/>
       <c r="C70" s="40" t="n"/>
-      <c r="D70" s="88" t="b">
+      <c r="D70" s="89" t="b">
         <v>0</v>
       </c>
-      <c r="E70" s="89" t="inlineStr">
+      <c r="E70" s="90" t="inlineStr">
         <is>
           <t>Medicina</t>
         </is>
@@ -7370,18 +7400,18 @@
       <c r="J70" s="10" t="n"/>
       <c r="K70" s="10" t="n"/>
       <c r="L70" s="11" t="n"/>
-      <c r="M70" s="90" t="inlineStr">
+      <c r="M70" s="91" t="inlineStr">
         <is>
           <t>Int</t>
         </is>
       </c>
       <c r="N70" s="11" t="n"/>
-      <c r="O70" s="91">
-        <f>$AB$17+IF($D$70=TRUE,(1+COUNTIF(DADOS!$X$5:$X$7,"&lt;="&amp;$AH$11)),0)</f>
+      <c r="O70" s="92">
+        <f>$L$17+IF($D70=TRUE,(1+COUNTIF(DADOS!$X$5:$X$7,"&lt;="&amp;$AH$11)),0)+Q70</f>
         <v/>
       </c>
       <c r="P70" s="11" t="n"/>
-      <c r="Q70" s="47" t="n"/>
+      <c r="Q70" s="93" t="n"/>
       <c r="R70" s="47" t="n"/>
       <c r="S70" s="47" t="n"/>
       <c r="T70" s="47" t="n"/>
@@ -7531,7 +7561,11 @@
       <c r="K73" s="47" t="n"/>
       <c r="L73" s="47" t="n"/>
       <c r="M73" s="47" t="n"/>
-      <c r="N73" s="47" t="n"/>
+      <c r="N73" s="88" t="inlineStr">
+        <is>
+          <t>Extra</t>
+        </is>
+      </c>
       <c r="O73" s="47" t="n"/>
       <c r="P73" s="47" t="n"/>
       <c r="Q73" s="47" t="n"/>
@@ -7543,7 +7577,11 @@
       <c r="W73" s="47" t="n"/>
       <c r="X73" s="47" t="n"/>
       <c r="Y73" s="47" t="n"/>
-      <c r="Z73" s="47" t="n"/>
+      <c r="Z73" s="88" t="inlineStr">
+        <is>
+          <t>Extra</t>
+        </is>
+      </c>
       <c r="AA73" s="47" t="n"/>
       <c r="AB73" s="47" t="n"/>
       <c r="AC73" s="47" t="n"/>
@@ -7553,7 +7591,11 @@
       <c r="AG73" s="47" t="n"/>
       <c r="AH73" s="47" t="n"/>
       <c r="AI73" s="47" t="n"/>
-      <c r="AJ73" s="47" t="n"/>
+      <c r="AJ73" s="88" t="inlineStr">
+        <is>
+          <t>Extra</t>
+        </is>
+      </c>
       <c r="AK73" s="47" t="n"/>
       <c r="AL73" s="47" t="n"/>
       <c r="AM73" s="47" t="n"/>
@@ -7570,10 +7612,10 @@
       <c r="A74" s="7" t="n"/>
       <c r="B74" s="7" t="n"/>
       <c r="C74" s="40" t="n"/>
-      <c r="D74" s="88" t="b">
+      <c r="D74" s="89" t="b">
         <v>0</v>
       </c>
-      <c r="E74" s="89" t="inlineStr">
+      <c r="E74" s="90" t="inlineStr">
         <is>
           <t>Condução</t>
         </is>
@@ -7582,48 +7624,48 @@
       <c r="G74" s="10" t="n"/>
       <c r="H74" s="10" t="n"/>
       <c r="I74" s="11" t="n"/>
-      <c r="J74" s="90" t="inlineStr">
+      <c r="J74" s="91" t="inlineStr">
         <is>
           <t>INTELIGÊNCIA</t>
         </is>
       </c>
       <c r="K74" s="10" t="n"/>
       <c r="L74" s="11" t="n"/>
-      <c r="M74" s="92">
-        <f>+IFS(J74="FORÇA",$D$17, J74="DESTREZA",$L$17, J74="CONSTITUIÇÃO",$T$17, J74="INTELIGÊNCIA",$AB$17, J74="ESSÊNCIA",$AJ$17)+IF($D74=TRUE,D$48,0)</f>
+      <c r="M74" s="93">
+        <f>+IFS(J74="FORÇA",$D$17, J74="DESTREZA",$L$17, J74="CONSTITUIÇÃO",$T$17, J74="INTELIGÊNCIA",$AB$17, J74="ESSÊNCIA",$AJ$17)+IF($D74=TRUE,D$48,0)+N74</f>
         <v/>
       </c>
-      <c r="N74" s="47" t="n"/>
-      <c r="O74" s="88" t="b">
+      <c r="N74" s="93" t="n"/>
+      <c r="O74" s="47" t="n"/>
+      <c r="P74" s="89" t="b">
         <v>0</v>
       </c>
-      <c r="P74" s="89" t="inlineStr">
+      <c r="Q74" s="90" t="inlineStr">
         <is>
           <t>Entalhador</t>
         </is>
       </c>
-      <c r="Q74" s="10" t="n"/>
       <c r="R74" s="10" t="n"/>
       <c r="S74" s="10" t="n"/>
-      <c r="T74" s="11" t="n"/>
-      <c r="U74" s="90" t="inlineStr">
+      <c r="T74" s="10" t="n"/>
+      <c r="U74" s="11" t="n"/>
+      <c r="V74" s="91" t="inlineStr">
         <is>
           <t>INTELIGÊNCIA</t>
         </is>
       </c>
-      <c r="V74" s="10" t="n"/>
-      <c r="W74" s="11" t="n"/>
-      <c r="X74" s="92">
-        <f>+IFS(U74="FORÇA",$D$17, U74="DESTREZA",$L$17, U74="CONSTITUIÇÃO",$T$17, U74="INTELIGÊNCIA",$AB$17, U74="ESSÊNCIA",$AJ$17)+IF($O74=TRUE,$D$48,0)</f>
+      <c r="W74" s="10" t="n"/>
+      <c r="X74" s="11" t="n"/>
+      <c r="Y74" s="93">
+        <f>+IFS(V74="FORÇA",$D$17, V74="DESTREZA",$L$17, V74="CONSTITUIÇÃO",$T$17, V74="INTELIGÊNCIA",$AB$17, V74="ESSÊNCIA",$AJ$17)+IF($P74=TRUE,$D$48,0)+Z74</f>
         <v/>
       </c>
-      <c r="Y74" s="47" t="n"/>
-      <c r="Z74" s="47" t="n"/>
+      <c r="Z74" s="93" t="n"/>
       <c r="AA74" s="47" t="n"/>
-      <c r="AB74" s="88" t="b">
+      <c r="AB74" s="89" t="b">
         <v>0</v>
       </c>
-      <c r="AC74" s="89" t="inlineStr">
+      <c r="AC74" s="94" t="inlineStr">
         <is>
           <t>Físico</t>
         </is>
@@ -7634,8 +7676,8 @@
       <c r="AG74" s="10" t="n"/>
       <c r="AH74" s="10" t="n"/>
       <c r="AI74" s="10" t="n"/>
-      <c r="AJ74" s="11" t="n"/>
-      <c r="AK74" s="93" t="inlineStr">
+      <c r="AJ74" s="90" t="n"/>
+      <c r="AK74" s="95" t="inlineStr">
         <is>
           <t>FORÇA</t>
         </is>
@@ -7644,24 +7686,24 @@
       <c r="AM74" s="10" t="n"/>
       <c r="AN74" s="10" t="n"/>
       <c r="AO74" s="11" t="n"/>
-      <c r="AP74" s="91">
-        <f>+IFS(AK48="FORÇA",$D$17, AK48="DESTREZA",$L$17)+IF($AB$74=TRUE,2,0)</f>
+      <c r="AP74" s="92">
+        <f>+IFS(AK74="FORÇA",$D$17, AK74="DESTREZA",$L$17)+IF($AB$74=TRUE,2,0)+AJ74</f>
         <v/>
       </c>
       <c r="AQ74" s="10" t="n"/>
       <c r="AR74" s="10" t="n"/>
       <c r="AS74" s="10" t="n"/>
       <c r="AT74" s="11" t="n"/>
-      <c r="AU74" s="94" t="n"/>
+      <c r="AU74" s="96" t="n"/>
     </row>
     <row r="75">
       <c r="A75" s="7" t="n"/>
       <c r="B75" s="7" t="n"/>
       <c r="C75" s="40" t="n"/>
-      <c r="D75" s="88" t="b">
+      <c r="D75" s="89" t="b">
         <v>0</v>
       </c>
-      <c r="E75" s="89" t="inlineStr">
+      <c r="E75" s="90" t="inlineStr">
         <is>
           <t>Arrombamento</t>
         </is>
@@ -7670,48 +7712,48 @@
       <c r="G75" s="10" t="n"/>
       <c r="H75" s="10" t="n"/>
       <c r="I75" s="11" t="n"/>
-      <c r="J75" s="90" t="inlineStr">
+      <c r="J75" s="91" t="inlineStr">
         <is>
           <t>INTELIGÊNCIA</t>
         </is>
       </c>
       <c r="K75" s="10" t="n"/>
       <c r="L75" s="11" t="n"/>
-      <c r="M75" s="92">
-        <f>+IFS(J75="FORÇA",$D$17, J75="DESTREZA",$L$17, J75="CONSTITUIÇÃO",$T$17, J75="INTELIGÊNCIA",$AB$17, J75="ESSÊNCIA",$AJ$17)+IF($D75=TRUE,D$48,0)</f>
+      <c r="M75" s="93">
+        <f>+IFS(J75="FORÇA",$D$17, J75="DESTREZA",$L$17, J75="CONSTITUIÇÃO",$T$17, J75="INTELIGÊNCIA",$AB$17, J75="ESSÊNCIA",$AJ$17)+IF($D75=TRUE,D$48,0)+N75</f>
         <v/>
       </c>
-      <c r="N75" s="47" t="n"/>
-      <c r="O75" s="88" t="b">
+      <c r="N75" s="93" t="n"/>
+      <c r="O75" s="47" t="n"/>
+      <c r="P75" s="89" t="b">
         <v>0</v>
       </c>
-      <c r="P75" s="89" t="inlineStr">
+      <c r="Q75" s="90" t="inlineStr">
         <is>
           <t xml:space="preserve">Alfaiate </t>
         </is>
       </c>
-      <c r="Q75" s="10" t="n"/>
       <c r="R75" s="10" t="n"/>
       <c r="S75" s="10" t="n"/>
-      <c r="T75" s="11" t="n"/>
-      <c r="U75" s="90" t="inlineStr">
+      <c r="T75" s="10" t="n"/>
+      <c r="U75" s="11" t="n"/>
+      <c r="V75" s="91" t="inlineStr">
         <is>
           <t>INTELIGÊNCIA</t>
         </is>
       </c>
-      <c r="V75" s="10" t="n"/>
-      <c r="W75" s="11" t="n"/>
-      <c r="X75" s="92">
-        <f>+IFS(U75="FORÇA",$D$17, U75="DESTREZA",$L$17, U75="CONSTITUIÇÃO",$T$17, U75="INTELIGÊNCIA",$AB$17, U75="ESSÊNCIA",$AJ$17)+IF($O75=TRUE,$D$48,0)</f>
+      <c r="W75" s="10" t="n"/>
+      <c r="X75" s="11" t="n"/>
+      <c r="Y75" s="93">
+        <f>+IFS(V75="FORÇA",$D$17, V75="DESTREZA",$L$17, V75="CONSTITUIÇÃO",$T$17, V75="INTELIGÊNCIA",$AB$17, V75="ESSÊNCIA",$AJ$17)+IF($P75=TRUE,$D$48,0)+Z75</f>
         <v/>
       </c>
-      <c r="Y75" s="47" t="n"/>
-      <c r="Z75" s="47" t="n"/>
+      <c r="Z75" s="93" t="n"/>
       <c r="AA75" s="47" t="n"/>
-      <c r="AB75" s="88" t="b">
+      <c r="AB75" s="89" t="b">
         <v>0</v>
       </c>
-      <c r="AC75" s="89" t="inlineStr">
+      <c r="AC75" s="94" t="inlineStr">
         <is>
           <t>Vigor</t>
         </is>
@@ -7722,8 +7764,8 @@
       <c r="AG75" s="10" t="n"/>
       <c r="AH75" s="10" t="n"/>
       <c r="AI75" s="10" t="n"/>
-      <c r="AJ75" s="11" t="n"/>
-      <c r="AK75" s="90" t="inlineStr">
+      <c r="AJ75" s="90" t="n"/>
+      <c r="AK75" s="91" t="inlineStr">
         <is>
           <t xml:space="preserve">CONSTITUIÇÃO </t>
         </is>
@@ -7732,24 +7774,24 @@
       <c r="AM75" s="10" t="n"/>
       <c r="AN75" s="10" t="n"/>
       <c r="AO75" s="11" t="n"/>
-      <c r="AP75" s="91">
-        <f>$T$17+IF($AB$75=TRUE,2,0)</f>
+      <c r="AP75" s="92">
+        <f>$T$17+IF($AB$75=TRUE,2,0)+AJ75</f>
         <v/>
       </c>
       <c r="AQ75" s="10" t="n"/>
       <c r="AR75" s="10" t="n"/>
       <c r="AS75" s="10" t="n"/>
       <c r="AT75" s="11" t="n"/>
-      <c r="AU75" s="94" t="n"/>
+      <c r="AU75" s="96" t="n"/>
     </row>
     <row r="76">
       <c r="A76" s="7" t="n"/>
       <c r="B76" s="7" t="n"/>
       <c r="C76" s="40" t="n"/>
-      <c r="D76" s="88" t="b">
+      <c r="D76" s="89" t="b">
         <v>0</v>
       </c>
-      <c r="E76" s="89" t="inlineStr">
+      <c r="E76" s="90" t="inlineStr">
         <is>
           <t>Herbalismo</t>
         </is>
@@ -7758,48 +7800,48 @@
       <c r="G76" s="10" t="n"/>
       <c r="H76" s="10" t="n"/>
       <c r="I76" s="11" t="n"/>
-      <c r="J76" s="90" t="inlineStr">
+      <c r="J76" s="91" t="inlineStr">
         <is>
           <t>INTELIGÊNCIA</t>
         </is>
       </c>
       <c r="K76" s="10" t="n"/>
       <c r="L76" s="11" t="n"/>
-      <c r="M76" s="92">
-        <f>+IFS(J76="FORÇA",$D$17, J76="DESTREZA",$L$17, J76="CONSTITUIÇÃO",$T$17, J76="INTELIGÊNCIA",$AB$17, J76="ESSÊNCIA",$AJ$17)+IF($D76=TRUE,D$48,0)</f>
+      <c r="M76" s="93">
+        <f>+IFS(J76="FORÇA",$D$17, J76="DESTREZA",$L$17, J76="CONSTITUIÇÃO",$T$17, J76="INTELIGÊNCIA",$AB$17, J76="ESSÊNCIA",$AJ$17)+IF($D76=TRUE,D$48,0)+N76</f>
         <v/>
       </c>
-      <c r="N76" s="47" t="n"/>
-      <c r="O76" s="88" t="b">
+      <c r="N76" s="93" t="n"/>
+      <c r="O76" s="47" t="n"/>
+      <c r="P76" s="89" t="b">
         <v>0</v>
       </c>
-      <c r="P76" s="95" t="inlineStr">
+      <c r="Q76" s="97" t="inlineStr">
         <is>
           <t>Culinária</t>
         </is>
       </c>
-      <c r="Q76" s="10" t="n"/>
       <c r="R76" s="10" t="n"/>
       <c r="S76" s="10" t="n"/>
-      <c r="T76" s="11" t="n"/>
-      <c r="U76" s="90" t="inlineStr">
+      <c r="T76" s="10" t="n"/>
+      <c r="U76" s="11" t="n"/>
+      <c r="V76" s="91" t="inlineStr">
         <is>
           <t>INTELIGÊNCIA</t>
         </is>
       </c>
-      <c r="V76" s="10" t="n"/>
-      <c r="W76" s="11" t="n"/>
-      <c r="X76" s="92">
-        <f>+IFS(U76="FORÇA",$D$17, U76="DESTREZA",$L$17, U76="CONSTITUIÇÃO",$T$17, U76="INTELIGÊNCIA",$AB$17, U76="ESSÊNCIA",$AJ$17)+IF($O76=TRUE,$D$48,0)</f>
+      <c r="W76" s="10" t="n"/>
+      <c r="X76" s="11" t="n"/>
+      <c r="Y76" s="93">
+        <f>+IFS(V76="FORÇA",$D$17, V76="DESTREZA",$L$17, V76="CONSTITUIÇÃO",$T$17, V76="INTELIGÊNCIA",$AB$17, V76="ESSÊNCIA",$AJ$17)+IF($P76=TRUE,$D$48,0)+Z76</f>
         <v/>
       </c>
-      <c r="Y76" s="47" t="n"/>
-      <c r="Z76" s="47" t="n"/>
+      <c r="Z76" s="93" t="n"/>
       <c r="AA76" s="47" t="n"/>
-      <c r="AB76" s="88" t="b">
+      <c r="AB76" s="89" t="b">
         <v>0</v>
       </c>
-      <c r="AC76" s="89" t="inlineStr">
+      <c r="AC76" s="94" t="inlineStr">
         <is>
           <t>Intelecto</t>
         </is>
@@ -7810,8 +7852,8 @@
       <c r="AG76" s="10" t="n"/>
       <c r="AH76" s="10" t="n"/>
       <c r="AI76" s="10" t="n"/>
-      <c r="AJ76" s="11" t="n"/>
-      <c r="AK76" s="90" t="inlineStr">
+      <c r="AJ76" s="94" t="n"/>
+      <c r="AK76" s="91" t="inlineStr">
         <is>
           <t>INTELIGÊNCIA</t>
         </is>
@@ -7820,24 +7862,24 @@
       <c r="AM76" s="10" t="n"/>
       <c r="AN76" s="10" t="n"/>
       <c r="AO76" s="11" t="n"/>
-      <c r="AP76" s="91">
-        <f>$AB$17+IF($AB$76=TRUE,2,0)</f>
+      <c r="AP76" s="92">
+        <f>$AB$17+IF($AB$76=TRUE,2,0)+AJ76</f>
         <v/>
       </c>
       <c r="AQ76" s="10" t="n"/>
       <c r="AR76" s="10" t="n"/>
       <c r="AS76" s="10" t="n"/>
       <c r="AT76" s="11" t="n"/>
-      <c r="AU76" s="94" t="n"/>
+      <c r="AU76" s="96" t="n"/>
     </row>
     <row r="77">
       <c r="A77" s="7" t="n"/>
       <c r="B77" s="7" t="n"/>
       <c r="C77" s="40" t="n"/>
-      <c r="D77" s="88" t="b">
+      <c r="D77" s="89" t="b">
         <v>0</v>
       </c>
-      <c r="E77" s="89" t="inlineStr">
+      <c r="E77" s="90" t="inlineStr">
         <is>
           <t>Forja</t>
         </is>
@@ -7846,48 +7888,48 @@
       <c r="G77" s="10" t="n"/>
       <c r="H77" s="10" t="n"/>
       <c r="I77" s="11" t="n"/>
-      <c r="J77" s="90" t="inlineStr">
+      <c r="J77" s="91" t="inlineStr">
         <is>
           <t>INTELIGÊNCIA</t>
         </is>
       </c>
       <c r="K77" s="10" t="n"/>
       <c r="L77" s="11" t="n"/>
-      <c r="M77" s="92">
-        <f>+IFS(J77="FORÇA",$D$17, J77="DESTREZA",$L$17, J77="CONSTITUIÇÃO",$T$17, J77="INTELIGÊNCIA",$AB$17, J77="ESSÊNCIA",$AJ$17)+IF($D77=TRUE,D$48,0)</f>
+      <c r="M77" s="93">
+        <f>+IFS(J77="FORÇA",$D$17, J77="DESTREZA",$L$17, J77="CONSTITUIÇÃO",$T$17, J77="INTELIGÊNCIA",$AB$17, J77="ESSÊNCIA",$AJ$17)+IF($D77=TRUE,D$48,0)+N77</f>
         <v/>
       </c>
-      <c r="N77" s="47" t="n"/>
-      <c r="O77" s="88" t="b">
+      <c r="N77" s="93" t="n"/>
+      <c r="O77" s="47" t="n"/>
+      <c r="P77" s="89" t="b">
         <v>0</v>
       </c>
-      <c r="P77" s="89" t="inlineStr">
+      <c r="Q77" s="90" t="inlineStr">
         <is>
           <t>Jogatina</t>
         </is>
       </c>
-      <c r="Q77" s="10" t="n"/>
       <c r="R77" s="10" t="n"/>
       <c r="S77" s="10" t="n"/>
-      <c r="T77" s="11" t="n"/>
-      <c r="U77" s="90" t="inlineStr">
+      <c r="T77" s="10" t="n"/>
+      <c r="U77" s="11" t="n"/>
+      <c r="V77" s="91" t="inlineStr">
         <is>
           <t>INTELIGÊNCIA</t>
         </is>
       </c>
-      <c r="V77" s="10" t="n"/>
-      <c r="W77" s="11" t="n"/>
-      <c r="X77" s="92">
-        <f>+IFS(U77="FORÇA",$D$17, U77="DESTREZA",$L$17, U77="CONSTITUIÇÃO",$T$17, U77="INTELIGÊNCIA",$AB$17, U77="ESSÊNCIA",$AJ$17)+IF($O77=TRUE,$D$48,0)</f>
+      <c r="W77" s="10" t="n"/>
+      <c r="X77" s="11" t="n"/>
+      <c r="Y77" s="93">
+        <f>+IFS(V77="FORÇA",$D$17, V77="DESTREZA",$L$17, V77="CONSTITUIÇÃO",$T$17, V77="INTELIGÊNCIA",$AB$17, V77="ESSÊNCIA",$AJ$17)+IF($P77=TRUE,$D$48,0)+Z77</f>
         <v/>
       </c>
-      <c r="Y77" s="47" t="n"/>
-      <c r="Z77" s="47" t="n"/>
+      <c r="Z77" s="93" t="n"/>
       <c r="AA77" s="47" t="n"/>
-      <c r="AB77" s="88" t="b">
+      <c r="AB77" s="89" t="b">
         <v>0</v>
       </c>
-      <c r="AC77" s="89" t="inlineStr">
+      <c r="AC77" s="94" t="inlineStr">
         <is>
           <t>Espírito</t>
         </is>
@@ -7898,8 +7940,8 @@
       <c r="AG77" s="10" t="n"/>
       <c r="AH77" s="10" t="n"/>
       <c r="AI77" s="10" t="n"/>
-      <c r="AJ77" s="11" t="n"/>
-      <c r="AK77" s="90" t="inlineStr">
+      <c r="AJ77" s="90" t="n"/>
+      <c r="AK77" s="91" t="inlineStr">
         <is>
           <t>ESSÊNCIA</t>
         </is>
@@ -7908,24 +7950,24 @@
       <c r="AM77" s="10" t="n"/>
       <c r="AN77" s="10" t="n"/>
       <c r="AO77" s="11" t="n"/>
-      <c r="AP77" s="91">
-        <f>$AJ$17+IF($AB$77=TRUE,2,0)</f>
+      <c r="AP77" s="92">
+        <f>$AJ$17+IF($AB$77=TRUE,2,0)+AJ77</f>
         <v/>
       </c>
       <c r="AQ77" s="10" t="n"/>
       <c r="AR77" s="10" t="n"/>
       <c r="AS77" s="10" t="n"/>
       <c r="AT77" s="11" t="n"/>
-      <c r="AU77" s="94" t="n"/>
+      <c r="AU77" s="96" t="n"/>
     </row>
     <row r="78">
       <c r="A78" s="7" t="n"/>
       <c r="B78" s="7" t="n"/>
       <c r="C78" s="40" t="n"/>
-      <c r="D78" s="88" t="b">
+      <c r="D78" s="89" t="b">
         <v>0</v>
       </c>
-      <c r="E78" s="89" t="inlineStr">
+      <c r="E78" s="90" t="inlineStr">
         <is>
           <t>Caligrafia</t>
         </is>
@@ -7934,43 +7976,43 @@
       <c r="G78" s="10" t="n"/>
       <c r="H78" s="10" t="n"/>
       <c r="I78" s="11" t="n"/>
-      <c r="J78" s="90" t="inlineStr">
+      <c r="J78" s="91" t="inlineStr">
         <is>
           <t>INTELIGÊNCIA</t>
         </is>
       </c>
       <c r="K78" s="10" t="n"/>
       <c r="L78" s="11" t="n"/>
-      <c r="M78" s="92">
-        <f>+IFS(J78="FORÇA",$D$17, J78="DESTREZA",$L$17, J78="CONSTITUIÇÃO",$T$17, J78="INTELIGÊNCIA",$AB$17, J78="ESSÊNCIA",$AJ$17)+IF($D78=TRUE,D$48,0)</f>
+      <c r="M78" s="93">
+        <f>+IFS(J78="FORÇA",$D$17, J78="DESTREZA",$L$17, J78="CONSTITUIÇÃO",$T$17, J78="INTELIGÊNCIA",$AB$17, J78="ESSÊNCIA",$AJ$17)+IF($D78=TRUE,D$48,0)+N78</f>
         <v/>
       </c>
-      <c r="N78" s="47" t="n"/>
-      <c r="O78" s="88" t="b">
+      <c r="N78" s="93" t="n"/>
+      <c r="O78" s="47" t="n"/>
+      <c r="P78" s="89" t="b">
         <v>0</v>
       </c>
-      <c r="P78" s="89" t="inlineStr">
+      <c r="Q78" s="90" t="inlineStr">
         <is>
           <t>Instrumento</t>
         </is>
       </c>
-      <c r="Q78" s="10" t="n"/>
       <c r="R78" s="10" t="n"/>
       <c r="S78" s="10" t="n"/>
-      <c r="T78" s="11" t="n"/>
-      <c r="U78" s="90" t="inlineStr">
+      <c r="T78" s="10" t="n"/>
+      <c r="U78" s="11" t="n"/>
+      <c r="V78" s="91" t="inlineStr">
         <is>
           <t>INTELIGÊNCIA</t>
         </is>
       </c>
-      <c r="V78" s="10" t="n"/>
-      <c r="W78" s="11" t="n"/>
-      <c r="X78" s="92">
-        <f>+IFS(U78="FORÇA",$D$17, U78="DESTREZA",$L$17, U78="CONSTITUIÇÃO",$T$17, U78="INTELIGÊNCIA",$AB$17, U78="ESSÊNCIA",$AJ$17)+IF($O78=TRUE,$D$48,0)</f>
+      <c r="W78" s="10" t="n"/>
+      <c r="X78" s="11" t="n"/>
+      <c r="Y78" s="93">
+        <f>+IFS(V78="FORÇA",$D$17, V78="DESTREZA",$L$17, V78="CONSTITUIÇÃO",$T$17, V78="INTELIGÊNCIA",$AB$17, V78="ESSÊNCIA",$AJ$17)+IF($P78=TRUE,$D$48,0)+Z78</f>
         <v/>
       </c>
-      <c r="Y78" s="47" t="n"/>
-      <c r="Z78" s="47" t="n"/>
+      <c r="Z78" s="93" t="n"/>
       <c r="AA78" s="47" t="n"/>
       <c r="AB78" s="47" t="n"/>
       <c r="AC78" s="47" t="n"/>
@@ -7997,10 +8039,10 @@
       <c r="A79" s="7" t="n"/>
       <c r="B79" s="7" t="n"/>
       <c r="C79" s="40" t="n"/>
-      <c r="D79" s="88" t="b">
+      <c r="D79" s="89" t="b">
         <v>0</v>
       </c>
-      <c r="E79" s="89" t="inlineStr">
+      <c r="E79" s="90" t="inlineStr">
         <is>
           <t>Burocracia</t>
         </is>
@@ -8009,18 +8051,18 @@
       <c r="G79" s="10" t="n"/>
       <c r="H79" s="10" t="n"/>
       <c r="I79" s="11" t="n"/>
-      <c r="J79" s="90" t="inlineStr">
+      <c r="J79" s="91" t="inlineStr">
         <is>
           <t>INTELIGÊNCIA</t>
         </is>
       </c>
       <c r="K79" s="10" t="n"/>
       <c r="L79" s="11" t="n"/>
-      <c r="M79" s="92">
-        <f>+IFS(J79="FORÇA",$D$17, J79="DESTREZA",$L$17, J79="CONSTITUIÇÃO",$T$17, J79="INTELIGÊNCIA",$AB$17, J79="ESSÊNCIA",$AJ$17)+IF($D79=TRUE,D$48,0)</f>
+      <c r="M79" s="93">
+        <f>+IFS(J79="FORÇA",$D$17, J79="DESTREZA",$L$17, J79="CONSTITUIÇÃO",$T$17, J79="INTELIGÊNCIA",$AB$17, J79="ESSÊNCIA",$AJ$17)+IF($D79=TRUE,D$48,0)+N79</f>
         <v/>
       </c>
-      <c r="N79" s="47" t="n"/>
+      <c r="N79" s="93" t="n"/>
       <c r="O79" s="47" t="n"/>
       <c r="P79" s="47" t="n"/>
       <c r="Q79" s="47" t="n"/>
@@ -8252,7 +8294,7 @@
       <c r="A84" s="7" t="n"/>
       <c r="B84" s="7" t="n"/>
       <c r="C84" s="40" t="n"/>
-      <c r="D84" s="96" t="inlineStr">
+      <c r="D84" s="98" t="inlineStr">
         <is>
           <t>Skill Base de Caminho 1</t>
         </is>
@@ -8268,7 +8310,7 @@
       <c r="M84" s="10" t="n"/>
       <c r="N84" s="11" t="n"/>
       <c r="O84" s="40" t="n"/>
-      <c r="P84" s="96" t="inlineStr">
+      <c r="P84" s="98" t="inlineStr">
         <is>
           <t>Skill Base de Trilha 1</t>
         </is>
@@ -8284,7 +8326,7 @@
       <c r="Y84" s="10" t="n"/>
       <c r="Z84" s="11" t="n"/>
       <c r="AA84" s="40" t="n"/>
-      <c r="AB84" s="96" t="inlineStr">
+      <c r="AB84" s="98" t="inlineStr">
         <is>
           <t>Outras Anotações</t>
         </is>
@@ -8553,7 +8595,7 @@
       <c r="A91" s="7" t="n"/>
       <c r="B91" s="7" t="n"/>
       <c r="C91" s="40" t="n"/>
-      <c r="D91" s="96" t="inlineStr">
+      <c r="D91" s="98" t="inlineStr">
         <is>
           <t>Skill Base de Caminho 2</t>
         </is>
@@ -8569,7 +8611,7 @@
       <c r="M91" s="10" t="n"/>
       <c r="N91" s="11" t="n"/>
       <c r="O91" s="40" t="n"/>
-      <c r="P91" s="96" t="inlineStr">
+      <c r="P91" s="98" t="inlineStr">
         <is>
           <t>Skill Base de Trilha 2</t>
         </is>
@@ -8585,7 +8627,7 @@
       <c r="Y91" s="10" t="n"/>
       <c r="Z91" s="11" t="n"/>
       <c r="AA91" s="40" t="n"/>
-      <c r="AB91" s="96" t="inlineStr">
+      <c r="AB91" s="98" t="inlineStr">
         <is>
           <t>Outras Anotações</t>
         </is>
@@ -8854,7 +8896,7 @@
       <c r="A98" s="7" t="n"/>
       <c r="B98" s="7" t="n"/>
       <c r="C98" s="40" t="n"/>
-      <c r="D98" s="96" t="inlineStr">
+      <c r="D98" s="98" t="inlineStr">
         <is>
           <t>Skill Base de Caminho 3</t>
         </is>
@@ -8870,7 +8912,7 @@
       <c r="M98" s="10" t="n"/>
       <c r="N98" s="11" t="n"/>
       <c r="O98" s="40" t="n"/>
-      <c r="P98" s="96" t="inlineStr">
+      <c r="P98" s="98" t="inlineStr">
         <is>
           <t>Skill Base de Trilha 3</t>
         </is>
@@ -8886,7 +8928,7 @@
       <c r="Y98" s="10" t="n"/>
       <c r="Z98" s="11" t="n"/>
       <c r="AA98" s="40" t="n"/>
-      <c r="AB98" s="96" t="inlineStr">
+      <c r="AB98" s="98" t="inlineStr">
         <is>
           <t>Outras Anotações</t>
         </is>
@@ -9155,7 +9197,7 @@
       <c r="A105" s="7" t="n"/>
       <c r="B105" s="7" t="n"/>
       <c r="C105" s="40" t="n"/>
-      <c r="D105" s="96" t="inlineStr">
+      <c r="D105" s="98" t="inlineStr">
         <is>
           <t>Skill Base de Caminho 3</t>
         </is>
@@ -9171,7 +9213,7 @@
       <c r="M105" s="10" t="n"/>
       <c r="N105" s="11" t="n"/>
       <c r="O105" s="40" t="n"/>
-      <c r="P105" s="96" t="inlineStr">
+      <c r="P105" s="98" t="inlineStr">
         <is>
           <t>Skill Base de Trilha 3</t>
         </is>
@@ -9187,7 +9229,7 @@
       <c r="Y105" s="10" t="n"/>
       <c r="Z105" s="11" t="n"/>
       <c r="AA105" s="40" t="n"/>
-      <c r="AB105" s="96" t="inlineStr">
+      <c r="AB105" s="98" t="inlineStr">
         <is>
           <t>Outras Anotações</t>
         </is>
@@ -9609,13 +9651,13 @@
       <c r="A115" s="7" t="n"/>
       <c r="B115" s="7" t="n"/>
       <c r="C115" s="40" t="n"/>
-      <c r="D115" s="96" t="inlineStr">
+      <c r="D115" s="98" t="inlineStr">
         <is>
           <t>Classe</t>
         </is>
       </c>
       <c r="E115" s="11" t="n"/>
-      <c r="F115" s="96" t="inlineStr">
+      <c r="F115" s="98" t="inlineStr">
         <is>
           <t>Feitiços</t>
         </is>
@@ -9634,8 +9676,8 @@
       <c r="R115" s="10" t="n"/>
       <c r="S115" s="10" t="n"/>
       <c r="T115" s="11" t="n"/>
-      <c r="U115" s="97" t="n"/>
-      <c r="V115" s="96" t="inlineStr">
+      <c r="U115" s="99" t="n"/>
+      <c r="V115" s="98" t="inlineStr">
         <is>
           <t>Refino 0/10</t>
         </is>
@@ -9670,41 +9712,41 @@
       <c r="A116" s="7" t="n"/>
       <c r="B116" s="7" t="n"/>
       <c r="C116" s="40" t="n"/>
-      <c r="D116" s="97" t="n"/>
-      <c r="E116" s="97" t="n"/>
-      <c r="F116" s="97" t="n"/>
-      <c r="G116" s="97" t="n"/>
-      <c r="H116" s="97" t="n"/>
-      <c r="I116" s="97" t="n"/>
-      <c r="J116" s="97" t="n"/>
-      <c r="K116" s="97" t="n"/>
-      <c r="L116" s="97" t="n"/>
-      <c r="M116" s="97" t="n"/>
-      <c r="N116" s="97" t="n"/>
-      <c r="O116" s="97" t="n"/>
-      <c r="P116" s="97" t="n"/>
-      <c r="Q116" s="97" t="n"/>
-      <c r="R116" s="97" t="n"/>
-      <c r="S116" s="97" t="n"/>
-      <c r="T116" s="97" t="n"/>
-      <c r="U116" s="97" t="n"/>
-      <c r="V116" s="97" t="n"/>
-      <c r="W116" s="97" t="n"/>
-      <c r="X116" s="97" t="n"/>
-      <c r="Y116" s="97" t="n"/>
-      <c r="Z116" s="97" t="n"/>
-      <c r="AA116" s="97" t="n"/>
-      <c r="AB116" s="97" t="n"/>
-      <c r="AC116" s="97" t="n"/>
-      <c r="AD116" s="97" t="n"/>
-      <c r="AE116" s="97" t="n"/>
-      <c r="AF116" s="97" t="n"/>
-      <c r="AG116" s="97" t="n"/>
-      <c r="AH116" s="97" t="n"/>
-      <c r="AI116" s="97" t="n"/>
-      <c r="AJ116" s="97" t="n"/>
-      <c r="AK116" s="97" t="n"/>
-      <c r="AL116" s="97" t="n"/>
+      <c r="D116" s="99" t="n"/>
+      <c r="E116" s="99" t="n"/>
+      <c r="F116" s="99" t="n"/>
+      <c r="G116" s="99" t="n"/>
+      <c r="H116" s="99" t="n"/>
+      <c r="I116" s="99" t="n"/>
+      <c r="J116" s="99" t="n"/>
+      <c r="K116" s="99" t="n"/>
+      <c r="L116" s="99" t="n"/>
+      <c r="M116" s="99" t="n"/>
+      <c r="N116" s="99" t="n"/>
+      <c r="O116" s="99" t="n"/>
+      <c r="P116" s="99" t="n"/>
+      <c r="Q116" s="99" t="n"/>
+      <c r="R116" s="99" t="n"/>
+      <c r="S116" s="99" t="n"/>
+      <c r="T116" s="99" t="n"/>
+      <c r="U116" s="99" t="n"/>
+      <c r="V116" s="99" t="n"/>
+      <c r="W116" s="99" t="n"/>
+      <c r="X116" s="99" t="n"/>
+      <c r="Y116" s="99" t="n"/>
+      <c r="Z116" s="99" t="n"/>
+      <c r="AA116" s="99" t="n"/>
+      <c r="AB116" s="99" t="n"/>
+      <c r="AC116" s="99" t="n"/>
+      <c r="AD116" s="99" t="n"/>
+      <c r="AE116" s="99" t="n"/>
+      <c r="AF116" s="99" t="n"/>
+      <c r="AG116" s="99" t="n"/>
+      <c r="AH116" s="99" t="n"/>
+      <c r="AI116" s="99" t="n"/>
+      <c r="AJ116" s="99" t="n"/>
+      <c r="AK116" s="99" t="n"/>
+      <c r="AL116" s="99" t="n"/>
       <c r="AM116" s="40" t="n"/>
       <c r="AN116" s="40" t="n"/>
       <c r="AO116" s="40" t="n"/>
@@ -9719,7 +9761,7 @@
       <c r="A117" s="7" t="n"/>
       <c r="B117" s="7" t="n"/>
       <c r="C117" s="40" t="n"/>
-      <c r="D117" s="98" t="n"/>
+      <c r="D117" s="100" t="n"/>
       <c r="E117" s="11" t="n"/>
       <c r="F117" s="34" t="n"/>
       <c r="G117" s="10" t="n"/>
@@ -9736,7 +9778,7 @@
       <c r="R117" s="10" t="n"/>
       <c r="S117" s="10" t="n"/>
       <c r="T117" s="11" t="n"/>
-      <c r="U117" s="97" t="n"/>
+      <c r="U117" s="99" t="n"/>
       <c r="V117" s="34" t="n"/>
       <c r="W117" s="10" t="n"/>
       <c r="X117" s="10" t="n"/>
@@ -9768,7 +9810,7 @@
       <c r="A118" s="7" t="n"/>
       <c r="B118" s="7" t="n"/>
       <c r="C118" s="40" t="n"/>
-      <c r="D118" s="98" t="n"/>
+      <c r="D118" s="100" t="n"/>
       <c r="E118" s="11" t="n"/>
       <c r="F118" s="34" t="n"/>
       <c r="G118" s="10" t="n"/>
@@ -9785,7 +9827,7 @@
       <c r="R118" s="10" t="n"/>
       <c r="S118" s="10" t="n"/>
       <c r="T118" s="11" t="n"/>
-      <c r="U118" s="97" t="n"/>
+      <c r="U118" s="99" t="n"/>
       <c r="V118" s="34" t="n"/>
       <c r="W118" s="10" t="n"/>
       <c r="X118" s="10" t="n"/>
@@ -9817,7 +9859,7 @@
       <c r="A119" s="7" t="n"/>
       <c r="B119" s="7" t="n"/>
       <c r="C119" s="40" t="n"/>
-      <c r="D119" s="98" t="n"/>
+      <c r="D119" s="100" t="n"/>
       <c r="E119" s="11" t="n"/>
       <c r="F119" s="34" t="n"/>
       <c r="G119" s="10" t="n"/>
@@ -9834,7 +9876,7 @@
       <c r="R119" s="10" t="n"/>
       <c r="S119" s="10" t="n"/>
       <c r="T119" s="11" t="n"/>
-      <c r="U119" s="97" t="n"/>
+      <c r="U119" s="99" t="n"/>
       <c r="V119" s="34" t="n"/>
       <c r="W119" s="10" t="n"/>
       <c r="X119" s="10" t="n"/>
@@ -9866,7 +9908,7 @@
       <c r="A120" s="7" t="n"/>
       <c r="B120" s="7" t="n"/>
       <c r="C120" s="40" t="n"/>
-      <c r="D120" s="98" t="n"/>
+      <c r="D120" s="100" t="n"/>
       <c r="E120" s="11" t="n"/>
       <c r="F120" s="34" t="n"/>
       <c r="G120" s="10" t="n"/>
@@ -9883,7 +9925,7 @@
       <c r="R120" s="10" t="n"/>
       <c r="S120" s="10" t="n"/>
       <c r="T120" s="11" t="n"/>
-      <c r="U120" s="97" t="n"/>
+      <c r="U120" s="99" t="n"/>
       <c r="V120" s="34" t="n"/>
       <c r="W120" s="10" t="n"/>
       <c r="X120" s="10" t="n"/>
@@ -9915,7 +9957,7 @@
       <c r="A121" s="7" t="n"/>
       <c r="B121" s="7" t="n"/>
       <c r="C121" s="40" t="n"/>
-      <c r="D121" s="98" t="n"/>
+      <c r="D121" s="100" t="n"/>
       <c r="E121" s="11" t="n"/>
       <c r="F121" s="34" t="n"/>
       <c r="G121" s="10" t="n"/>
@@ -9932,7 +9974,7 @@
       <c r="R121" s="10" t="n"/>
       <c r="S121" s="10" t="n"/>
       <c r="T121" s="11" t="n"/>
-      <c r="U121" s="97" t="n"/>
+      <c r="U121" s="99" t="n"/>
       <c r="V121" s="34" t="n"/>
       <c r="W121" s="10" t="n"/>
       <c r="X121" s="10" t="n"/>
@@ -9964,7 +10006,7 @@
       <c r="A122" s="7" t="n"/>
       <c r="B122" s="7" t="n"/>
       <c r="C122" s="40" t="n"/>
-      <c r="D122" s="98" t="n"/>
+      <c r="D122" s="100" t="n"/>
       <c r="E122" s="11" t="n"/>
       <c r="F122" s="34" t="n"/>
       <c r="G122" s="10" t="n"/>
@@ -9981,7 +10023,7 @@
       <c r="R122" s="10" t="n"/>
       <c r="S122" s="10" t="n"/>
       <c r="T122" s="11" t="n"/>
-      <c r="U122" s="97" t="n"/>
+      <c r="U122" s="99" t="n"/>
       <c r="V122" s="34" t="n"/>
       <c r="W122" s="10" t="n"/>
       <c r="X122" s="10" t="n"/>
@@ -10013,7 +10055,7 @@
       <c r="A123" s="7" t="n"/>
       <c r="B123" s="7" t="n"/>
       <c r="C123" s="40" t="n"/>
-      <c r="D123" s="98" t="n"/>
+      <c r="D123" s="100" t="n"/>
       <c r="E123" s="11" t="n"/>
       <c r="F123" s="34" t="n"/>
       <c r="G123" s="10" t="n"/>
@@ -10030,7 +10072,7 @@
       <c r="R123" s="10" t="n"/>
       <c r="S123" s="10" t="n"/>
       <c r="T123" s="11" t="n"/>
-      <c r="U123" s="97" t="n"/>
+      <c r="U123" s="99" t="n"/>
       <c r="V123" s="34" t="n"/>
       <c r="W123" s="10" t="n"/>
       <c r="X123" s="10" t="n"/>
@@ -10062,7 +10104,7 @@
       <c r="A124" s="7" t="n"/>
       <c r="B124" s="7" t="n"/>
       <c r="C124" s="40" t="n"/>
-      <c r="D124" s="98" t="n"/>
+      <c r="D124" s="100" t="n"/>
       <c r="E124" s="11" t="n"/>
       <c r="F124" s="34" t="n"/>
       <c r="G124" s="10" t="n"/>
@@ -10079,7 +10121,7 @@
       <c r="R124" s="10" t="n"/>
       <c r="S124" s="10" t="n"/>
       <c r="T124" s="11" t="n"/>
-      <c r="U124" s="97" t="n"/>
+      <c r="U124" s="99" t="n"/>
       <c r="V124" s="34" t="n"/>
       <c r="W124" s="10" t="n"/>
       <c r="X124" s="10" t="n"/>
@@ -10111,7 +10153,7 @@
       <c r="A125" s="7" t="n"/>
       <c r="B125" s="7" t="n"/>
       <c r="C125" s="40" t="n"/>
-      <c r="D125" s="98" t="n"/>
+      <c r="D125" s="100" t="n"/>
       <c r="E125" s="11" t="n"/>
       <c r="F125" s="34" t="n"/>
       <c r="G125" s="10" t="n"/>
@@ -10128,7 +10170,7 @@
       <c r="R125" s="10" t="n"/>
       <c r="S125" s="10" t="n"/>
       <c r="T125" s="11" t="n"/>
-      <c r="U125" s="97" t="n"/>
+      <c r="U125" s="99" t="n"/>
       <c r="V125" s="34" t="n"/>
       <c r="W125" s="10" t="n"/>
       <c r="X125" s="10" t="n"/>
@@ -10160,7 +10202,7 @@
       <c r="A126" s="7" t="n"/>
       <c r="B126" s="7" t="n"/>
       <c r="C126" s="40" t="n"/>
-      <c r="D126" s="98" t="n"/>
+      <c r="D126" s="100" t="n"/>
       <c r="E126" s="11" t="n"/>
       <c r="F126" s="34" t="n"/>
       <c r="G126" s="10" t="n"/>
@@ -10177,7 +10219,7 @@
       <c r="R126" s="10" t="n"/>
       <c r="S126" s="10" t="n"/>
       <c r="T126" s="11" t="n"/>
-      <c r="U126" s="97" t="n"/>
+      <c r="U126" s="99" t="n"/>
       <c r="V126" s="34" t="n"/>
       <c r="W126" s="10" t="n"/>
       <c r="X126" s="10" t="n"/>
@@ -10209,7 +10251,7 @@
       <c r="A127" s="7" t="n"/>
       <c r="B127" s="7" t="n"/>
       <c r="C127" s="40" t="n"/>
-      <c r="D127" s="98" t="n"/>
+      <c r="D127" s="100" t="n"/>
       <c r="E127" s="11" t="n"/>
       <c r="F127" s="34" t="n"/>
       <c r="G127" s="10" t="n"/>
@@ -10226,7 +10268,7 @@
       <c r="R127" s="10" t="n"/>
       <c r="S127" s="10" t="n"/>
       <c r="T127" s="11" t="n"/>
-      <c r="U127" s="97" t="n"/>
+      <c r="U127" s="99" t="n"/>
       <c r="V127" s="34" t="n"/>
       <c r="W127" s="10" t="n"/>
       <c r="X127" s="10" t="n"/>
@@ -10258,7 +10300,7 @@
       <c r="A128" s="7" t="n"/>
       <c r="B128" s="7" t="n"/>
       <c r="C128" s="40" t="n"/>
-      <c r="D128" s="98" t="n"/>
+      <c r="D128" s="100" t="n"/>
       <c r="E128" s="11" t="n"/>
       <c r="F128" s="34" t="n"/>
       <c r="G128" s="10" t="n"/>
@@ -10275,7 +10317,7 @@
       <c r="R128" s="10" t="n"/>
       <c r="S128" s="10" t="n"/>
       <c r="T128" s="11" t="n"/>
-      <c r="U128" s="97" t="n"/>
+      <c r="U128" s="99" t="n"/>
       <c r="V128" s="34" t="n"/>
       <c r="W128" s="10" t="n"/>
       <c r="X128" s="10" t="n"/>
@@ -10307,7 +10349,7 @@
       <c r="A129" s="7" t="n"/>
       <c r="B129" s="7" t="n"/>
       <c r="C129" s="40" t="n"/>
-      <c r="D129" s="98" t="n"/>
+      <c r="D129" s="100" t="n"/>
       <c r="E129" s="11" t="n"/>
       <c r="F129" s="34" t="n"/>
       <c r="G129" s="10" t="n"/>
@@ -10356,7 +10398,7 @@
       <c r="A130" s="7" t="n"/>
       <c r="B130" s="7" t="n"/>
       <c r="C130" s="40" t="n"/>
-      <c r="D130" s="98" t="n"/>
+      <c r="D130" s="100" t="n"/>
       <c r="E130" s="11" t="n"/>
       <c r="F130" s="34" t="n"/>
       <c r="G130" s="10" t="n"/>
@@ -10405,7 +10447,7 @@
       <c r="A131" s="7" t="n"/>
       <c r="B131" s="7" t="n"/>
       <c r="C131" s="40" t="n"/>
-      <c r="D131" s="98" t="n"/>
+      <c r="D131" s="100" t="n"/>
       <c r="E131" s="11" t="n"/>
       <c r="F131" s="34" t="n"/>
       <c r="G131" s="10" t="n"/>
@@ -10454,7 +10496,7 @@
       <c r="A132" s="7" t="n"/>
       <c r="B132" s="7" t="n"/>
       <c r="C132" s="40" t="n"/>
-      <c r="D132" s="98" t="n"/>
+      <c r="D132" s="100" t="n"/>
       <c r="E132" s="11" t="n"/>
       <c r="F132" s="34" t="n"/>
       <c r="G132" s="10" t="n"/>
@@ -10503,7 +10545,7 @@
       <c r="A133" s="7" t="n"/>
       <c r="B133" s="7" t="n"/>
       <c r="C133" s="40" t="n"/>
-      <c r="D133" s="98" t="n"/>
+      <c r="D133" s="100" t="n"/>
       <c r="E133" s="11" t="n"/>
       <c r="F133" s="34" t="n"/>
       <c r="G133" s="10" t="n"/>
@@ -10651,29 +10693,31 @@
     <mergeCell ref="D107:N110"/>
     <mergeCell ref="O47:X47"/>
     <mergeCell ref="AK75:AO75"/>
+    <mergeCell ref="AD68:AE68"/>
     <mergeCell ref="M59:N59"/>
     <mergeCell ref="D2:X2"/>
     <mergeCell ref="J74:L74"/>
     <mergeCell ref="V122:AL122"/>
+    <mergeCell ref="AD67:AE67"/>
+    <mergeCell ref="V74:X74"/>
     <mergeCell ref="D39:M39"/>
     <mergeCell ref="AI65:AR66"/>
     <mergeCell ref="D84:N84"/>
     <mergeCell ref="D22:N22"/>
-    <mergeCell ref="AC62:AD62"/>
     <mergeCell ref="AH2:AT2"/>
+    <mergeCell ref="AB60:AC60"/>
+    <mergeCell ref="M70:N70"/>
     <mergeCell ref="D93:N96"/>
-    <mergeCell ref="P84:Z84"/>
-    <mergeCell ref="M70:N70"/>
     <mergeCell ref="V121:AL121"/>
     <mergeCell ref="M60:N60"/>
-    <mergeCell ref="AC77:AJ77"/>
-    <mergeCell ref="AC74:AJ74"/>
+    <mergeCell ref="AD60:AE60"/>
+    <mergeCell ref="P84:Z84"/>
+    <mergeCell ref="AD69:AE69"/>
     <mergeCell ref="P107:Z110"/>
     <mergeCell ref="J75:L75"/>
-    <mergeCell ref="AA60:AB60"/>
+    <mergeCell ref="AB59:AC59"/>
     <mergeCell ref="AF23:AK23"/>
     <mergeCell ref="O63:P63"/>
-    <mergeCell ref="S67:Z67"/>
     <mergeCell ref="AB107:AL110"/>
     <mergeCell ref="AH10:AL10"/>
     <mergeCell ref="AM31:AR31"/>
@@ -10681,18 +10725,15 @@
     <mergeCell ref="D19:J19"/>
     <mergeCell ref="E60:L60"/>
     <mergeCell ref="E69:L69"/>
+    <mergeCell ref="Q78:U78"/>
     <mergeCell ref="A8:B26"/>
-    <mergeCell ref="P77:T77"/>
     <mergeCell ref="F130:T130"/>
+    <mergeCell ref="AB61:AC61"/>
+    <mergeCell ref="D125:E125"/>
     <mergeCell ref="AP74:AT74"/>
-    <mergeCell ref="D125:E125"/>
     <mergeCell ref="F117:T117"/>
-    <mergeCell ref="S69:Z69"/>
-    <mergeCell ref="AA63:AB63"/>
-    <mergeCell ref="AC63:AD63"/>
     <mergeCell ref="E59:L59"/>
     <mergeCell ref="AI60:AR60"/>
-    <mergeCell ref="AA68:AB68"/>
     <mergeCell ref="D34:AT34"/>
     <mergeCell ref="O39:X39"/>
     <mergeCell ref="AF22:AK22"/>
@@ -10704,11 +10745,10 @@
     <mergeCell ref="AM26:AR26"/>
     <mergeCell ref="F119:T119"/>
     <mergeCell ref="V120:AL120"/>
-    <mergeCell ref="AC60:AD60"/>
     <mergeCell ref="E61:L61"/>
     <mergeCell ref="D10:L10"/>
+    <mergeCell ref="T60:AA60"/>
     <mergeCell ref="O60:P60"/>
-    <mergeCell ref="P78:T78"/>
     <mergeCell ref="AI67:AR68"/>
     <mergeCell ref="AM23:AR23"/>
     <mergeCell ref="M62:N62"/>
@@ -10717,163 +10757,162 @@
     <mergeCell ref="F118:T118"/>
     <mergeCell ref="D43:M43"/>
     <mergeCell ref="D112:F113"/>
+    <mergeCell ref="V78:X78"/>
     <mergeCell ref="F127:T127"/>
     <mergeCell ref="V124:AL124"/>
-    <mergeCell ref="U77:W77"/>
     <mergeCell ref="D8:F9"/>
     <mergeCell ref="D26:N26"/>
     <mergeCell ref="AN11:AT11"/>
+    <mergeCell ref="AB65:AC65"/>
     <mergeCell ref="D115:E115"/>
     <mergeCell ref="D11:L11"/>
     <mergeCell ref="Z48:AI48"/>
     <mergeCell ref="O68:P68"/>
     <mergeCell ref="AK40:AT40"/>
-    <mergeCell ref="U75:W75"/>
     <mergeCell ref="V126:AL126"/>
+    <mergeCell ref="Q77:U77"/>
     <mergeCell ref="J79:L79"/>
+    <mergeCell ref="Z44:AI44"/>
+    <mergeCell ref="AE50:AO50"/>
+    <mergeCell ref="O48:X48"/>
+    <mergeCell ref="AB63:AC63"/>
+    <mergeCell ref="D131:E131"/>
     <mergeCell ref="D83:M83"/>
-    <mergeCell ref="Z44:AI44"/>
-    <mergeCell ref="O48:X48"/>
-    <mergeCell ref="AE50:AO50"/>
-    <mergeCell ref="D131:E131"/>
-    <mergeCell ref="S62:Z62"/>
-    <mergeCell ref="AA61:AB61"/>
+    <mergeCell ref="AD63:AE63"/>
     <mergeCell ref="D51:F52"/>
     <mergeCell ref="M64:N64"/>
+    <mergeCell ref="AD59:AE59"/>
     <mergeCell ref="F129:T129"/>
     <mergeCell ref="D124:E124"/>
     <mergeCell ref="D54:M54"/>
+    <mergeCell ref="T65:AA65"/>
+    <mergeCell ref="O65:P65"/>
     <mergeCell ref="AB91:AL91"/>
-    <mergeCell ref="O65:P65"/>
     <mergeCell ref="F121:T121"/>
+    <mergeCell ref="AI63:AR64"/>
+    <mergeCell ref="E63:L63"/>
+    <mergeCell ref="T62:AA62"/>
     <mergeCell ref="J31:N32"/>
-    <mergeCell ref="AI63:AR64"/>
-    <mergeCell ref="AC76:AJ76"/>
-    <mergeCell ref="E63:L63"/>
+    <mergeCell ref="T59:AA59"/>
     <mergeCell ref="AF26:AK26"/>
     <mergeCell ref="F131:T131"/>
-    <mergeCell ref="P93:Z96"/>
+    <mergeCell ref="D126:E126"/>
     <mergeCell ref="AB84:AL84"/>
     <mergeCell ref="E78:I78"/>
-    <mergeCell ref="S66:Z66"/>
+    <mergeCell ref="P93:Z96"/>
     <mergeCell ref="E65:L65"/>
-    <mergeCell ref="D126:E126"/>
-    <mergeCell ref="AC64:AD64"/>
     <mergeCell ref="M65:N65"/>
+    <mergeCell ref="AC75:AI75"/>
+    <mergeCell ref="T64:AA64"/>
     <mergeCell ref="D40:M40"/>
     <mergeCell ref="E77:I77"/>
     <mergeCell ref="J23:N24"/>
-    <mergeCell ref="S68:Z68"/>
+    <mergeCell ref="AC74:AI74"/>
     <mergeCell ref="O62:P62"/>
+    <mergeCell ref="AB67:AC67"/>
+    <mergeCell ref="P27:AD28"/>
     <mergeCell ref="D100:N103"/>
-    <mergeCell ref="P27:AD28"/>
     <mergeCell ref="AF27:AK27"/>
+    <mergeCell ref="AD61:AE61"/>
     <mergeCell ref="AB16:AH16"/>
-    <mergeCell ref="P75:T75"/>
     <mergeCell ref="D118:E118"/>
     <mergeCell ref="V128:AL128"/>
-    <mergeCell ref="AC65:AD65"/>
     <mergeCell ref="D72:F73"/>
+    <mergeCell ref="AB69:AC69"/>
     <mergeCell ref="AP77:AT77"/>
     <mergeCell ref="Z47:AI47"/>
-    <mergeCell ref="U74:W74"/>
+    <mergeCell ref="AB100:AL103"/>
     <mergeCell ref="M66:N66"/>
     <mergeCell ref="D129:E129"/>
+    <mergeCell ref="L17:R18"/>
+    <mergeCell ref="M63:N63"/>
+    <mergeCell ref="O43:X43"/>
+    <mergeCell ref="J78:L78"/>
+    <mergeCell ref="AB62:AC62"/>
     <mergeCell ref="D86:N89"/>
-    <mergeCell ref="AB100:AL103"/>
-    <mergeCell ref="L17:R18"/>
-    <mergeCell ref="J78:L78"/>
     <mergeCell ref="D98:N98"/>
-    <mergeCell ref="O43:X43"/>
-    <mergeCell ref="M63:N63"/>
+    <mergeCell ref="AD62:AE62"/>
+    <mergeCell ref="D5:Z5"/>
+    <mergeCell ref="T67:AA67"/>
+    <mergeCell ref="D37:F38"/>
     <mergeCell ref="AP75:AT75"/>
-    <mergeCell ref="D5:Z5"/>
-    <mergeCell ref="D37:F38"/>
-    <mergeCell ref="U76:W76"/>
     <mergeCell ref="M68:N68"/>
     <mergeCell ref="F133:T133"/>
     <mergeCell ref="AK44:AT44"/>
     <mergeCell ref="AE51:AO51"/>
+    <mergeCell ref="AB64:AC64"/>
     <mergeCell ref="D128:E128"/>
+    <mergeCell ref="AD64:AE64"/>
     <mergeCell ref="AJ17:AP18"/>
     <mergeCell ref="G37:X37"/>
-    <mergeCell ref="AC66:AD66"/>
+    <mergeCell ref="E62:L62"/>
     <mergeCell ref="M67:N67"/>
-    <mergeCell ref="E62:L62"/>
     <mergeCell ref="G57:AD57"/>
     <mergeCell ref="F126:T126"/>
     <mergeCell ref="AF30:AK30"/>
     <mergeCell ref="T19:Z19"/>
-    <mergeCell ref="S61:Z61"/>
     <mergeCell ref="F122:T122"/>
     <mergeCell ref="D81:F82"/>
+    <mergeCell ref="E64:L64"/>
     <mergeCell ref="D105:N105"/>
-    <mergeCell ref="AC68:AD68"/>
     <mergeCell ref="M69:N69"/>
-    <mergeCell ref="E64:L64"/>
     <mergeCell ref="F125:T125"/>
+    <mergeCell ref="N10:V10"/>
     <mergeCell ref="AK74:AO74"/>
-    <mergeCell ref="N10:V10"/>
+    <mergeCell ref="D120:E120"/>
     <mergeCell ref="P105:Z105"/>
-    <mergeCell ref="D120:E120"/>
     <mergeCell ref="D44:M44"/>
     <mergeCell ref="AK48:AT48"/>
-    <mergeCell ref="AC67:AD67"/>
+    <mergeCell ref="AD65:AE65"/>
+    <mergeCell ref="AF31:AK31"/>
     <mergeCell ref="G72:AH72"/>
-    <mergeCell ref="AF31:AK31"/>
     <mergeCell ref="O53:X53"/>
     <mergeCell ref="E74:I74"/>
     <mergeCell ref="G81:AH81"/>
     <mergeCell ref="G51:X51"/>
     <mergeCell ref="D91:N91"/>
     <mergeCell ref="V127:AL127"/>
-    <mergeCell ref="AC69:AD69"/>
-    <mergeCell ref="AA65:AB65"/>
     <mergeCell ref="D23:H24"/>
+    <mergeCell ref="O59:P59"/>
     <mergeCell ref="J76:L76"/>
-    <mergeCell ref="O59:P59"/>
     <mergeCell ref="P91:Z91"/>
     <mergeCell ref="F120:T120"/>
     <mergeCell ref="P31:AD32"/>
-    <mergeCell ref="AA59:AB59"/>
     <mergeCell ref="D57:F58"/>
     <mergeCell ref="AK43:AT43"/>
-    <mergeCell ref="U78:W78"/>
+    <mergeCell ref="AC77:AI77"/>
     <mergeCell ref="Z53:AI53"/>
+    <mergeCell ref="T61:AA61"/>
     <mergeCell ref="O61:P61"/>
-    <mergeCell ref="S65:Z65"/>
+    <mergeCell ref="AB66:AC66"/>
+    <mergeCell ref="AD66:AE66"/>
     <mergeCell ref="O70:P70"/>
     <mergeCell ref="D27:H28"/>
     <mergeCell ref="D117:E117"/>
     <mergeCell ref="O54:X54"/>
-    <mergeCell ref="AC61:AD61"/>
+    <mergeCell ref="D30:N30"/>
+    <mergeCell ref="D48:M48"/>
     <mergeCell ref="AK77:AO77"/>
-    <mergeCell ref="D48:M48"/>
-    <mergeCell ref="D30:N30"/>
-    <mergeCell ref="AA62:AB62"/>
     <mergeCell ref="D133:E133"/>
     <mergeCell ref="P100:Z103"/>
+    <mergeCell ref="AB68:AC68"/>
+    <mergeCell ref="D16:J16"/>
     <mergeCell ref="AP76:AT76"/>
-    <mergeCell ref="D16:J16"/>
     <mergeCell ref="F124:T124"/>
     <mergeCell ref="V125:AL125"/>
     <mergeCell ref="E66:L66"/>
     <mergeCell ref="Z39:AI39"/>
     <mergeCell ref="A30:B48"/>
-    <mergeCell ref="P74:T74"/>
     <mergeCell ref="J27:N28"/>
-    <mergeCell ref="S60:Z60"/>
+    <mergeCell ref="V77:X77"/>
     <mergeCell ref="O40:X40"/>
     <mergeCell ref="D14:F15"/>
     <mergeCell ref="E68:L68"/>
-    <mergeCell ref="P76:T76"/>
+    <mergeCell ref="D119:E119"/>
     <mergeCell ref="P86:Z89"/>
-    <mergeCell ref="D119:E119"/>
     <mergeCell ref="T16:Z16"/>
-    <mergeCell ref="S59:Z59"/>
-    <mergeCell ref="AC75:AJ75"/>
+    <mergeCell ref="E67:L67"/>
     <mergeCell ref="AB86:AL89"/>
-    <mergeCell ref="E67:L67"/>
     <mergeCell ref="D3:Z4"/>
     <mergeCell ref="D17:J18"/>
     <mergeCell ref="AJ16:AP16"/>
@@ -10881,8 +10920,11 @@
     <mergeCell ref="AB19:AH19"/>
     <mergeCell ref="AN10:AT10"/>
     <mergeCell ref="Z40:AI40"/>
+    <mergeCell ref="T63:AA63"/>
     <mergeCell ref="AM30:AR30"/>
     <mergeCell ref="F115:T115"/>
+    <mergeCell ref="T68:AA68"/>
+    <mergeCell ref="V75:X75"/>
     <mergeCell ref="G14:X14"/>
     <mergeCell ref="AH3:AT3"/>
     <mergeCell ref="V115:AL115"/>
@@ -10894,49 +10936,49 @@
     <mergeCell ref="X10:AF10"/>
     <mergeCell ref="Z54:AI54"/>
     <mergeCell ref="L19:R19"/>
-    <mergeCell ref="AA69:AB69"/>
     <mergeCell ref="D31:H32"/>
     <mergeCell ref="AB105:AL105"/>
     <mergeCell ref="V123:AL123"/>
     <mergeCell ref="D122:E122"/>
+    <mergeCell ref="AM27:AR27"/>
+    <mergeCell ref="V119:AL119"/>
+    <mergeCell ref="AK47:AT47"/>
+    <mergeCell ref="AH11:AL11"/>
     <mergeCell ref="AK76:AO76"/>
-    <mergeCell ref="V119:AL119"/>
-    <mergeCell ref="AA66:AB66"/>
-    <mergeCell ref="AH11:AL11"/>
-    <mergeCell ref="AM27:AR27"/>
     <mergeCell ref="AK39:AT39"/>
-    <mergeCell ref="AK47:AT47"/>
+    <mergeCell ref="AI61:AR62"/>
     <mergeCell ref="AB98:AL98"/>
-    <mergeCell ref="AI61:AR62"/>
     <mergeCell ref="M61:N61"/>
     <mergeCell ref="E70:L70"/>
+    <mergeCell ref="Q74:U74"/>
     <mergeCell ref="Z43:AI43"/>
+    <mergeCell ref="T69:AA69"/>
+    <mergeCell ref="AC76:AI76"/>
+    <mergeCell ref="D121:E121"/>
+    <mergeCell ref="P23:AD24"/>
+    <mergeCell ref="T66:AA66"/>
     <mergeCell ref="O64:P64"/>
-    <mergeCell ref="D121:E121"/>
     <mergeCell ref="N11:V11"/>
+    <mergeCell ref="D130:E130"/>
+    <mergeCell ref="V76:X76"/>
+    <mergeCell ref="E76:I76"/>
     <mergeCell ref="AJ19:AP19"/>
-    <mergeCell ref="P23:AD24"/>
-    <mergeCell ref="D130:E130"/>
-    <mergeCell ref="E76:I76"/>
-    <mergeCell ref="S64:Z64"/>
     <mergeCell ref="X11:AF11"/>
     <mergeCell ref="O44:X44"/>
-    <mergeCell ref="AA64:AB64"/>
     <mergeCell ref="G112:AH112"/>
     <mergeCell ref="O67:P67"/>
     <mergeCell ref="V118:AL118"/>
-    <mergeCell ref="AC59:AD59"/>
+    <mergeCell ref="Q76:U76"/>
     <mergeCell ref="F128:T128"/>
     <mergeCell ref="D53:M53"/>
-    <mergeCell ref="AA67:AB67"/>
     <mergeCell ref="D123:E123"/>
+    <mergeCell ref="AM22:AR22"/>
     <mergeCell ref="E75:I75"/>
-    <mergeCell ref="S63:Z63"/>
+    <mergeCell ref="D47:M47"/>
     <mergeCell ref="D132:E132"/>
-    <mergeCell ref="AM22:AR22"/>
-    <mergeCell ref="D47:M47"/>
     <mergeCell ref="J77:L77"/>
     <mergeCell ref="G8:X8"/>
+    <mergeCell ref="Q75:U75"/>
   </mergeCells>
   <conditionalFormatting sqref="D23">
     <cfRule type="expression" priority="1" dxfId="0">
@@ -10963,7 +11005,7 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="5">
-    <dataValidation sqref="J74:J79 U74:U78 Z48 AE51 AK48 AU48" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="J74:J79 V74:V78 Z48 AE51 AK48 AU48" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"FORÇA,DESTREZA,CONSTITUIÇÃO,INTELIGÊNCIA,ESSÊNCIA"</formula1>
     </dataValidation>
     <dataValidation sqref="D11" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
@@ -11050,20 +11092,20 @@
   </cols>
   <sheetData>
     <row r="1" ht="17.25" customHeight="1">
-      <c r="A1" s="99" t="inlineStr">
+      <c r="A1" s="101" t="inlineStr">
         <is>
           <t>VERSÃO DO CATÁLOGO</t>
         </is>
       </c>
-      <c r="B1" s="100" t="n">
+      <c r="B1" s="102" t="n">
         <v>104</v>
       </c>
-      <c r="C1" s="101" t="inlineStr">
+      <c r="C1" s="103" t="inlineStr">
         <is>
           <t>versão corrente (puxada da central)</t>
         </is>
       </c>
-      <c r="D1" s="100" t="n">
+      <c r="D1" s="102" t="n">
         <v>104</v>
       </c>
       <c r="E1" s="40" t="n"/>
@@ -11118,7 +11160,7 @@
       <c r="BB1" s="40" t="n"/>
     </row>
     <row r="2">
-      <c r="A2" s="101" t="inlineStr">
+      <c r="A2" s="103" t="inlineStr">
         <is>
           <t>cole aqui o IMPORTRANGE da central em D1 quando ela existir; enquanto não existir, D1 fica igual a B1 e o aviso some</t>
         </is>
@@ -11178,68 +11220,68 @@
       <c r="BB2" s="40" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="102" t="inlineStr">
+      <c r="A3" s="104" t="inlineStr">
         <is>
           <t>Caminhos</t>
         </is>
       </c>
-      <c r="B3" s="102" t="inlineStr">
+      <c r="B3" s="104" t="inlineStr">
         <is>
           <t>Perícias</t>
         </is>
       </c>
-      <c r="C3" s="102" t="inlineStr">
+      <c r="C3" s="104" t="inlineStr">
         <is>
           <t>Ofícios</t>
         </is>
       </c>
-      <c r="D3" s="102" t="inlineStr">
+      <c r="D3" s="104" t="inlineStr">
         <is>
           <t>Famílias</t>
         </is>
       </c>
-      <c r="E3" s="102" t="inlineStr">
+      <c r="E3" s="104" t="inlineStr">
         <is>
           <t>Formas</t>
         </is>
       </c>
-      <c r="F3" s="102" t="inlineStr">
+      <c r="F3" s="104" t="inlineStr">
         <is>
           <t>Melhorias</t>
         </is>
       </c>
-      <c r="G3" s="102" t="inlineStr">
+      <c r="G3" s="104" t="inlineStr">
         <is>
           <t>Restrições</t>
         </is>
       </c>
-      <c r="H3" s="102" t="inlineStr">
+      <c r="H3" s="104" t="inlineStr">
         <is>
           <t>Condições</t>
         </is>
       </c>
-      <c r="I3" s="102" t="inlineStr">
+      <c r="I3" s="104" t="inlineStr">
         <is>
           <t>Origens</t>
         </is>
       </c>
-      <c r="J3" s="102" t="inlineStr">
+      <c r="J3" s="104" t="inlineStr">
         <is>
           <t>Testes</t>
         </is>
       </c>
-      <c r="K3" s="102" t="inlineStr">
+      <c r="K3" s="104" t="inlineStr">
         <is>
           <t>Atributos</t>
         </is>
       </c>
-      <c r="L3" s="102" t="inlineStr">
+      <c r="L3" s="104" t="inlineStr">
         <is>
           <t>Trilhas</t>
         </is>
       </c>
       <c r="M3" s="40" t="n"/>
-      <c r="N3" s="102" t="inlineStr">
+      <c r="N3" s="104" t="inlineStr">
         <is>
           <t>tabela dos Caminhos</t>
         </is>
@@ -11286,135 +11328,135 @@
       <c r="BB3" s="40" t="n"/>
     </row>
     <row r="4" ht="17.25" customHeight="1">
-      <c r="A4" s="103" t="inlineStr">
+      <c r="A4" s="105" t="inlineStr">
         <is>
           <t>Bastião</t>
         </is>
       </c>
-      <c r="B4" s="103" t="inlineStr">
+      <c r="B4" s="105" t="inlineStr">
         <is>
           <t>Atletismo</t>
         </is>
       </c>
-      <c r="C4" s="103" t="inlineStr">
+      <c r="C4" s="105" t="inlineStr">
         <is>
           <t>Condução</t>
         </is>
       </c>
-      <c r="D4" s="103" t="inlineStr">
+      <c r="D4" s="105" t="inlineStr">
         <is>
           <t>Alcance</t>
         </is>
       </c>
-      <c r="E4" s="103" t="inlineStr">
+      <c r="E4" s="105" t="inlineStr">
         <is>
           <t>Projétil</t>
         </is>
       </c>
-      <c r="F4" s="103" t="inlineStr">
+      <c r="F4" s="105" t="inlineStr">
         <is>
           <t>Longe</t>
         </is>
       </c>
-      <c r="G4" s="103" t="inlineStr">
+      <c r="G4" s="105" t="inlineStr">
         <is>
           <t>Corpo a Corpo</t>
         </is>
       </c>
-      <c r="H4" s="103" t="inlineStr">
+      <c r="H4" s="105" t="inlineStr">
         <is>
           <t>Lento</t>
         </is>
       </c>
-      <c r="I4" s="103" t="inlineStr">
+      <c r="I4" s="105" t="inlineStr">
         <is>
           <t>Latente</t>
         </is>
       </c>
-      <c r="J4" s="103" t="inlineStr">
+      <c r="J4" s="105" t="inlineStr">
         <is>
           <t>Físico</t>
         </is>
       </c>
-      <c r="K4" s="103" t="inlineStr">
+      <c r="K4" s="105" t="inlineStr">
         <is>
           <t>lista</t>
         </is>
       </c>
-      <c r="L4" s="103" t="inlineStr">
+      <c r="L4" s="105" t="inlineStr">
         <is>
           <t>Muro</t>
         </is>
       </c>
       <c r="M4" s="40" t="n"/>
-      <c r="N4" s="104" t="inlineStr">
+      <c r="N4" s="106" t="inlineStr">
         <is>
           <t>Caminho</t>
         </is>
       </c>
-      <c r="O4" s="104" t="inlineStr">
+      <c r="O4" s="106" t="inlineStr">
         <is>
           <t>dado</t>
         </is>
       </c>
-      <c r="P4" s="104" t="inlineStr">
+      <c r="P4" s="106" t="inlineStr">
         <is>
           <t>vida inicial</t>
         </is>
       </c>
-      <c r="Q4" s="104" t="inlineStr">
+      <c r="Q4" s="106" t="inlineStr">
         <is>
           <t>vida por nível</t>
         </is>
       </c>
-      <c r="R4" s="104" t="inlineStr">
+      <c r="R4" s="106" t="inlineStr">
         <is>
           <t>PE por nível</t>
         </is>
       </c>
-      <c r="S4" s="104" t="inlineStr">
+      <c r="S4" s="106" t="inlineStr">
         <is>
           <t>perícia fixa 1</t>
         </is>
       </c>
-      <c r="T4" s="104" t="inlineStr">
+      <c r="T4" s="106" t="inlineStr">
         <is>
           <t>perícia fixa 2</t>
         </is>
       </c>
-      <c r="U4" s="104" t="inlineStr">
+      <c r="U4" s="106" t="inlineStr">
         <is>
           <t>ofício fixo</t>
         </is>
       </c>
       <c r="V4" s="40" t="n"/>
-      <c r="W4" s="104" t="inlineStr">
+      <c r="W4" s="106" t="inlineStr">
         <is>
           <t>marcos</t>
         </is>
       </c>
-      <c r="X4" s="104" t="inlineStr">
+      <c r="X4" s="106" t="inlineStr">
         <is>
           <t>maestria</t>
         </is>
       </c>
-      <c r="Y4" s="104" t="inlineStr">
+      <c r="Y4" s="106" t="inlineStr">
         <is>
           <t>classe</t>
         </is>
       </c>
-      <c r="Z4" s="104" t="inlineStr">
+      <c r="Z4" s="106" t="inlineStr">
         <is>
           <t>classe 0</t>
         </is>
       </c>
       <c r="AA4" s="40" t="n"/>
-      <c r="AB4" s="104" t="inlineStr">
+      <c r="AB4" s="106" t="inlineStr">
         <is>
           <t>perícia</t>
         </is>
       </c>
-      <c r="AC4" s="104" t="inlineStr">
+      <c r="AC4" s="106" t="inlineStr">
         <is>
           <t>atributo</t>
         </is>
@@ -11442,133 +11484,133 @@
       <c r="AX4" s="40" t="n"/>
       <c r="AY4" s="40" t="n"/>
       <c r="AZ4" s="40" t="n"/>
-      <c r="BA4" s="104" t="inlineStr">
+      <c r="BA4" s="106" t="inlineStr">
         <is>
           <t>campo</t>
         </is>
       </c>
-      <c r="BB4" s="104" t="inlineStr">
+      <c r="BB4" s="106" t="inlineStr">
         <is>
           <t>célula</t>
         </is>
       </c>
     </row>
     <row r="5" ht="17.25" customHeight="1">
-      <c r="A5" s="103" t="inlineStr">
+      <c r="A5" s="105" t="inlineStr">
         <is>
           <t>Vanguarda</t>
         </is>
       </c>
-      <c r="B5" s="103" t="inlineStr">
+      <c r="B5" s="105" t="inlineStr">
         <is>
           <t>Acrobacia</t>
         </is>
       </c>
-      <c r="C5" s="103" t="inlineStr">
+      <c r="C5" s="105" t="inlineStr">
         <is>
           <t>Arrombamento</t>
         </is>
       </c>
-      <c r="D5" s="103" t="inlineStr">
+      <c r="D5" s="105" t="inlineStr">
         <is>
           <t>Área</t>
         </is>
       </c>
-      <c r="E5" s="103" t="inlineStr">
+      <c r="E5" s="105" t="inlineStr">
         <is>
           <t>Toque</t>
         </is>
       </c>
-      <c r="F5" s="103" t="inlineStr">
+      <c r="F5" s="105" t="inlineStr">
         <is>
           <t>Muito Longe</t>
         </is>
       </c>
-      <c r="G5" s="103" t="inlineStr">
+      <c r="G5" s="105" t="inlineStr">
         <is>
           <t>Lento</t>
         </is>
       </c>
-      <c r="H5" s="103" t="inlineStr">
+      <c r="H5" s="105" t="inlineStr">
         <is>
           <t>Incapacitado</t>
         </is>
       </c>
-      <c r="I5" s="103" t="inlineStr">
+      <c r="I5" s="105" t="inlineStr">
         <is>
           <t>Receptáculo</t>
         </is>
       </c>
-      <c r="J5" s="103" t="inlineStr">
+      <c r="J5" s="105" t="inlineStr">
         <is>
           <t>Vigor</t>
         </is>
       </c>
-      <c r="K5" s="103" t="inlineStr">
+      <c r="K5" s="105" t="inlineStr">
         <is>
           <t>escala</t>
         </is>
       </c>
-      <c r="L5" s="103" t="inlineStr">
+      <c r="L5" s="105" t="inlineStr">
         <is>
           <t>Punho</t>
         </is>
       </c>
       <c r="M5" s="40" t="n"/>
-      <c r="N5" s="103" t="inlineStr">
+      <c r="N5" s="105" t="inlineStr">
         <is>
           <t>Bastião</t>
         </is>
       </c>
-      <c r="O5" s="103" t="inlineStr">
+      <c r="O5" s="105" t="inlineStr">
         <is>
           <t>d12</t>
         </is>
       </c>
-      <c r="P5" s="103" t="n">
+      <c r="P5" s="105" t="n">
         <v>12</v>
       </c>
-      <c r="Q5" s="103" t="n">
+      <c r="Q5" s="105" t="n">
         <v>7</v>
       </c>
-      <c r="R5" s="103" t="n">
+      <c r="R5" s="105" t="n">
         <v>4</v>
       </c>
-      <c r="S5" s="103" t="inlineStr">
+      <c r="S5" s="105" t="inlineStr">
         <is>
           <t>Atletismo</t>
         </is>
       </c>
-      <c r="T5" s="103" t="inlineStr">
+      <c r="T5" s="105" t="inlineStr">
         <is>
           <t>Intimidação</t>
         </is>
       </c>
-      <c r="U5" s="103" t="inlineStr">
+      <c r="U5" s="105" t="inlineStr">
         <is>
           <t>Forja</t>
         </is>
       </c>
       <c r="V5" s="40" t="n"/>
-      <c r="W5" s="105" t="n">
+      <c r="W5" s="107" t="n">
         <v>6</v>
       </c>
-      <c r="X5" s="105" t="n">
+      <c r="X5" s="107" t="n">
         <v>10</v>
       </c>
-      <c r="Y5" s="105" t="n">
+      <c r="Y5" s="107" t="n">
         <v>1</v>
       </c>
-      <c r="Z5" s="105" t="n">
+      <c r="Z5" s="107" t="n">
         <v>5</v>
       </c>
       <c r="AA5" s="40" t="n"/>
-      <c r="AB5" s="103" t="inlineStr">
+      <c r="AB5" s="105" t="inlineStr">
         <is>
           <t>Atletismo</t>
         </is>
       </c>
-      <c r="AC5" s="103" t="inlineStr">
+      <c r="AC5" s="105" t="inlineStr">
         <is>
           <t>Força</t>
         </is>
@@ -11596,133 +11638,133 @@
       <c r="AX5" s="40" t="n"/>
       <c r="AY5" s="40" t="n"/>
       <c r="AZ5" s="40" t="n"/>
-      <c r="BA5" s="103" t="inlineStr">
+      <c r="BA5" s="105" t="inlineStr">
         <is>
           <t>nome</t>
         </is>
       </c>
-      <c r="BB5" s="103" t="inlineStr">
+      <c r="BB5" s="105" t="inlineStr">
         <is>
           <t>D3</t>
         </is>
       </c>
     </row>
     <row r="6" ht="17.25" customHeight="1">
-      <c r="A6" s="103" t="inlineStr">
+      <c r="A6" s="105" t="inlineStr">
         <is>
           <t>Guia</t>
         </is>
       </c>
-      <c r="B6" s="103" t="inlineStr">
+      <c r="B6" s="105" t="inlineStr">
         <is>
           <t>Furtividade</t>
         </is>
       </c>
-      <c r="C6" s="103" t="inlineStr">
+      <c r="C6" s="105" t="inlineStr">
         <is>
           <t>Herbalismo</t>
         </is>
       </c>
-      <c r="D6" s="103" t="inlineStr">
+      <c r="D6" s="105" t="inlineStr">
         <is>
           <t>Mira</t>
         </is>
       </c>
-      <c r="E6" s="103" t="inlineStr">
+      <c r="E6" s="105" t="inlineStr">
         <is>
           <t>Explosão</t>
         </is>
       </c>
-      <c r="F6" s="103" t="inlineStr">
+      <c r="F6" s="105" t="inlineStr">
         <is>
           <t>Sem Ver</t>
         </is>
       </c>
-      <c r="G6" s="103" t="inlineStr">
+      <c r="G6" s="105" t="inlineStr">
         <is>
           <t>Parado</t>
         </is>
       </c>
-      <c r="H6" s="103" t="inlineStr">
+      <c r="H6" s="105" t="inlineStr">
         <is>
           <t>Derrubado</t>
         </is>
       </c>
-      <c r="I6" s="103" t="inlineStr">
+      <c r="I6" s="105" t="inlineStr">
         <is>
           <t>Descendente</t>
         </is>
       </c>
-      <c r="J6" s="103" t="inlineStr">
+      <c r="J6" s="105" t="inlineStr">
         <is>
           <t>Intelecto</t>
         </is>
       </c>
-      <c r="K6" s="103" t="inlineStr">
+      <c r="K6" s="105" t="inlineStr">
         <is>
           <t>criacao</t>
         </is>
       </c>
-      <c r="L6" s="103" t="inlineStr">
+      <c r="L6" s="105" t="inlineStr">
         <is>
           <t>Brasa</t>
         </is>
       </c>
       <c r="M6" s="40" t="n"/>
-      <c r="N6" s="103" t="inlineStr">
+      <c r="N6" s="105" t="inlineStr">
         <is>
           <t>Vanguarda</t>
         </is>
       </c>
-      <c r="O6" s="103" t="inlineStr">
+      <c r="O6" s="105" t="inlineStr">
         <is>
           <t>d8</t>
         </is>
       </c>
-      <c r="P6" s="103" t="n">
+      <c r="P6" s="105" t="n">
         <v>8</v>
       </c>
-      <c r="Q6" s="103" t="n">
+      <c r="Q6" s="105" t="n">
         <v>5</v>
       </c>
-      <c r="R6" s="103" t="n">
+      <c r="R6" s="105" t="n">
         <v>5</v>
       </c>
-      <c r="S6" s="103" t="inlineStr">
+      <c r="S6" s="105" t="inlineStr">
         <is>
           <t>Acrobacia</t>
         </is>
       </c>
-      <c r="T6" s="103" t="inlineStr">
+      <c r="T6" s="105" t="inlineStr">
         <is>
           <t>Percepção</t>
         </is>
       </c>
-      <c r="U6" s="103" t="inlineStr">
+      <c r="U6" s="105" t="inlineStr">
         <is>
           <t>Arrombamento</t>
         </is>
       </c>
       <c r="V6" s="40" t="n"/>
-      <c r="W6" s="105" t="n">
+      <c r="W6" s="107" t="n">
         <v>10</v>
       </c>
-      <c r="X6" s="105" t="n">
+      <c r="X6" s="107" t="n">
         <v>18</v>
       </c>
-      <c r="Y6" s="105" t="n">
+      <c r="Y6" s="107" t="n">
         <v>5</v>
       </c>
-      <c r="Z6" s="105" t="n">
+      <c r="Z6" s="107" t="n">
         <v>11</v>
       </c>
       <c r="AA6" s="40" t="n"/>
-      <c r="AB6" s="103" t="inlineStr">
+      <c r="AB6" s="105" t="inlineStr">
         <is>
           <t>Acrobacia</t>
         </is>
       </c>
-      <c r="AC6" s="103" t="inlineStr">
+      <c r="AC6" s="105" t="inlineStr">
         <is>
           <t>Destreza</t>
         </is>
@@ -11750,133 +11792,133 @@
       <c r="AX6" s="40" t="n"/>
       <c r="AY6" s="40" t="n"/>
       <c r="AZ6" s="40" t="n"/>
-      <c r="BA6" s="103" t="inlineStr">
+      <c r="BA6" s="105" t="inlineStr">
         <is>
           <t>caminho</t>
         </is>
       </c>
-      <c r="BB6" s="103" t="inlineStr">
+      <c r="BB6" s="105" t="inlineStr">
         <is>
           <t>D11</t>
         </is>
       </c>
     </row>
     <row r="7" ht="17.25" customHeight="1">
-      <c r="A7" s="103" t="inlineStr">
+      <c r="A7" s="105" t="inlineStr">
         <is>
           <t>Emanador</t>
         </is>
       </c>
-      <c r="B7" s="103" t="inlineStr">
+      <c r="B7" s="105" t="inlineStr">
         <is>
           <t>Pontaria</t>
         </is>
       </c>
-      <c r="C7" s="103" t="inlineStr">
+      <c r="C7" s="105" t="inlineStr">
         <is>
           <t>Forja</t>
         </is>
       </c>
-      <c r="D7" s="103" t="inlineStr">
+      <c r="D7" s="105" t="inlineStr">
         <is>
           <t>Controle</t>
         </is>
       </c>
-      <c r="E7" s="103" t="inlineStr">
+      <c r="E7" s="105" t="inlineStr">
         <is>
           <t>Aura</t>
         </is>
       </c>
-      <c r="F7" s="103" t="inlineStr">
+      <c r="F7" s="105" t="inlineStr">
         <is>
           <t>Passo</t>
         </is>
       </c>
-      <c r="G7" s="103" t="inlineStr">
+      <c r="G7" s="105" t="inlineStr">
         <is>
           <t>Gesto</t>
         </is>
       </c>
-      <c r="H7" s="103" t="inlineStr">
+      <c r="H7" s="105" t="inlineStr">
         <is>
           <t>Agarrado</t>
         </is>
       </c>
-      <c r="I7" s="103" t="inlineStr">
+      <c r="I7" s="105" t="inlineStr">
         <is>
           <t>Reencarnado</t>
         </is>
       </c>
-      <c r="J7" s="103" t="inlineStr">
+      <c r="J7" s="105" t="inlineStr">
         <is>
           <t>Espírito</t>
         </is>
       </c>
-      <c r="K7" s="103" t="inlineStr">
+      <c r="K7" s="105" t="inlineStr">
         <is>
           <t>nota</t>
         </is>
       </c>
-      <c r="L7" s="103" t="inlineStr">
+      <c r="L7" s="105" t="inlineStr">
         <is>
           <t>Estocada</t>
         </is>
       </c>
       <c r="M7" s="40" t="n"/>
-      <c r="N7" s="103" t="inlineStr">
+      <c r="N7" s="105" t="inlineStr">
         <is>
           <t>Guia</t>
         </is>
       </c>
-      <c r="O7" s="103" t="inlineStr">
+      <c r="O7" s="105" t="inlineStr">
         <is>
           <t>d8</t>
         </is>
       </c>
-      <c r="P7" s="103" t="n">
+      <c r="P7" s="105" t="n">
         <v>8</v>
       </c>
-      <c r="Q7" s="103" t="n">
+      <c r="Q7" s="105" t="n">
         <v>5</v>
       </c>
-      <c r="R7" s="103" t="n">
+      <c r="R7" s="105" t="n">
         <v>5</v>
       </c>
-      <c r="S7" s="103" t="inlineStr">
+      <c r="S7" s="105" t="inlineStr">
         <is>
           <t>Persuasão</t>
         </is>
       </c>
-      <c r="T7" s="103" t="inlineStr">
+      <c r="T7" s="105" t="inlineStr">
         <is>
           <t>Medicina</t>
         </is>
       </c>
-      <c r="U7" s="103" t="inlineStr">
+      <c r="U7" s="105" t="inlineStr">
         <is>
           <t>Herbalismo</t>
         </is>
       </c>
       <c r="V7" s="40" t="n"/>
-      <c r="W7" s="105" t="n">
+      <c r="W7" s="107" t="n">
         <v>14</v>
       </c>
-      <c r="X7" s="105" t="n">
+      <c r="X7" s="107" t="n">
         <v>26</v>
       </c>
-      <c r="Y7" s="105" t="n">
+      <c r="Y7" s="107" t="n">
         <v>9</v>
       </c>
-      <c r="Z7" s="105" t="n">
+      <c r="Z7" s="107" t="n">
         <v>17</v>
       </c>
       <c r="AA7" s="40" t="n"/>
-      <c r="AB7" s="103" t="inlineStr">
+      <c r="AB7" s="105" t="inlineStr">
         <is>
           <t>Furtividade</t>
         </is>
       </c>
-      <c r="AC7" s="103" t="inlineStr">
+      <c r="AC7" s="105" t="inlineStr">
         <is>
           <t>Destreza</t>
         </is>
@@ -11904,12 +11946,12 @@
       <c r="AX7" s="40" t="n"/>
       <c r="AY7" s="40" t="n"/>
       <c r="AZ7" s="40" t="n"/>
-      <c r="BA7" s="103" t="inlineStr">
+      <c r="BA7" s="105" t="inlineStr">
         <is>
           <t>trilha</t>
         </is>
       </c>
-      <c r="BB7" s="103" t="inlineStr">
+      <c r="BB7" s="105" t="inlineStr">
         <is>
           <t>N11</t>
         </is>
@@ -11917,108 +11959,108 @@
     </row>
     <row r="8" ht="17.25" customHeight="1">
       <c r="A8" s="40" t="n"/>
-      <c r="B8" s="103" t="inlineStr">
+      <c r="B8" s="105" t="inlineStr">
         <is>
           <t>Prestidigitação</t>
         </is>
       </c>
-      <c r="C8" s="103" t="inlineStr">
+      <c r="C8" s="105" t="inlineStr">
         <is>
           <t>Caligrafia</t>
         </is>
       </c>
-      <c r="D8" s="103" t="inlineStr">
+      <c r="D8" s="105" t="inlineStr">
         <is>
           <t>Auxiliares</t>
         </is>
       </c>
-      <c r="E8" s="103" t="inlineStr">
+      <c r="E8" s="105" t="inlineStr">
         <is>
           <t>Cone</t>
         </is>
       </c>
-      <c r="F8" s="103" t="inlineStr">
+      <c r="F8" s="105" t="inlineStr">
         <is>
           <t>Empurrão</t>
         </is>
       </c>
-      <c r="G8" s="103" t="inlineStr">
+      <c r="G8" s="105" t="inlineStr">
         <is>
           <t>Sangra</t>
         </is>
       </c>
-      <c r="H8" s="103" t="inlineStr">
+      <c r="H8" s="105" t="inlineStr">
         <is>
           <t>Desarmado</t>
         </is>
       </c>
-      <c r="I8" s="103" t="inlineStr">
+      <c r="I8" s="105" t="inlineStr">
         <is>
           <t>Feto</t>
         </is>
       </c>
       <c r="J8" s="40" t="n"/>
-      <c r="K8" s="103" t="inlineStr">
+      <c r="K8" s="105" t="inlineStr">
         <is>
           <t>pagina</t>
         </is>
       </c>
-      <c r="L8" s="103" t="inlineStr">
+      <c r="L8" s="105" t="inlineStr">
         <is>
           <t>Batedor</t>
         </is>
       </c>
       <c r="M8" s="40" t="n"/>
-      <c r="N8" s="103" t="inlineStr">
+      <c r="N8" s="105" t="inlineStr">
         <is>
           <t>Evocador</t>
         </is>
       </c>
-      <c r="O8" s="103" t="inlineStr">
+      <c r="O8" s="105" t="inlineStr">
         <is>
           <t>d6</t>
         </is>
       </c>
-      <c r="P8" s="103" t="n">
+      <c r="P8" s="105" t="n">
         <v>6</v>
       </c>
-      <c r="Q8" s="103" t="n">
+      <c r="Q8" s="105" t="n">
         <v>4</v>
       </c>
-      <c r="R8" s="103" t="n">
+      <c r="R8" s="105" t="n">
         <v>6</v>
       </c>
-      <c r="S8" s="103" t="inlineStr">
+      <c r="S8" s="105" t="inlineStr">
         <is>
           <t>Religião</t>
         </is>
       </c>
-      <c r="T8" s="103" t="inlineStr">
+      <c r="T8" s="105" t="inlineStr">
         <is>
           <t>Lidar com Animais</t>
         </is>
       </c>
-      <c r="U8" s="103" t="inlineStr">
+      <c r="U8" s="105" t="inlineStr">
         <is>
           <t>Entalhador</t>
         </is>
       </c>
       <c r="V8" s="40" t="n"/>
-      <c r="W8" s="105" t="n">
+      <c r="W8" s="107" t="n">
         <v>18</v>
       </c>
       <c r="X8" s="40" t="n"/>
-      <c r="Y8" s="105" t="n">
+      <c r="Y8" s="107" t="n">
         <v>13</v>
       </c>
       <c r="Z8" s="40" t="n"/>
       <c r="AA8" s="40" t="n"/>
-      <c r="AB8" s="103" t="inlineStr">
+      <c r="AB8" s="105" t="inlineStr">
         <is>
           <t>Pontaria</t>
         </is>
       </c>
-      <c r="AC8" s="103" t="inlineStr">
+      <c r="AC8" s="105" t="inlineStr">
         <is>
           <t>Destreza</t>
         </is>
@@ -12046,12 +12088,12 @@
       <c r="AX8" s="40" t="n"/>
       <c r="AY8" s="40" t="n"/>
       <c r="AZ8" s="40" t="n"/>
-      <c r="BA8" s="103" t="inlineStr">
+      <c r="BA8" s="105" t="inlineStr">
         <is>
           <t>origem</t>
         </is>
       </c>
-      <c r="BB8" s="103" t="inlineStr">
+      <c r="BB8" s="105" t="inlineStr">
         <is>
           <t>X11</t>
         </is>
@@ -12059,104 +12101,104 @@
     </row>
     <row r="9" ht="17.25" customHeight="1">
       <c r="A9" s="40" t="n"/>
-      <c r="B9" s="103" t="inlineStr">
+      <c r="B9" s="105" t="inlineStr">
         <is>
           <t>Investigação</t>
         </is>
       </c>
-      <c r="C9" s="103" t="inlineStr">
+      <c r="C9" s="105" t="inlineStr">
         <is>
           <t>Burocracia</t>
         </is>
       </c>
-      <c r="D9" s="103" t="inlineStr">
+      <c r="D9" s="105" t="inlineStr">
         <is>
           <t>Castigo</t>
         </is>
       </c>
-      <c r="E9" s="103" t="inlineStr">
+      <c r="E9" s="105" t="inlineStr">
         <is>
           <t>Linha</t>
         </is>
       </c>
-      <c r="F9" s="103" t="inlineStr">
+      <c r="F9" s="105" t="inlineStr">
         <is>
           <t>Troca</t>
         </is>
       </c>
-      <c r="G9" s="103" t="inlineStr">
+      <c r="G9" s="105" t="inlineStr">
         <is>
           <t>Recuo</t>
         </is>
       </c>
-      <c r="H9" s="103" t="inlineStr">
+      <c r="H9" s="105" t="inlineStr">
         <is>
           <t>Surdo</t>
         </is>
       </c>
-      <c r="I9" s="103" t="inlineStr">
+      <c r="I9" s="105" t="inlineStr">
         <is>
           <t>Corpo Amaldiçoado</t>
         </is>
       </c>
       <c r="J9" s="40" t="n"/>
       <c r="K9" s="40" t="n"/>
-      <c r="L9" s="103" t="inlineStr">
+      <c r="L9" s="105" t="inlineStr">
         <is>
           <t>Executor</t>
         </is>
       </c>
       <c r="M9" s="40" t="n"/>
-      <c r="N9" s="103" t="inlineStr">
+      <c r="N9" s="105" t="inlineStr">
         <is>
           <t>Emanador</t>
         </is>
       </c>
-      <c r="O9" s="103" t="inlineStr">
+      <c r="O9" s="105" t="inlineStr">
         <is>
           <t>d6</t>
         </is>
       </c>
-      <c r="P9" s="103" t="n">
+      <c r="P9" s="105" t="n">
         <v>6</v>
       </c>
-      <c r="Q9" s="103" t="n">
+      <c r="Q9" s="105" t="n">
         <v>4</v>
       </c>
-      <c r="R9" s="103" t="n">
+      <c r="R9" s="105" t="n">
         <v>6</v>
       </c>
-      <c r="S9" s="103" t="inlineStr">
+      <c r="S9" s="105" t="inlineStr">
         <is>
           <t>Ocultismo</t>
         </is>
       </c>
-      <c r="T9" s="103" t="inlineStr">
+      <c r="T9" s="105" t="inlineStr">
         <is>
           <t>Investigação</t>
         </is>
       </c>
-      <c r="U9" s="103" t="inlineStr">
+      <c r="U9" s="105" t="inlineStr">
         <is>
           <t>Caligrafia</t>
         </is>
       </c>
       <c r="V9" s="40" t="n"/>
-      <c r="W9" s="105" t="n">
+      <c r="W9" s="107" t="n">
         <v>22</v>
       </c>
       <c r="X9" s="40" t="n"/>
-      <c r="Y9" s="105" t="n">
+      <c r="Y9" s="107" t="n">
         <v>17</v>
       </c>
       <c r="Z9" s="40" t="n"/>
       <c r="AA9" s="40" t="n"/>
-      <c r="AB9" s="103" t="inlineStr">
+      <c r="AB9" s="105" t="inlineStr">
         <is>
           <t>Prestidigitação</t>
         </is>
       </c>
-      <c r="AC9" s="103" t="inlineStr">
+      <c r="AC9" s="105" t="inlineStr">
         <is>
           <t>Destreza</t>
         </is>
@@ -12184,12 +12226,12 @@
       <c r="AX9" s="40" t="n"/>
       <c r="AY9" s="40" t="n"/>
       <c r="AZ9" s="40" t="n"/>
-      <c r="BA9" s="103" t="inlineStr">
+      <c r="BA9" s="105" t="inlineStr">
         <is>
           <t>nivel</t>
         </is>
       </c>
-      <c r="BB9" s="103" t="inlineStr">
+      <c r="BB9" s="105" t="inlineStr">
         <is>
           <t>AH11</t>
         </is>
@@ -12197,49 +12239,49 @@
     </row>
     <row r="10" ht="17.25" customHeight="1">
       <c r="A10" s="40" t="n"/>
-      <c r="B10" s="103" t="inlineStr">
+      <c r="B10" s="105" t="inlineStr">
         <is>
           <t>Intuição</t>
         </is>
       </c>
-      <c r="C10" s="103" t="inlineStr">
+      <c r="C10" s="105" t="inlineStr">
         <is>
           <t>Entalhador</t>
         </is>
       </c>
-      <c r="D10" s="103" t="inlineStr">
+      <c r="D10" s="105" t="inlineStr">
         <is>
           <t>Tempo</t>
         </is>
       </c>
-      <c r="E10" s="103" t="inlineStr">
+      <c r="E10" s="105" t="inlineStr">
         <is>
           <t>Cura</t>
         </is>
       </c>
-      <c r="F10" s="103" t="inlineStr">
+      <c r="F10" s="105" t="inlineStr">
         <is>
           <t>Perseguir</t>
         </is>
       </c>
-      <c r="G10" s="103" t="inlineStr">
+      <c r="G10" s="105" t="inlineStr">
         <is>
           <t>Carregar</t>
         </is>
       </c>
-      <c r="H10" s="103" t="inlineStr">
+      <c r="H10" s="105" t="inlineStr">
         <is>
           <t>Calado</t>
         </is>
       </c>
-      <c r="I10" s="103" t="inlineStr">
+      <c r="I10" s="105" t="inlineStr">
         <is>
           <t>Restrição Celestial</t>
         </is>
       </c>
       <c r="J10" s="40" t="n"/>
       <c r="K10" s="40" t="n"/>
-      <c r="L10" s="103" t="inlineStr">
+      <c r="L10" s="105" t="inlineStr">
         <is>
           <t>Elo</t>
         </is>
@@ -12254,21 +12296,21 @@
       <c r="T10" s="40" t="n"/>
       <c r="U10" s="40" t="n"/>
       <c r="V10" s="40" t="n"/>
-      <c r="W10" s="105" t="n">
+      <c r="W10" s="107" t="n">
         <v>26</v>
       </c>
       <c r="X10" s="40" t="n"/>
-      <c r="Y10" s="105" t="n">
+      <c r="Y10" s="107" t="n">
         <v>21</v>
       </c>
       <c r="Z10" s="40" t="n"/>
       <c r="AA10" s="40" t="n"/>
-      <c r="AB10" s="103" t="inlineStr">
+      <c r="AB10" s="105" t="inlineStr">
         <is>
           <t>Investigação</t>
         </is>
       </c>
-      <c r="AC10" s="103" t="inlineStr">
+      <c r="AC10" s="105" t="inlineStr">
         <is>
           <t>Inteligência</t>
         </is>
@@ -12296,12 +12338,12 @@
       <c r="AX10" s="40" t="n"/>
       <c r="AY10" s="40" t="n"/>
       <c r="AZ10" s="40" t="n"/>
-      <c r="BA10" s="103" t="inlineStr">
+      <c r="BA10" s="105" t="inlineStr">
         <is>
           <t>xp</t>
         </is>
       </c>
-      <c r="BB10" s="103" t="inlineStr">
+      <c r="BB10" s="105" t="inlineStr">
         <is>
           <t>AN11</t>
         </is>
@@ -12309,37 +12351,37 @@
     </row>
     <row r="11" ht="17.25" customHeight="1">
       <c r="A11" s="40" t="n"/>
-      <c r="B11" s="103" t="inlineStr">
+      <c r="B11" s="105" t="inlineStr">
         <is>
           <t>Ocultismo</t>
         </is>
       </c>
-      <c r="C11" s="103" t="inlineStr">
+      <c r="C11" s="105" t="inlineStr">
         <is>
           <t>Alfaiate</t>
         </is>
       </c>
-      <c r="D11" s="103" t="inlineStr">
+      <c r="D11" s="105" t="inlineStr">
         <is>
           <t>Marca</t>
         </is>
       </c>
-      <c r="E11" s="103" t="inlineStr">
+      <c r="E11" s="105" t="inlineStr">
         <is>
           <t>Apoio</t>
         </is>
       </c>
-      <c r="F11" s="103" t="inlineStr">
+      <c r="F11" s="105" t="inlineStr">
         <is>
           <t>Maior</t>
         </is>
       </c>
-      <c r="G11" s="103" t="inlineStr">
+      <c r="G11" s="105" t="inlineStr">
         <is>
           <t>Tudo ou Nada</t>
         </is>
       </c>
-      <c r="H11" s="103" t="inlineStr">
+      <c r="H11" s="105" t="inlineStr">
         <is>
           <t>Enfeitiçado</t>
         </is>
@@ -12347,7 +12389,7 @@
       <c r="I11" s="40" t="n"/>
       <c r="J11" s="40" t="n"/>
       <c r="K11" s="40" t="n"/>
-      <c r="L11" s="103" t="inlineStr">
+      <c r="L11" s="105" t="inlineStr">
         <is>
           <t>Sutura</t>
         </is>
@@ -12362,21 +12404,21 @@
       <c r="T11" s="40" t="n"/>
       <c r="U11" s="40" t="n"/>
       <c r="V11" s="40" t="n"/>
-      <c r="W11" s="105" t="n">
+      <c r="W11" s="107" t="n">
         <v>30</v>
       </c>
       <c r="X11" s="40" t="n"/>
-      <c r="Y11" s="105" t="n">
+      <c r="Y11" s="107" t="n">
         <v>26</v>
       </c>
       <c r="Z11" s="40" t="n"/>
       <c r="AA11" s="40" t="n"/>
-      <c r="AB11" s="103" t="inlineStr">
+      <c r="AB11" s="105" t="inlineStr">
         <is>
           <t>Intuição</t>
         </is>
       </c>
-      <c r="AC11" s="103" t="inlineStr">
+      <c r="AC11" s="105" t="inlineStr">
         <is>
           <t>Inteligência</t>
         </is>
@@ -12404,12 +12446,12 @@
       <c r="AX11" s="40" t="n"/>
       <c r="AY11" s="40" t="n"/>
       <c r="AZ11" s="40" t="n"/>
-      <c r="BA11" s="103" t="inlineStr">
+      <c r="BA11" s="105" t="inlineStr">
         <is>
           <t>atr_Força</t>
         </is>
       </c>
-      <c r="BB11" s="103" t="inlineStr">
+      <c r="BB11" s="105" t="inlineStr">
         <is>
           <t>D17</t>
         </is>
@@ -12417,37 +12459,37 @@
     </row>
     <row r="12" ht="17.25" customHeight="1">
       <c r="A12" s="40" t="n"/>
-      <c r="B12" s="103" t="inlineStr">
+      <c r="B12" s="105" t="inlineStr">
         <is>
           <t>Religião</t>
         </is>
       </c>
-      <c r="C12" s="103" t="inlineStr">
+      <c r="C12" s="105" t="inlineStr">
         <is>
           <t>Culinária</t>
         </is>
       </c>
-      <c r="D12" s="103" t="inlineStr">
+      <c r="D12" s="105" t="inlineStr">
         <is>
           <t>Amparo</t>
         </is>
       </c>
-      <c r="E12" s="103" t="inlineStr">
+      <c r="E12" s="105" t="inlineStr">
         <is>
           <t>Onda</t>
         </is>
       </c>
-      <c r="F12" s="103" t="inlineStr">
+      <c r="F12" s="105" t="inlineStr">
         <is>
           <t>Muito Maior</t>
         </is>
       </c>
-      <c r="G12" s="103" t="inlineStr">
+      <c r="G12" s="105" t="inlineStr">
         <is>
           <t>Uma Vez</t>
         </is>
       </c>
-      <c r="H12" s="103" t="inlineStr">
+      <c r="H12" s="105" t="inlineStr">
         <is>
           <t>Petrificado</t>
         </is>
@@ -12455,7 +12497,7 @@
       <c r="I12" s="40" t="n"/>
       <c r="J12" s="40" t="n"/>
       <c r="K12" s="40" t="n"/>
-      <c r="L12" s="103" t="inlineStr">
+      <c r="L12" s="105" t="inlineStr">
         <is>
           <t>Perímetro</t>
         </is>
@@ -12475,12 +12517,12 @@
       <c r="Y12" s="40" t="n"/>
       <c r="Z12" s="40" t="n"/>
       <c r="AA12" s="40" t="n"/>
-      <c r="AB12" s="103" t="inlineStr">
+      <c r="AB12" s="105" t="inlineStr">
         <is>
           <t>Ocultismo</t>
         </is>
       </c>
-      <c r="AC12" s="103" t="inlineStr">
+      <c r="AC12" s="105" t="inlineStr">
         <is>
           <t>Inteligência</t>
         </is>
@@ -12508,12 +12550,12 @@
       <c r="AX12" s="40" t="n"/>
       <c r="AY12" s="40" t="n"/>
       <c r="AZ12" s="40" t="n"/>
-      <c r="BA12" s="103" t="inlineStr">
+      <c r="BA12" s="105" t="inlineStr">
         <is>
           <t>atr_Destreza</t>
         </is>
       </c>
-      <c r="BB12" s="103" t="inlineStr">
+      <c r="BB12" s="105" t="inlineStr">
         <is>
           <t>L17</t>
         </is>
@@ -12521,33 +12563,33 @@
     </row>
     <row r="13" ht="17.25" customHeight="1">
       <c r="A13" s="40" t="n"/>
-      <c r="B13" s="103" t="inlineStr">
+      <c r="B13" s="105" t="inlineStr">
         <is>
           <t>História</t>
         </is>
       </c>
-      <c r="C13" s="103" t="inlineStr">
+      <c r="C13" s="105" t="inlineStr">
         <is>
           <t>Instrumento</t>
         </is>
       </c>
       <c r="D13" s="40" t="n"/>
-      <c r="E13" s="103" t="inlineStr">
+      <c r="E13" s="105" t="inlineStr">
         <is>
           <t>Efeito</t>
         </is>
       </c>
-      <c r="F13" s="103" t="inlineStr">
+      <c r="F13" s="105" t="inlineStr">
         <is>
           <t>Escolher</t>
         </is>
       </c>
-      <c r="G13" s="103" t="inlineStr">
+      <c r="G13" s="105" t="inlineStr">
         <is>
           <t>Condicional</t>
         </is>
       </c>
-      <c r="H13" s="103" t="inlineStr">
+      <c r="H13" s="105" t="inlineStr">
         <is>
           <t>Impedido</t>
         </is>
@@ -12555,7 +12597,7 @@
       <c r="I13" s="40" t="n"/>
       <c r="J13" s="40" t="n"/>
       <c r="K13" s="40" t="n"/>
-      <c r="L13" s="103" t="inlineStr">
+      <c r="L13" s="105" t="inlineStr">
         <is>
           <t>Torrente</t>
         </is>
@@ -12575,12 +12617,12 @@
       <c r="Y13" s="40" t="n"/>
       <c r="Z13" s="40" t="n"/>
       <c r="AA13" s="40" t="n"/>
-      <c r="AB13" s="103" t="inlineStr">
+      <c r="AB13" s="105" t="inlineStr">
         <is>
           <t>Religião</t>
         </is>
       </c>
-      <c r="AC13" s="103" t="inlineStr">
+      <c r="AC13" s="105" t="inlineStr">
         <is>
           <t>Inteligência</t>
         </is>
@@ -12608,12 +12650,12 @@
       <c r="AX13" s="40" t="n"/>
       <c r="AY13" s="40" t="n"/>
       <c r="AZ13" s="40" t="n"/>
-      <c r="BA13" s="103" t="inlineStr">
+      <c r="BA13" s="105" t="inlineStr">
         <is>
           <t>atr_Constituição</t>
         </is>
       </c>
-      <c r="BB13" s="103" t="inlineStr">
+      <c r="BB13" s="105" t="inlineStr">
         <is>
           <t>T17</t>
         </is>
@@ -12621,29 +12663,29 @@
     </row>
     <row r="14" ht="17.25" customHeight="1">
       <c r="A14" s="40" t="n"/>
-      <c r="B14" s="103" t="inlineStr">
+      <c r="B14" s="105" t="inlineStr">
         <is>
           <t>Hierarquia</t>
         </is>
       </c>
-      <c r="C14" s="103" t="inlineStr">
+      <c r="C14" s="105" t="inlineStr">
         <is>
           <t>Jogatina</t>
         </is>
       </c>
       <c r="D14" s="40" t="n"/>
       <c r="E14" s="40" t="n"/>
-      <c r="F14" s="103" t="inlineStr">
+      <c r="F14" s="105" t="inlineStr">
         <is>
           <t>Fica</t>
         </is>
       </c>
-      <c r="G14" s="103" t="inlineStr">
+      <c r="G14" s="105" t="inlineStr">
         <is>
           <t>Fraqueza</t>
         </is>
       </c>
-      <c r="H14" s="103" t="inlineStr">
+      <c r="H14" s="105" t="inlineStr">
         <is>
           <t>Cego</t>
         </is>
@@ -12651,7 +12693,7 @@
       <c r="I14" s="40" t="n"/>
       <c r="J14" s="40" t="n"/>
       <c r="K14" s="40" t="n"/>
-      <c r="L14" s="103" t="inlineStr">
+      <c r="L14" s="105" t="inlineStr">
         <is>
           <t>Explosivo</t>
         </is>
@@ -12671,12 +12713,12 @@
       <c r="Y14" s="40" t="n"/>
       <c r="Z14" s="40" t="n"/>
       <c r="AA14" s="40" t="n"/>
-      <c r="AB14" s="103" t="inlineStr">
+      <c r="AB14" s="105" t="inlineStr">
         <is>
           <t>História</t>
         </is>
       </c>
-      <c r="AC14" s="103" t="inlineStr">
+      <c r="AC14" s="105" t="inlineStr">
         <is>
           <t>Inteligência</t>
         </is>
@@ -12704,12 +12746,12 @@
       <c r="AX14" s="40" t="n"/>
       <c r="AY14" s="40" t="n"/>
       <c r="AZ14" s="40" t="n"/>
-      <c r="BA14" s="103" t="inlineStr">
+      <c r="BA14" s="105" t="inlineStr">
         <is>
           <t>atr_Inteligência</t>
         </is>
       </c>
-      <c r="BB14" s="103" t="inlineStr">
+      <c r="BB14" s="105" t="inlineStr">
         <is>
           <t>AB17</t>
         </is>
@@ -12717,7 +12759,7 @@
     </row>
     <row r="15" ht="17.25" customHeight="1">
       <c r="A15" s="40" t="n"/>
-      <c r="B15" s="103" t="inlineStr">
+      <c r="B15" s="105" t="inlineStr">
         <is>
           <t>Medicina</t>
         </is>
@@ -12725,17 +12767,17 @@
       <c r="C15" s="40" t="n"/>
       <c r="D15" s="40" t="n"/>
       <c r="E15" s="40" t="n"/>
-      <c r="F15" s="103" t="inlineStr">
+      <c r="F15" s="105" t="inlineStr">
         <is>
           <t>Mais Um</t>
         </is>
       </c>
-      <c r="G15" s="103" t="inlineStr">
+      <c r="G15" s="105" t="inlineStr">
         <is>
           <t>Frágil</t>
         </is>
       </c>
-      <c r="H15" s="103" t="inlineStr">
+      <c r="H15" s="105" t="inlineStr">
         <is>
           <t>Amedrontado</t>
         </is>
@@ -12743,7 +12785,7 @@
       <c r="I15" s="40" t="n"/>
       <c r="J15" s="40" t="n"/>
       <c r="K15" s="40" t="n"/>
-      <c r="L15" s="103" t="inlineStr">
+      <c r="L15" s="105" t="inlineStr">
         <is>
           <t>Arremate</t>
         </is>
@@ -12763,12 +12805,12 @@
       <c r="Y15" s="40" t="n"/>
       <c r="Z15" s="40" t="n"/>
       <c r="AA15" s="40" t="n"/>
-      <c r="AB15" s="103" t="inlineStr">
+      <c r="AB15" s="105" t="inlineStr">
         <is>
           <t>Hierarquia</t>
         </is>
       </c>
-      <c r="AC15" s="103" t="inlineStr">
+      <c r="AC15" s="105" t="inlineStr">
         <is>
           <t>Inteligência</t>
         </is>
@@ -12796,12 +12838,12 @@
       <c r="AX15" s="40" t="n"/>
       <c r="AY15" s="40" t="n"/>
       <c r="AZ15" s="40" t="n"/>
-      <c r="BA15" s="103" t="inlineStr">
+      <c r="BA15" s="105" t="inlineStr">
         <is>
           <t>atr_Essência</t>
         </is>
       </c>
-      <c r="BB15" s="103" t="inlineStr">
+      <c r="BB15" s="105" t="inlineStr">
         <is>
           <t>AJ17</t>
         </is>
@@ -12809,7 +12851,7 @@
     </row>
     <row r="16" ht="17.25" customHeight="1">
       <c r="A16" s="40" t="n"/>
-      <c r="B16" s="103" t="inlineStr">
+      <c r="B16" s="105" t="inlineStr">
         <is>
           <t>Sobrevivência</t>
         </is>
@@ -12817,17 +12859,17 @@
       <c r="C16" s="40" t="n"/>
       <c r="D16" s="40" t="n"/>
       <c r="E16" s="40" t="n"/>
-      <c r="F16" s="103" t="inlineStr">
+      <c r="F16" s="105" t="inlineStr">
         <is>
           <t>Rajada</t>
         </is>
       </c>
-      <c r="G16" s="103" t="inlineStr">
+      <c r="G16" s="105" t="inlineStr">
         <is>
           <t>Barulho</t>
         </is>
       </c>
-      <c r="H16" s="103" t="inlineStr">
+      <c r="H16" s="105" t="inlineStr">
         <is>
           <t>Envenenado</t>
         </is>
@@ -12835,7 +12877,7 @@
       <c r="I16" s="40" t="n"/>
       <c r="J16" s="40" t="n"/>
       <c r="K16" s="40" t="n"/>
-      <c r="L16" s="103" t="inlineStr">
+      <c r="L16" s="105" t="inlineStr">
         <is>
           <t>Servo</t>
         </is>
@@ -12855,12 +12897,12 @@
       <c r="Y16" s="40" t="n"/>
       <c r="Z16" s="40" t="n"/>
       <c r="AA16" s="40" t="n"/>
-      <c r="AB16" s="103" t="inlineStr">
+      <c r="AB16" s="105" t="inlineStr">
         <is>
           <t>Medicina</t>
         </is>
       </c>
-      <c r="AC16" s="103" t="inlineStr">
+      <c r="AC16" s="105" t="inlineStr">
         <is>
           <t>Inteligência</t>
         </is>
@@ -12888,12 +12930,12 @@
       <c r="AX16" s="40" t="n"/>
       <c r="AY16" s="40" t="n"/>
       <c r="AZ16" s="40" t="n"/>
-      <c r="BA16" s="103" t="inlineStr">
+      <c r="BA16" s="105" t="inlineStr">
         <is>
           <t>vida</t>
         </is>
       </c>
-      <c r="BB16" s="103" t="inlineStr">
+      <c r="BB16" s="105" t="inlineStr">
         <is>
           <t>D23</t>
         </is>
@@ -12901,7 +12943,7 @@
     </row>
     <row r="17" ht="17.25" customHeight="1">
       <c r="A17" s="40" t="n"/>
-      <c r="B17" s="103" t="inlineStr">
+      <c r="B17" s="105" t="inlineStr">
         <is>
           <t>Natureza</t>
         </is>
@@ -12909,17 +12951,17 @@
       <c r="C17" s="40" t="n"/>
       <c r="D17" s="40" t="n"/>
       <c r="E17" s="40" t="n"/>
-      <c r="F17" s="103" t="inlineStr">
+      <c r="F17" s="105" t="inlineStr">
         <is>
           <t>Salto</t>
         </is>
       </c>
-      <c r="G17" s="103" t="inlineStr">
+      <c r="G17" s="105" t="inlineStr">
         <is>
           <t>Assinatura</t>
         </is>
       </c>
-      <c r="H17" s="103" t="inlineStr">
+      <c r="H17" s="105" t="inlineStr">
         <is>
           <t>Atordoado</t>
         </is>
@@ -12927,7 +12969,7 @@
       <c r="I17" s="40" t="n"/>
       <c r="J17" s="40" t="n"/>
       <c r="K17" s="40" t="n"/>
-      <c r="L17" s="103" t="inlineStr">
+      <c r="L17" s="105" t="inlineStr">
         <is>
           <t>Matilha</t>
         </is>
@@ -12947,12 +12989,12 @@
       <c r="Y17" s="40" t="n"/>
       <c r="Z17" s="40" t="n"/>
       <c r="AA17" s="40" t="n"/>
-      <c r="AB17" s="103" t="inlineStr">
+      <c r="AB17" s="105" t="inlineStr">
         <is>
           <t>Sobrevivência</t>
         </is>
       </c>
-      <c r="AC17" s="103" t="inlineStr">
+      <c r="AC17" s="105" t="inlineStr">
         <is>
           <t>Inteligência</t>
         </is>
@@ -12980,12 +13022,12 @@
       <c r="AX17" s="40" t="n"/>
       <c r="AY17" s="40" t="n"/>
       <c r="AZ17" s="40" t="n"/>
-      <c r="BA17" s="103" t="inlineStr">
+      <c r="BA17" s="105" t="inlineStr">
         <is>
           <t>vida_max</t>
         </is>
       </c>
-      <c r="BB17" s="103" t="inlineStr">
+      <c r="BB17" s="105" t="inlineStr">
         <is>
           <t>J23</t>
         </is>
@@ -12993,7 +13035,7 @@
     </row>
     <row r="18" ht="17.25" customHeight="1">
       <c r="A18" s="40" t="n"/>
-      <c r="B18" s="103" t="inlineStr">
+      <c r="B18" s="105" t="inlineStr">
         <is>
           <t>Lidar com Animais</t>
         </is>
@@ -13001,12 +13043,12 @@
       <c r="C18" s="40" t="n"/>
       <c r="D18" s="40" t="n"/>
       <c r="E18" s="40" t="n"/>
-      <c r="F18" s="103" t="inlineStr">
+      <c r="F18" s="105" t="inlineStr">
         <is>
           <t>Contorno</t>
         </is>
       </c>
-      <c r="G18" s="103" t="inlineStr">
+      <c r="G18" s="105" t="inlineStr">
         <is>
           <t>Aquecer</t>
         </is>
@@ -13015,7 +13057,7 @@
       <c r="I18" s="40" t="n"/>
       <c r="J18" s="40" t="n"/>
       <c r="K18" s="40" t="n"/>
-      <c r="L18" s="103" t="inlineStr">
+      <c r="L18" s="105" t="inlineStr">
         <is>
           <t>Coro</t>
         </is>
@@ -13035,12 +13077,12 @@
       <c r="Y18" s="40" t="n"/>
       <c r="Z18" s="40" t="n"/>
       <c r="AA18" s="40" t="n"/>
-      <c r="AB18" s="103" t="inlineStr">
+      <c r="AB18" s="105" t="inlineStr">
         <is>
           <t>Natureza</t>
         </is>
       </c>
-      <c r="AC18" s="103" t="inlineStr">
+      <c r="AC18" s="105" t="inlineStr">
         <is>
           <t>Inteligência</t>
         </is>
@@ -13068,12 +13110,12 @@
       <c r="AX18" s="40" t="n"/>
       <c r="AY18" s="40" t="n"/>
       <c r="AZ18" s="40" t="n"/>
-      <c r="BA18" s="103" t="inlineStr">
+      <c r="BA18" s="105" t="inlineStr">
         <is>
           <t>vida_temp</t>
         </is>
       </c>
-      <c r="BB18" s="103" t="inlineStr">
+      <c r="BB18" s="105" t="inlineStr">
         <is>
           <t>AF23</t>
         </is>
@@ -13081,7 +13123,7 @@
     </row>
     <row r="19" ht="17.25" customHeight="1">
       <c r="A19" s="40" t="n"/>
-      <c r="B19" s="103" t="inlineStr">
+      <c r="B19" s="105" t="inlineStr">
         <is>
           <t>Tecnologia</t>
         </is>
@@ -13089,12 +13131,12 @@
       <c r="C19" s="40" t="n"/>
       <c r="D19" s="40" t="n"/>
       <c r="E19" s="40" t="n"/>
-      <c r="F19" s="103" t="inlineStr">
+      <c r="F19" s="105" t="inlineStr">
         <is>
           <t>Precisão</t>
         </is>
       </c>
-      <c r="G19" s="103" t="inlineStr">
+      <c r="G19" s="105" t="inlineStr">
         <is>
           <t>Dívida</t>
         </is>
@@ -13119,12 +13161,12 @@
       <c r="Y19" s="40" t="n"/>
       <c r="Z19" s="40" t="n"/>
       <c r="AA19" s="40" t="n"/>
-      <c r="AB19" s="103" t="inlineStr">
+      <c r="AB19" s="105" t="inlineStr">
         <is>
           <t>Lidar com Animais</t>
         </is>
       </c>
-      <c r="AC19" s="103" t="inlineStr">
+      <c r="AC19" s="105" t="inlineStr">
         <is>
           <t>Inteligência</t>
         </is>
@@ -13152,12 +13194,12 @@
       <c r="AX19" s="40" t="n"/>
       <c r="AY19" s="40" t="n"/>
       <c r="AZ19" s="40" t="n"/>
-      <c r="BA19" s="103" t="inlineStr">
+      <c r="BA19" s="105" t="inlineStr">
         <is>
           <t>vida_delta</t>
         </is>
       </c>
-      <c r="BB19" s="103" t="inlineStr">
+      <c r="BB19" s="105" t="inlineStr">
         <is>
           <t>AM23</t>
         </is>
@@ -13165,7 +13207,7 @@
     </row>
     <row r="20" ht="17.25" customHeight="1">
       <c r="A20" s="40" t="n"/>
-      <c r="B20" s="103" t="inlineStr">
+      <c r="B20" s="105" t="inlineStr">
         <is>
           <t>Sentir Energia</t>
         </is>
@@ -13173,12 +13215,12 @@
       <c r="C20" s="40" t="n"/>
       <c r="D20" s="40" t="n"/>
       <c r="E20" s="40" t="n"/>
-      <c r="F20" s="103" t="inlineStr">
+      <c r="F20" s="105" t="inlineStr">
         <is>
           <t>Certeiro</t>
         </is>
       </c>
-      <c r="G20" s="103" t="inlineStr">
+      <c r="G20" s="105" t="inlineStr">
         <is>
           <t>Peso Morto</t>
         </is>
@@ -13203,12 +13245,12 @@
       <c r="Y20" s="40" t="n"/>
       <c r="Z20" s="40" t="n"/>
       <c r="AA20" s="40" t="n"/>
-      <c r="AB20" s="103" t="inlineStr">
+      <c r="AB20" s="105" t="inlineStr">
         <is>
           <t>Tecnologia</t>
         </is>
       </c>
-      <c r="AC20" s="103" t="inlineStr">
+      <c r="AC20" s="105" t="inlineStr">
         <is>
           <t>Inteligência</t>
         </is>
@@ -13236,12 +13278,12 @@
       <c r="AX20" s="40" t="n"/>
       <c r="AY20" s="40" t="n"/>
       <c r="AZ20" s="40" t="n"/>
-      <c r="BA20" s="103" t="inlineStr">
+      <c r="BA20" s="105" t="inlineStr">
         <is>
           <t>energia</t>
         </is>
       </c>
-      <c r="BB20" s="103" t="inlineStr">
+      <c r="BB20" s="105" t="inlineStr">
         <is>
           <t>D27</t>
         </is>
@@ -13249,7 +13291,7 @@
     </row>
     <row r="21" ht="17.25" customHeight="1">
       <c r="A21" s="40" t="n"/>
-      <c r="B21" s="103" t="inlineStr">
+      <c r="B21" s="105" t="inlineStr">
         <is>
           <t>Percepção</t>
         </is>
@@ -13257,12 +13299,12 @@
       <c r="C21" s="40" t="n"/>
       <c r="D21" s="40" t="n"/>
       <c r="E21" s="40" t="n"/>
-      <c r="F21" s="103" t="inlineStr">
+      <c r="F21" s="105" t="inlineStr">
         <is>
           <t>Inescapável</t>
         </is>
       </c>
-      <c r="G21" s="103" t="inlineStr">
+      <c r="G21" s="105" t="inlineStr">
         <is>
           <t>Sem Volta</t>
         </is>
@@ -13287,12 +13329,12 @@
       <c r="Y21" s="40" t="n"/>
       <c r="Z21" s="40" t="n"/>
       <c r="AA21" s="40" t="n"/>
-      <c r="AB21" s="103" t="inlineStr">
+      <c r="AB21" s="105" t="inlineStr">
         <is>
           <t>Sentir Energia</t>
         </is>
       </c>
-      <c r="AC21" s="103" t="inlineStr">
+      <c r="AC21" s="105" t="inlineStr">
         <is>
           <t>Essência</t>
         </is>
@@ -13320,12 +13362,12 @@
       <c r="AX21" s="40" t="n"/>
       <c r="AY21" s="40" t="n"/>
       <c r="AZ21" s="40" t="n"/>
-      <c r="BA21" s="103" t="inlineStr">
+      <c r="BA21" s="105" t="inlineStr">
         <is>
           <t>energia_max</t>
         </is>
       </c>
-      <c r="BB21" s="103" t="inlineStr">
+      <c r="BB21" s="105" t="inlineStr">
         <is>
           <t>J27</t>
         </is>
@@ -13333,7 +13375,7 @@
     </row>
     <row r="22" ht="17.25" customHeight="1">
       <c r="A22" s="40" t="n"/>
-      <c r="B22" s="103" t="inlineStr">
+      <c r="B22" s="105" t="inlineStr">
         <is>
           <t>Persuasão</t>
         </is>
@@ -13341,12 +13383,12 @@
       <c r="C22" s="40" t="n"/>
       <c r="D22" s="40" t="n"/>
       <c r="E22" s="40" t="n"/>
-      <c r="F22" s="103" t="inlineStr">
+      <c r="F22" s="105" t="inlineStr">
         <is>
           <t>Fura</t>
         </is>
       </c>
-      <c r="G22" s="103" t="inlineStr">
+      <c r="G22" s="105" t="inlineStr">
         <is>
           <t>Restrição Própria</t>
         </is>
@@ -13371,12 +13413,12 @@
       <c r="Y22" s="40" t="n"/>
       <c r="Z22" s="40" t="n"/>
       <c r="AA22" s="40" t="n"/>
-      <c r="AB22" s="103" t="inlineStr">
+      <c r="AB22" s="105" t="inlineStr">
         <is>
           <t>Percepção</t>
         </is>
       </c>
-      <c r="AC22" s="103" t="inlineStr">
+      <c r="AC22" s="105" t="inlineStr">
         <is>
           <t>Essência</t>
         </is>
@@ -13404,12 +13446,12 @@
       <c r="AX22" s="40" t="n"/>
       <c r="AY22" s="40" t="n"/>
       <c r="AZ22" s="40" t="n"/>
-      <c r="BA22" s="103" t="inlineStr">
+      <c r="BA22" s="105" t="inlineStr">
         <is>
           <t>energia_temp</t>
         </is>
       </c>
-      <c r="BB22" s="103" t="inlineStr">
+      <c r="BB22" s="105" t="inlineStr">
         <is>
           <t>AF27</t>
         </is>
@@ -13417,7 +13459,7 @@
     </row>
     <row r="23" ht="17.25" customHeight="1">
       <c r="A23" s="40" t="n"/>
-      <c r="B23" s="103" t="inlineStr">
+      <c r="B23" s="105" t="inlineStr">
         <is>
           <t>Enganação</t>
         </is>
@@ -13425,7 +13467,7 @@
       <c r="C23" s="40" t="n"/>
       <c r="D23" s="40" t="n"/>
       <c r="E23" s="40" t="n"/>
-      <c r="F23" s="103" t="inlineStr">
+      <c r="F23" s="105" t="inlineStr">
         <is>
           <t>Corrói</t>
         </is>
@@ -13451,12 +13493,12 @@
       <c r="Y23" s="40" t="n"/>
       <c r="Z23" s="40" t="n"/>
       <c r="AA23" s="40" t="n"/>
-      <c r="AB23" s="103" t="inlineStr">
+      <c r="AB23" s="105" t="inlineStr">
         <is>
           <t>Persuasão</t>
         </is>
       </c>
-      <c r="AC23" s="103" t="inlineStr">
+      <c r="AC23" s="105" t="inlineStr">
         <is>
           <t>Essência</t>
         </is>
@@ -13484,12 +13526,12 @@
       <c r="AX23" s="40" t="n"/>
       <c r="AY23" s="40" t="n"/>
       <c r="AZ23" s="40" t="n"/>
-      <c r="BA23" s="103" t="inlineStr">
+      <c r="BA23" s="105" t="inlineStr">
         <is>
           <t>energia_delta</t>
         </is>
       </c>
-      <c r="BB23" s="103" t="inlineStr">
+      <c r="BB23" s="105" t="inlineStr">
         <is>
           <t>AM27</t>
         </is>
@@ -13497,7 +13539,7 @@
     </row>
     <row r="24" ht="17.25" customHeight="1">
       <c r="A24" s="40" t="n"/>
-      <c r="B24" s="103" t="inlineStr">
+      <c r="B24" s="105" t="inlineStr">
         <is>
           <t>Intimidação</t>
         </is>
@@ -13505,7 +13547,7 @@
       <c r="C24" s="40" t="n"/>
       <c r="D24" s="40" t="n"/>
       <c r="E24" s="40" t="n"/>
-      <c r="F24" s="103" t="inlineStr">
+      <c r="F24" s="105" t="inlineStr">
         <is>
           <t>Sem Cobertura</t>
         </is>
@@ -13531,12 +13573,12 @@
       <c r="Y24" s="40" t="n"/>
       <c r="Z24" s="40" t="n"/>
       <c r="AA24" s="40" t="n"/>
-      <c r="AB24" s="103" t="inlineStr">
+      <c r="AB24" s="105" t="inlineStr">
         <is>
           <t>Enganação</t>
         </is>
       </c>
-      <c r="AC24" s="103" t="inlineStr">
+      <c r="AC24" s="105" t="inlineStr">
         <is>
           <t>Essência</t>
         </is>
@@ -13564,12 +13606,12 @@
       <c r="AX24" s="40" t="n"/>
       <c r="AY24" s="40" t="n"/>
       <c r="AZ24" s="40" t="n"/>
-      <c r="BA24" s="103" t="inlineStr">
+      <c r="BA24" s="105" t="inlineStr">
         <is>
           <t>integridade</t>
         </is>
       </c>
-      <c r="BB24" s="103" t="inlineStr">
+      <c r="BB24" s="105" t="inlineStr">
         <is>
           <t>D31</t>
         </is>
@@ -13577,7 +13619,7 @@
     </row>
     <row r="25" ht="17.25" customHeight="1">
       <c r="A25" s="40" t="n"/>
-      <c r="B25" s="103" t="inlineStr">
+      <c r="B25" s="105" t="inlineStr">
         <is>
           <t>Atuação</t>
         </is>
@@ -13585,7 +13627,7 @@
       <c r="C25" s="40" t="n"/>
       <c r="D25" s="40" t="n"/>
       <c r="E25" s="40" t="n"/>
-      <c r="F25" s="103" t="inlineStr">
+      <c r="F25" s="105" t="inlineStr">
         <is>
           <t>De Novo</t>
         </is>
@@ -13611,12 +13653,12 @@
       <c r="Y25" s="40" t="n"/>
       <c r="Z25" s="40" t="n"/>
       <c r="AA25" s="40" t="n"/>
-      <c r="AB25" s="103" t="inlineStr">
+      <c r="AB25" s="105" t="inlineStr">
         <is>
           <t>Intimidação</t>
         </is>
       </c>
-      <c r="AC25" s="103" t="inlineStr">
+      <c r="AC25" s="105" t="inlineStr">
         <is>
           <t>Essência</t>
         </is>
@@ -13644,12 +13686,12 @@
       <c r="AX25" s="40" t="n"/>
       <c r="AY25" s="40" t="n"/>
       <c r="AZ25" s="40" t="n"/>
-      <c r="BA25" s="103" t="inlineStr">
+      <c r="BA25" s="105" t="inlineStr">
         <is>
           <t>integridade_max</t>
         </is>
       </c>
-      <c r="BB25" s="103" t="inlineStr">
+      <c r="BB25" s="105" t="inlineStr">
         <is>
           <t>J31</t>
         </is>
@@ -13657,7 +13699,7 @@
     </row>
     <row r="26" ht="17.25" customHeight="1">
       <c r="A26" s="40" t="n"/>
-      <c r="B26" s="103" t="inlineStr">
+      <c r="B26" s="105" t="inlineStr">
         <is>
           <t>Provocar</t>
         </is>
@@ -13665,7 +13707,7 @@
       <c r="C26" s="40" t="n"/>
       <c r="D26" s="40" t="n"/>
       <c r="E26" s="40" t="n"/>
-      <c r="F26" s="103" t="inlineStr">
+      <c r="F26" s="105" t="inlineStr">
         <is>
           <t>Toca a Alma</t>
         </is>
@@ -13691,12 +13733,12 @@
       <c r="Y26" s="40" t="n"/>
       <c r="Z26" s="40" t="n"/>
       <c r="AA26" s="40" t="n"/>
-      <c r="AB26" s="103" t="inlineStr">
+      <c r="AB26" s="105" t="inlineStr">
         <is>
           <t>Atuação</t>
         </is>
       </c>
-      <c r="AC26" s="103" t="inlineStr">
+      <c r="AC26" s="105" t="inlineStr">
         <is>
           <t>Essência</t>
         </is>
@@ -13724,12 +13766,12 @@
       <c r="AX26" s="40" t="n"/>
       <c r="AY26" s="40" t="n"/>
       <c r="AZ26" s="40" t="n"/>
-      <c r="BA26" s="103" t="inlineStr">
+      <c r="BA26" s="105" t="inlineStr">
         <is>
           <t>integridade_temp</t>
         </is>
       </c>
-      <c r="BB26" s="103" t="inlineStr">
+      <c r="BB26" s="105" t="inlineStr">
         <is>
           <t>AF31</t>
         </is>
@@ -13741,7 +13783,7 @@
       <c r="C27" s="40" t="n"/>
       <c r="D27" s="40" t="n"/>
       <c r="E27" s="40" t="n"/>
-      <c r="F27" s="103" t="inlineStr">
+      <c r="F27" s="105" t="inlineStr">
         <is>
           <t>Terreno</t>
         </is>
@@ -13767,12 +13809,12 @@
       <c r="Y27" s="40" t="n"/>
       <c r="Z27" s="40" t="n"/>
       <c r="AA27" s="40" t="n"/>
-      <c r="AB27" s="103" t="inlineStr">
+      <c r="AB27" s="105" t="inlineStr">
         <is>
           <t>Provocar</t>
         </is>
       </c>
-      <c r="AC27" s="103" t="inlineStr">
+      <c r="AC27" s="105" t="inlineStr">
         <is>
           <t>Essência</t>
         </is>
@@ -13800,12 +13842,12 @@
       <c r="AX27" s="40" t="n"/>
       <c r="AY27" s="40" t="n"/>
       <c r="AZ27" s="40" t="n"/>
-      <c r="BA27" s="103" t="inlineStr">
+      <c r="BA27" s="105" t="inlineStr">
         <is>
           <t>integridade_delta</t>
         </is>
       </c>
-      <c r="BB27" s="103" t="inlineStr">
+      <c r="BB27" s="105" t="inlineStr">
         <is>
           <t>AM31</t>
         </is>
@@ -13817,7 +13859,7 @@
       <c r="C28" s="40" t="n"/>
       <c r="D28" s="40" t="n"/>
       <c r="E28" s="40" t="n"/>
-      <c r="F28" s="103" t="inlineStr">
+      <c r="F28" s="105" t="inlineStr">
         <is>
           <t>Anteparo</t>
         </is>
@@ -13868,12 +13910,12 @@
       <c r="AX28" s="40" t="n"/>
       <c r="AY28" s="40" t="n"/>
       <c r="AZ28" s="40" t="n"/>
-      <c r="BA28" s="103" t="inlineStr">
+      <c r="BA28" s="105" t="inlineStr">
         <is>
           <t>estagio_alma</t>
         </is>
       </c>
-      <c r="BB28" s="103" t="inlineStr">
+      <c r="BB28" s="105" t="inlineStr">
         <is>
           <t>D34</t>
         </is>
@@ -13885,7 +13927,7 @@
       <c r="C29" s="40" t="n"/>
       <c r="D29" s="40" t="n"/>
       <c r="E29" s="40" t="n"/>
-      <c r="F29" s="103" t="inlineStr">
+      <c r="F29" s="105" t="inlineStr">
         <is>
           <t>Prende</t>
         </is>
@@ -13936,12 +13978,12 @@
       <c r="AX29" s="40" t="n"/>
       <c r="AY29" s="40" t="n"/>
       <c r="AZ29" s="40" t="n"/>
-      <c r="BA29" s="103" t="inlineStr">
+      <c r="BA29" s="105" t="inlineStr">
         <is>
           <t>defesa</t>
         </is>
       </c>
-      <c r="BB29" s="103" t="inlineStr">
+      <c r="BB29" s="105" t="inlineStr">
         <is>
           <t>D40</t>
         </is>
@@ -13953,7 +13995,7 @@
       <c r="C30" s="40" t="n"/>
       <c r="D30" s="40" t="n"/>
       <c r="E30" s="40" t="n"/>
-      <c r="F30" s="103" t="inlineStr">
+      <c r="F30" s="105" t="inlineStr">
         <is>
           <t>Cerca</t>
         </is>
@@ -14004,12 +14046,12 @@
       <c r="AX30" s="40" t="n"/>
       <c r="AY30" s="40" t="n"/>
       <c r="AZ30" s="40" t="n"/>
-      <c r="BA30" s="103" t="inlineStr">
+      <c r="BA30" s="105" t="inlineStr">
         <is>
           <t>proteção</t>
         </is>
       </c>
-      <c r="BB30" s="103" t="inlineStr">
+      <c r="BB30" s="105" t="inlineStr">
         <is>
           <t>O40</t>
         </is>
@@ -14021,7 +14063,7 @@
       <c r="C31" s="40" t="n"/>
       <c r="D31" s="40" t="n"/>
       <c r="E31" s="40" t="n"/>
-      <c r="F31" s="103" t="inlineStr">
+      <c r="F31" s="105" t="inlineStr">
         <is>
           <t>Puxa</t>
         </is>
@@ -14072,12 +14114,12 @@
       <c r="AX31" s="40" t="n"/>
       <c r="AY31" s="40" t="n"/>
       <c r="AZ31" s="40" t="n"/>
-      <c r="BA31" s="103" t="inlineStr">
+      <c r="BA31" s="105" t="inlineStr">
         <is>
           <t>equipamento</t>
         </is>
       </c>
-      <c r="BB31" s="103" t="inlineStr">
+      <c r="BB31" s="105" t="inlineStr">
         <is>
           <t>Z40</t>
         </is>
@@ -14089,7 +14131,7 @@
       <c r="C32" s="40" t="n"/>
       <c r="D32" s="40" t="n"/>
       <c r="E32" s="40" t="n"/>
-      <c r="F32" s="103" t="inlineStr">
+      <c r="F32" s="105" t="inlineStr">
         <is>
           <t>Desarma o Feitiço</t>
         </is>
@@ -14140,12 +14182,12 @@
       <c r="AX32" s="40" t="n"/>
       <c r="AY32" s="40" t="n"/>
       <c r="AZ32" s="40" t="n"/>
-      <c r="BA32" s="103" t="inlineStr">
+      <c r="BA32" s="105" t="inlineStr">
         <is>
           <t>iniciativa</t>
         </is>
       </c>
-      <c r="BB32" s="103" t="inlineStr">
+      <c r="BB32" s="105" t="inlineStr">
         <is>
           <t>AK40</t>
         </is>
@@ -14157,7 +14199,7 @@
       <c r="C33" s="40" t="n"/>
       <c r="D33" s="40" t="n"/>
       <c r="E33" s="40" t="n"/>
-      <c r="F33" s="103" t="inlineStr">
+      <c r="F33" s="105" t="inlineStr">
         <is>
           <t>Nível</t>
         </is>
@@ -14208,12 +14250,12 @@
       <c r="AX33" s="40" t="n"/>
       <c r="AY33" s="40" t="n"/>
       <c r="AZ33" s="40" t="n"/>
-      <c r="BA33" s="103" t="inlineStr">
+      <c r="BA33" s="105" t="inlineStr">
         <is>
           <t>cd de feitiço</t>
         </is>
       </c>
-      <c r="BB33" s="103" t="inlineStr">
+      <c r="BB33" s="105" t="inlineStr">
         <is>
           <t>D44</t>
         </is>
@@ -14225,7 +14267,7 @@
       <c r="C34" s="40" t="n"/>
       <c r="D34" s="40" t="n"/>
       <c r="E34" s="40" t="n"/>
-      <c r="F34" s="103" t="inlineStr">
+      <c r="F34" s="105" t="inlineStr">
         <is>
           <t>Impulso</t>
         </is>
@@ -14276,12 +14318,12 @@
       <c r="AX34" s="40" t="n"/>
       <c r="AY34" s="40" t="n"/>
       <c r="AZ34" s="40" t="n"/>
-      <c r="BA34" s="103" t="inlineStr">
+      <c r="BA34" s="105" t="inlineStr">
         <is>
           <t>conjuração</t>
         </is>
       </c>
-      <c r="BB34" s="103" t="inlineStr">
+      <c r="BB34" s="105" t="inlineStr">
         <is>
           <t>O44</t>
         </is>
@@ -14293,7 +14335,7 @@
       <c r="C35" s="40" t="n"/>
       <c r="D35" s="40" t="n"/>
       <c r="E35" s="40" t="n"/>
-      <c r="F35" s="103" t="inlineStr">
+      <c r="F35" s="105" t="inlineStr">
         <is>
           <t>Trava</t>
         </is>
@@ -14344,12 +14386,12 @@
       <c r="AX35" s="40" t="n"/>
       <c r="AY35" s="40" t="n"/>
       <c r="AZ35" s="40" t="n"/>
-      <c r="BA35" s="103" t="inlineStr">
+      <c r="BA35" s="105" t="inlineStr">
         <is>
           <t>corpo a corpo</t>
         </is>
       </c>
-      <c r="BB35" s="103" t="inlineStr">
+      <c r="BB35" s="105" t="inlineStr">
         <is>
           <t>Z44</t>
         </is>
@@ -14361,7 +14403,7 @@
       <c r="C36" s="40" t="n"/>
       <c r="D36" s="40" t="n"/>
       <c r="E36" s="40" t="n"/>
-      <c r="F36" s="103" t="inlineStr">
+      <c r="F36" s="105" t="inlineStr">
         <is>
           <t>Abre Ferida</t>
         </is>
@@ -14412,12 +14454,12 @@
       <c r="AX36" s="40" t="n"/>
       <c r="AY36" s="40" t="n"/>
       <c r="AZ36" s="40" t="n"/>
-      <c r="BA36" s="103" t="inlineStr">
+      <c r="BA36" s="105" t="inlineStr">
         <is>
           <t>à distância</t>
         </is>
       </c>
-      <c r="BB36" s="103" t="inlineStr">
+      <c r="BB36" s="105" t="inlineStr">
         <is>
           <t>AK44</t>
         </is>
@@ -14429,7 +14471,7 @@
       <c r="C37" s="40" t="n"/>
       <c r="D37" s="40" t="n"/>
       <c r="E37" s="40" t="n"/>
-      <c r="F37" s="103" t="inlineStr">
+      <c r="F37" s="105" t="inlineStr">
         <is>
           <t>Sobrecarga</t>
         </is>
@@ -14480,12 +14522,12 @@
       <c r="AX37" s="40" t="n"/>
       <c r="AY37" s="40" t="n"/>
       <c r="AZ37" s="40" t="n"/>
-      <c r="BA37" s="103" t="inlineStr">
+      <c r="BA37" s="105" t="inlineStr">
         <is>
           <t>maestria</t>
         </is>
       </c>
-      <c r="BB37" s="103" t="inlineStr">
+      <c r="BB37" s="105" t="inlineStr">
         <is>
           <t>D48</t>
         </is>
@@ -14497,7 +14539,7 @@
       <c r="C38" s="40" t="n"/>
       <c r="D38" s="40" t="n"/>
       <c r="E38" s="40" t="n"/>
-      <c r="F38" s="103" t="inlineStr">
+      <c r="F38" s="105" t="inlineStr">
         <is>
           <t>Firmeza</t>
         </is>
@@ -14548,12 +14590,12 @@
       <c r="AX38" s="40" t="n"/>
       <c r="AY38" s="40" t="n"/>
       <c r="AZ38" s="40" t="n"/>
-      <c r="BA38" s="103" t="inlineStr">
+      <c r="BA38" s="105" t="inlineStr">
         <is>
           <t>deslocamento</t>
         </is>
       </c>
-      <c r="BB38" s="103" t="inlineStr">
+      <c r="BB38" s="105" t="inlineStr">
         <is>
           <t>O48</t>
         </is>
@@ -14565,7 +14607,7 @@
       <c r="C39" s="40" t="n"/>
       <c r="D39" s="40" t="n"/>
       <c r="E39" s="40" t="n"/>
-      <c r="F39" s="103" t="inlineStr">
+      <c r="F39" s="105" t="inlineStr">
         <is>
           <t>Guarda</t>
         </is>
@@ -14616,12 +14658,12 @@
       <c r="AX39" s="40" t="n"/>
       <c r="AY39" s="40" t="n"/>
       <c r="AZ39" s="40" t="n"/>
-      <c r="BA39" s="103" t="inlineStr">
+      <c r="BA39" s="105" t="inlineStr">
         <is>
           <t>espaços de feitiço</t>
         </is>
       </c>
-      <c r="BB39" s="103" t="inlineStr">
+      <c r="BB39" s="105" t="inlineStr">
         <is>
           <t>D54</t>
         </is>
@@ -14633,7 +14675,7 @@
       <c r="C40" s="40" t="n"/>
       <c r="D40" s="40" t="n"/>
       <c r="E40" s="40" t="n"/>
-      <c r="F40" s="103" t="inlineStr">
+      <c r="F40" s="105" t="inlineStr">
         <is>
           <t>Pressa</t>
         </is>
@@ -14684,12 +14726,12 @@
       <c r="AX40" s="40" t="n"/>
       <c r="AY40" s="40" t="n"/>
       <c r="AZ40" s="40" t="n"/>
-      <c r="BA40" s="103" t="inlineStr">
+      <c r="BA40" s="105" t="inlineStr">
         <is>
           <t>refino de graça</t>
         </is>
       </c>
-      <c r="BB40" s="103" t="inlineStr">
+      <c r="BB40" s="105" t="inlineStr">
         <is>
           <t>O54</t>
         </is>
@@ -14701,7 +14743,7 @@
       <c r="C41" s="40" t="n"/>
       <c r="D41" s="40" t="n"/>
       <c r="E41" s="40" t="n"/>
-      <c r="F41" s="103" t="inlineStr">
+      <c r="F41" s="105" t="inlineStr">
         <is>
           <t>Enfraquece</t>
         </is>
@@ -14752,12 +14794,12 @@
       <c r="AX41" s="40" t="n"/>
       <c r="AY41" s="40" t="n"/>
       <c r="AZ41" s="40" t="n"/>
-      <c r="BA41" s="103" t="inlineStr">
+      <c r="BA41" s="105" t="inlineStr">
         <is>
           <t>classe máxima</t>
         </is>
       </c>
-      <c r="BB41" s="103" t="inlineStr">
+      <c r="BB41" s="105" t="inlineStr">
         <is>
           <t>Z54</t>
         </is>
@@ -14769,7 +14811,7 @@
       <c r="C42" s="40" t="n"/>
       <c r="D42" s="40" t="n"/>
       <c r="E42" s="40" t="n"/>
-      <c r="F42" s="103" t="inlineStr">
+      <c r="F42" s="105" t="inlineStr">
         <is>
           <t>Ecoa</t>
         </is>
@@ -14820,12 +14862,12 @@
       <c r="AX42" s="40" t="n"/>
       <c r="AY42" s="40" t="n"/>
       <c r="AZ42" s="40" t="n"/>
-      <c r="BA42" s="103" t="inlineStr">
+      <c r="BA42" s="105" t="inlineStr">
         <is>
           <t>classe 0 grátis</t>
         </is>
       </c>
-      <c r="BB42" s="103" t="inlineStr">
+      <c r="BB42" s="105" t="inlineStr">
         <is>
           <t>AK54</t>
         </is>
@@ -14837,7 +14879,7 @@
       <c r="C43" s="40" t="n"/>
       <c r="D43" s="40" t="n"/>
       <c r="E43" s="40" t="n"/>
-      <c r="F43" s="103" t="inlineStr">
+      <c r="F43" s="105" t="inlineStr">
         <is>
           <t>Queima</t>
         </is>
@@ -14897,7 +14939,7 @@
       <c r="C44" s="40" t="n"/>
       <c r="D44" s="40" t="n"/>
       <c r="E44" s="40" t="n"/>
-      <c r="F44" s="103" t="inlineStr">
+      <c r="F44" s="105" t="inlineStr">
         <is>
           <t>Acúmulo</t>
         </is>
@@ -14957,7 +14999,7 @@
       <c r="C45" s="40" t="n"/>
       <c r="D45" s="40" t="n"/>
       <c r="E45" s="40" t="n"/>
-      <c r="F45" s="103" t="inlineStr">
+      <c r="F45" s="105" t="inlineStr">
         <is>
           <t>Remate</t>
         </is>
@@ -15017,7 +15059,7 @@
       <c r="C46" s="40" t="n"/>
       <c r="D46" s="40" t="n"/>
       <c r="E46" s="40" t="n"/>
-      <c r="F46" s="103" t="inlineStr">
+      <c r="F46" s="105" t="inlineStr">
         <is>
           <t>Estilhaço</t>
         </is>
@@ -15077,7 +15119,7 @@
       <c r="C47" s="40" t="n"/>
       <c r="D47" s="40" t="n"/>
       <c r="E47" s="40" t="n"/>
-      <c r="F47" s="103" t="inlineStr">
+      <c r="F47" s="105" t="inlineStr">
         <is>
           <t>Quebra Coisa</t>
         </is>
@@ -15137,7 +15179,7 @@
       <c r="C48" s="40" t="n"/>
       <c r="D48" s="40" t="n"/>
       <c r="E48" s="40" t="n"/>
-      <c r="F48" s="103" t="inlineStr">
+      <c r="F48" s="105" t="inlineStr">
         <is>
           <t>Rasga Escudo</t>
         </is>
@@ -15197,7 +15239,7 @@
       <c r="C49" s="40" t="n"/>
       <c r="D49" s="40" t="n"/>
       <c r="E49" s="40" t="n"/>
-      <c r="F49" s="103" t="inlineStr">
+      <c r="F49" s="105" t="inlineStr">
         <is>
           <t>Sem Cura</t>
         </is>
@@ -15257,7 +15299,7 @@
       <c r="C50" s="40" t="n"/>
       <c r="D50" s="40" t="n"/>
       <c r="E50" s="40" t="n"/>
-      <c r="F50" s="103" t="inlineStr">
+      <c r="F50" s="105" t="inlineStr">
         <is>
           <t>Rápido</t>
         </is>
@@ -15317,7 +15359,7 @@
       <c r="C51" s="40" t="n"/>
       <c r="D51" s="40" t="n"/>
       <c r="E51" s="40" t="n"/>
-      <c r="F51" s="103" t="inlineStr">
+      <c r="F51" s="105" t="inlineStr">
         <is>
           <t>Reação</t>
         </is>
@@ -15377,7 +15419,7 @@
       <c r="C52" s="40" t="n"/>
       <c r="D52" s="40" t="n"/>
       <c r="E52" s="40" t="n"/>
-      <c r="F52" s="103" t="inlineStr">
+      <c r="F52" s="105" t="inlineStr">
         <is>
           <t>Armado</t>
         </is>
@@ -15437,7 +15479,7 @@
       <c r="C53" s="40" t="n"/>
       <c r="D53" s="40" t="n"/>
       <c r="E53" s="40" t="n"/>
-      <c r="F53" s="103" t="inlineStr">
+      <c r="F53" s="105" t="inlineStr">
         <is>
           <t>Silencioso</t>
         </is>
@@ -15497,7 +15539,7 @@
       <c r="C54" s="40" t="n"/>
       <c r="D54" s="40" t="n"/>
       <c r="E54" s="40" t="n"/>
-      <c r="F54" s="103" t="inlineStr">
+      <c r="F54" s="105" t="inlineStr">
         <is>
           <t>Adianta</t>
         </is>
@@ -15557,7 +15599,7 @@
       <c r="C55" s="40" t="n"/>
       <c r="D55" s="40" t="n"/>
       <c r="E55" s="40" t="n"/>
-      <c r="F55" s="103" t="inlineStr">
+      <c r="F55" s="105" t="inlineStr">
         <is>
           <t>Segura</t>
         </is>
@@ -15617,7 +15659,7 @@
       <c r="C56" s="40" t="n"/>
       <c r="D56" s="40" t="n"/>
       <c r="E56" s="40" t="n"/>
-      <c r="F56" s="103" t="inlineStr">
+      <c r="F56" s="105" t="inlineStr">
         <is>
           <t>Marca</t>
         </is>
@@ -15677,7 +15719,7 @@
       <c r="C57" s="40" t="n"/>
       <c r="D57" s="40" t="n"/>
       <c r="E57" s="40" t="n"/>
-      <c r="F57" s="103" t="inlineStr">
+      <c r="F57" s="105" t="inlineStr">
         <is>
           <t>Rastro</t>
         </is>
@@ -15737,7 +15779,7 @@
       <c r="C58" s="40" t="n"/>
       <c r="D58" s="40" t="n"/>
       <c r="E58" s="40" t="n"/>
-      <c r="F58" s="103" t="inlineStr">
+      <c r="F58" s="105" t="inlineStr">
         <is>
           <t>Sugar</t>
         </is>
@@ -15797,7 +15839,7 @@
       <c r="C59" s="40" t="n"/>
       <c r="D59" s="40" t="n"/>
       <c r="E59" s="40" t="n"/>
-      <c r="F59" s="103" t="inlineStr">
+      <c r="F59" s="105" t="inlineStr">
         <is>
           <t>Isca</t>
         </is>
@@ -15857,7 +15899,7 @@
       <c r="C60" s="40" t="n"/>
       <c r="D60" s="40" t="n"/>
       <c r="E60" s="40" t="n"/>
-      <c r="F60" s="103" t="inlineStr">
+      <c r="F60" s="105" t="inlineStr">
         <is>
           <t>Cobrança</t>
         </is>
@@ -15917,7 +15959,7 @@
       <c r="C61" s="40" t="n"/>
       <c r="D61" s="40" t="n"/>
       <c r="E61" s="40" t="n"/>
-      <c r="F61" s="103" t="inlineStr">
+      <c r="F61" s="105" t="inlineStr">
         <is>
           <t>Aviso</t>
         </is>
@@ -15977,7 +16019,7 @@
       <c r="C62" s="40" t="n"/>
       <c r="D62" s="40" t="n"/>
       <c r="E62" s="40" t="n"/>
-      <c r="F62" s="103" t="inlineStr">
+      <c r="F62" s="105" t="inlineStr">
         <is>
           <t>Limpa</t>
         </is>
@@ -16037,7 +16079,7 @@
       <c r="C63" s="40" t="n"/>
       <c r="D63" s="40" t="n"/>
       <c r="E63" s="40" t="n"/>
-      <c r="F63" s="103" t="inlineStr">
+      <c r="F63" s="105" t="inlineStr">
         <is>
           <t>Limpa Fundo</t>
         </is>
@@ -16097,7 +16139,7 @@
       <c r="C64" s="40" t="n"/>
       <c r="D64" s="40" t="n"/>
       <c r="E64" s="40" t="n"/>
-      <c r="F64" s="103" t="inlineStr">
+      <c r="F64" s="105" t="inlineStr">
         <is>
           <t>Levanta</t>
         </is>
@@ -16157,7 +16199,7 @@
       <c r="C65" s="40" t="n"/>
       <c r="D65" s="40" t="n"/>
       <c r="E65" s="40" t="n"/>
-      <c r="F65" s="103" t="inlineStr">
+      <c r="F65" s="105" t="inlineStr">
         <is>
           <t>Divide</t>
         </is>
@@ -16217,7 +16259,7 @@
       <c r="C66" s="40" t="n"/>
       <c r="D66" s="40" t="n"/>
       <c r="E66" s="40" t="n"/>
-      <c r="F66" s="103" t="inlineStr">
+      <c r="F66" s="105" t="inlineStr">
         <is>
           <t>Junto</t>
         </is>
@@ -16277,7 +16319,7 @@
       <c r="C67" s="40" t="n"/>
       <c r="D67" s="40" t="n"/>
       <c r="E67" s="40" t="n"/>
-      <c r="F67" s="103" t="inlineStr">
+      <c r="F67" s="105" t="inlineStr">
         <is>
           <t>Reserva</t>
         </is>
@@ -16337,7 +16379,7 @@
       <c r="C68" s="40" t="n"/>
       <c r="D68" s="40" t="n"/>
       <c r="E68" s="40" t="n"/>
-      <c r="F68" s="103" t="inlineStr">
+      <c r="F68" s="105" t="inlineStr">
         <is>
           <t>Remenda</t>
         </is>
@@ -16397,7 +16439,7 @@
       <c r="C69" s="40" t="n"/>
       <c r="D69" s="40" t="n"/>
       <c r="E69" s="40" t="n"/>
-      <c r="F69" s="103" t="inlineStr">
+      <c r="F69" s="105" t="inlineStr">
         <is>
           <t>Condicao</t>
         </is>

--- a/ficha-v01/ficha-projeto-m-0.1.xlsx
+++ b/ficha-v01/ficha-projeto-m-0.1.xlsx
@@ -4862,8 +4862,9 @@
     </row>
     <row r="23" ht="27" customHeight="1">
       <c r="C23" s="40" t="n"/>
-      <c r="D23" s="69" t="n">
-        <v>19</v>
+      <c r="D23" s="69">
+        <f>J23</f>
+        <v/>
       </c>
       <c r="E23" s="13" t="n"/>
       <c r="F23" s="13" t="n"/>
@@ -5071,8 +5072,9 @@
       <c r="A27" s="7" t="n"/>
       <c r="B27" s="7" t="n"/>
       <c r="C27" s="40" t="n"/>
-      <c r="D27" s="69" t="n">
-        <v>8</v>
+      <c r="D27" s="69">
+        <f>J27</f>
+        <v/>
       </c>
       <c r="E27" s="13" t="n"/>
       <c r="F27" s="13" t="n"/>
@@ -5287,8 +5289,9 @@
     </row>
     <row r="31" ht="27" customHeight="1">
       <c r="C31" s="40" t="n"/>
-      <c r="D31" s="69" t="n">
-        <v>25</v>
+      <c r="D31" s="69">
+        <f>J31</f>
+        <v/>
       </c>
       <c r="E31" s="13" t="n"/>
       <c r="F31" s="13" t="n"/>
